--- a/first-atlas/producao_2026-05.xlsx
+++ b/first-atlas/producao_2026-05.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11763A1D-191E-47D4-9FDA-C63C4F39276D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8E84E7-7C18-4387-B374-4D3D6B076743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13740" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="422">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -1008,6 +1008,303 @@
   </si>
   <si>
     <t>M A X DA COSTA</t>
+  </si>
+  <si>
+    <t>MENSAGERIA</t>
+  </si>
+  <si>
+    <t>25421772000128</t>
+  </si>
+  <si>
+    <t>ANDRE JUNIOR SOARES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>11756656000155</t>
+  </si>
+  <si>
+    <t>FEDERACAO PERNAMBUCANA DE KICK BOXING &amp; MUAY THAI-FPKM</t>
+  </si>
+  <si>
+    <t>32547089000105</t>
+  </si>
+  <si>
+    <t>ELISAINY MIGUEL DA SILVA</t>
+  </si>
+  <si>
+    <t>46291024000148</t>
+  </si>
+  <si>
+    <t>TRANSPORTADORA URBANO PEREIRA LTDA.</t>
+  </si>
+  <si>
+    <t>47187433000161</t>
+  </si>
+  <si>
+    <t>A. J. DA COSTA</t>
+  </si>
+  <si>
+    <t>CARIMBADA</t>
+  </si>
+  <si>
+    <t>49339840000172</t>
+  </si>
+  <si>
+    <t>KARIOCA CHIC LTDA</t>
+  </si>
+  <si>
+    <t>58453711000100</t>
+  </si>
+  <si>
+    <t>AP CONSTRUTORA ALTO PADRAO LTDA</t>
+  </si>
+  <si>
+    <t>47820239000171</t>
+  </si>
+  <si>
+    <t>LUIZ OTAVIO DE JESUS SILVA</t>
+  </si>
+  <si>
+    <t>11382283000108</t>
+  </si>
+  <si>
+    <t>E P G IMOVEIS LTDA</t>
+  </si>
+  <si>
+    <t>48554138000169</t>
+  </si>
+  <si>
+    <t>ECO BRAS PNEUS LTDA</t>
+  </si>
+  <si>
+    <t>43686734000189</t>
+  </si>
+  <si>
+    <t>RENOVACAO UNIFORMES LTDA</t>
+  </si>
+  <si>
+    <t>19337035000149</t>
+  </si>
+  <si>
+    <t>VANESSA MARIA CHAVES DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>63444967000182</t>
+  </si>
+  <si>
+    <t>63.444.967 JOSE FERREIRA BARRETO</t>
+  </si>
+  <si>
+    <t>52007915000122</t>
+  </si>
+  <si>
+    <t>52.007.915 JEFFERSON LUIS SEVERO DE LIMA</t>
+  </si>
+  <si>
+    <t>58526509000152</t>
+  </si>
+  <si>
+    <t>CJR ASSESSORIA LTDA</t>
+  </si>
+  <si>
+    <t>08274089000196</t>
+  </si>
+  <si>
+    <t>COOPERATIVA MISTA AGROPECUARIA DO NORTE COOMAN</t>
+  </si>
+  <si>
+    <t>44519527000100</t>
+  </si>
+  <si>
+    <t>JAQUELINA ARAUJO DOS SANTOS - FARMACIA</t>
+  </si>
+  <si>
+    <t>28615625000187</t>
+  </si>
+  <si>
+    <t>JULIO CESAR ANDRADE DE SANTANA</t>
+  </si>
+  <si>
+    <t>46110832000161</t>
+  </si>
+  <si>
+    <t>RONY TERRAPLANAGEM LTDA</t>
+  </si>
+  <si>
+    <t>21902896000174</t>
+  </si>
+  <si>
+    <t>ISABELA SANTOS TORRES</t>
+  </si>
+  <si>
+    <t>07644227000119</t>
+  </si>
+  <si>
+    <t>CRISTIANO RAFAEL DOS SANTOS BASTOS</t>
+  </si>
+  <si>
+    <t>51932206000190</t>
+  </si>
+  <si>
+    <t>COMERCIAL E DISTRIBUIDORA VIEIRA LTDA.</t>
+  </si>
+  <si>
+    <t>59849009000114</t>
+  </si>
+  <si>
+    <t>FRUTIFICA EQUIPAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>55711944000169</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA E DEPOSITO DE BEBIDAS MACEDO LTDA</t>
+  </si>
+  <si>
+    <t>64105762000135</t>
+  </si>
+  <si>
+    <t>Rso Consulting</t>
+  </si>
+  <si>
+    <t>21535080000150</t>
+  </si>
+  <si>
+    <t>TRANSPORTES MIX LTDA</t>
+  </si>
+  <si>
+    <t>55527449000102</t>
+  </si>
+  <si>
+    <t>COMERCIAL WAAL LTDA</t>
+  </si>
+  <si>
+    <t>43392156000178</t>
+  </si>
+  <si>
+    <t>ANDREA DOHASHI HIRUMITSU LTDA</t>
+  </si>
+  <si>
+    <t>32001338000154</t>
+  </si>
+  <si>
+    <t>CASA DOS PNEUS MECANICA LTDA</t>
+  </si>
+  <si>
+    <t>63696175000103</t>
+  </si>
+  <si>
+    <t>OC CARINHANHA ODONTOLOGIA LTDA</t>
+  </si>
+  <si>
+    <t>13525996000109</t>
+  </si>
+  <si>
+    <t>AGNALDO CHRISOSTOMO LTDA</t>
+  </si>
+  <si>
+    <t>54647423000127</t>
+  </si>
+  <si>
+    <t>COMPANY FACILITY SERVICE LTDA</t>
+  </si>
+  <si>
+    <t>47845669000148</t>
+  </si>
+  <si>
+    <t>47.845.669 LUCAS DE FREITAS RIBEIRO</t>
+  </si>
+  <si>
+    <t>42179120000148</t>
+  </si>
+  <si>
+    <t>SABRINA MOREIRA ORTIZ DE CAMARGO</t>
+  </si>
+  <si>
+    <t>31989492000113</t>
+  </si>
+  <si>
+    <t>LUIZ ROBSON DE MOURA SILVA</t>
+  </si>
+  <si>
+    <t>59961013000170</t>
+  </si>
+  <si>
+    <t>M.M. RODRIGUES MR CONSTRUTORA LTDA</t>
+  </si>
+  <si>
+    <t>56103255000134</t>
+  </si>
+  <si>
+    <t>COSME FERNANDES ESTEVAN</t>
+  </si>
+  <si>
+    <t>55637536000368</t>
+  </si>
+  <si>
+    <t>TONON PARK LTDA</t>
+  </si>
+  <si>
+    <t>69710978000143</t>
+  </si>
+  <si>
+    <t>QUEIJO COALHO SERTANEJO LTDA</t>
+  </si>
+  <si>
+    <t>52142244000102</t>
+  </si>
+  <si>
+    <t>JORGE ALEXANDRE OSHIRO CONSULTORIA EMPRESARIAL LTDA</t>
+  </si>
+  <si>
+    <t>41162871000199</t>
+  </si>
+  <si>
+    <t>RAFAEL LUCAS DIAS</t>
+  </si>
+  <si>
+    <t>48889027000103</t>
+  </si>
+  <si>
+    <t>WILLIAN LUIZ DE SOUZA CARVALHO</t>
+  </si>
+  <si>
+    <t>12214718000160</t>
+  </si>
+  <si>
+    <t>RITA DE CASSIA S. SALES LTDA.</t>
+  </si>
+  <si>
+    <t>12929271000105</t>
+  </si>
+  <si>
+    <t>NATURAL ENGENHARIA LTDA</t>
+  </si>
+  <si>
+    <t>31770900000141</t>
+  </si>
+  <si>
+    <t>EMILENE TSUNEA DARE MIYAMOTO SILVA</t>
+  </si>
+  <si>
+    <t>29328375000167</t>
+  </si>
+  <si>
+    <t>ENOVAR CONSTRUTORA LTDA</t>
+  </si>
+  <si>
+    <t>05296627000155</t>
+  </si>
+  <si>
+    <t>NUTRY SERTAO LTDA</t>
+  </si>
+  <si>
+    <t>63934397000109</t>
+  </si>
+  <si>
+    <t>AGRO XUI LTDA</t>
+  </si>
+  <si>
+    <t>Ata de eleicao da diretoria atualizada e registrado no orgao competente&lt;br&gt;&lt;br&gt;Estatuto social atualizado e registrado no orgao competente</t>
   </si>
 </sst>
 </file>
@@ -1380,7 +1677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:H142"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -2376,7 +2673,7 @@
         <v>8</v>
       </c>
       <c r="G38" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H38" t="s">
         <v>37</v>
@@ -3829,7 +4126,7 @@
         <v>7</v>
       </c>
       <c r="G94" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -4193,7 +4490,7 @@
         <v>8</v>
       </c>
       <c r="G108" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -4219,7 +4516,7 @@
         <v>7</v>
       </c>
       <c r="G109" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -4349,7 +4646,7 @@
         <v>8</v>
       </c>
       <c r="G114" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H114">
         <v>0</v>
@@ -4375,7 +4672,7 @@
         <v>7</v>
       </c>
       <c r="G115" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H115">
         <v>0</v>
@@ -4453,7 +4750,10 @@
         <v>7</v>
       </c>
       <c r="G118" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -4554,7 +4854,7 @@
         <v>7</v>
       </c>
       <c r="G122" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H122">
         <v>0</v>
@@ -4681,7 +4981,10 @@
         <v>8</v>
       </c>
       <c r="G127" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -4704,7 +5007,7 @@
         <v>7</v>
       </c>
       <c r="G128" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -4730,7 +5033,7 @@
         <v>8</v>
       </c>
       <c r="G129" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H129">
         <v>0</v>
@@ -5071,6 +5374,1248 @@
         <v>17</v>
       </c>
       <c r="H142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B143" t="s">
+        <v>324</v>
+      </c>
+      <c r="C143" t="s">
+        <v>325</v>
+      </c>
+      <c r="D143" t="s">
+        <v>6</v>
+      </c>
+      <c r="E143" t="s">
+        <v>29</v>
+      </c>
+      <c r="F143" t="s">
+        <v>7</v>
+      </c>
+      <c r="G143" t="s">
+        <v>17</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B144" t="s">
+        <v>326</v>
+      </c>
+      <c r="C144" t="s">
+        <v>327</v>
+      </c>
+      <c r="D144" t="s">
+        <v>9</v>
+      </c>
+      <c r="E144" t="s">
+        <v>31</v>
+      </c>
+      <c r="F144" t="s">
+        <v>7</v>
+      </c>
+      <c r="G144" t="s">
+        <v>36</v>
+      </c>
+      <c r="H144" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B145" t="s">
+        <v>328</v>
+      </c>
+      <c r="C145" t="s">
+        <v>329</v>
+      </c>
+      <c r="D145" t="s">
+        <v>22</v>
+      </c>
+      <c r="E145" t="s">
+        <v>31</v>
+      </c>
+      <c r="F145" t="s">
+        <v>7</v>
+      </c>
+      <c r="G145" t="s">
+        <v>17</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B146" t="s">
+        <v>330</v>
+      </c>
+      <c r="C146" t="s">
+        <v>331</v>
+      </c>
+      <c r="D146" t="s">
+        <v>13</v>
+      </c>
+      <c r="E146" t="s">
+        <v>29</v>
+      </c>
+      <c r="F146" t="s">
+        <v>8</v>
+      </c>
+      <c r="G146" t="s">
+        <v>19</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B147" t="s">
+        <v>332</v>
+      </c>
+      <c r="C147" t="s">
+        <v>333</v>
+      </c>
+      <c r="D147" t="s">
+        <v>42</v>
+      </c>
+      <c r="E147" t="s">
+        <v>29</v>
+      </c>
+      <c r="F147" t="s">
+        <v>8</v>
+      </c>
+      <c r="G147" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B148" t="s">
+        <v>335</v>
+      </c>
+      <c r="C148" t="s">
+        <v>336</v>
+      </c>
+      <c r="D148" t="s">
+        <v>14</v>
+      </c>
+      <c r="E148" t="s">
+        <v>29</v>
+      </c>
+      <c r="F148" t="s">
+        <v>8</v>
+      </c>
+      <c r="G148" t="s">
+        <v>19</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>337</v>
+      </c>
+      <c r="C149" t="s">
+        <v>338</v>
+      </c>
+      <c r="D149" t="s">
+        <v>42</v>
+      </c>
+      <c r="E149" t="s">
+        <v>29</v>
+      </c>
+      <c r="F149" t="s">
+        <v>8</v>
+      </c>
+      <c r="G149" t="s">
+        <v>18</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B150" t="s">
+        <v>339</v>
+      </c>
+      <c r="C150" t="s">
+        <v>340</v>
+      </c>
+      <c r="D150" t="s">
+        <v>27</v>
+      </c>
+      <c r="E150" t="s">
+        <v>31</v>
+      </c>
+      <c r="F150" t="s">
+        <v>7</v>
+      </c>
+      <c r="G150" t="s">
+        <v>19</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B151" t="s">
+        <v>341</v>
+      </c>
+      <c r="C151" t="s">
+        <v>342</v>
+      </c>
+      <c r="D151" t="s">
+        <v>6</v>
+      </c>
+      <c r="E151" t="s">
+        <v>29</v>
+      </c>
+      <c r="F151" t="s">
+        <v>8</v>
+      </c>
+      <c r="G151" t="s">
+        <v>17</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B152" t="s">
+        <v>343</v>
+      </c>
+      <c r="C152" t="s">
+        <v>344</v>
+      </c>
+      <c r="D152" t="s">
+        <v>26</v>
+      </c>
+      <c r="E152" t="s">
+        <v>29</v>
+      </c>
+      <c r="F152" t="s">
+        <v>8</v>
+      </c>
+      <c r="G152" t="s">
+        <v>17</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B153" t="s">
+        <v>345</v>
+      </c>
+      <c r="C153" t="s">
+        <v>346</v>
+      </c>
+      <c r="D153" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" t="s">
+        <v>29</v>
+      </c>
+      <c r="F153" t="s">
+        <v>8</v>
+      </c>
+      <c r="G153" t="s">
+        <v>17</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B154" t="s">
+        <v>347</v>
+      </c>
+      <c r="C154" t="s">
+        <v>348</v>
+      </c>
+      <c r="D154" t="s">
+        <v>13</v>
+      </c>
+      <c r="E154" t="s">
+        <v>29</v>
+      </c>
+      <c r="F154" t="s">
+        <v>8</v>
+      </c>
+      <c r="G154" t="s">
+        <v>17</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B155" t="s">
+        <v>349</v>
+      </c>
+      <c r="C155" t="s">
+        <v>350</v>
+      </c>
+      <c r="D155" t="s">
+        <v>42</v>
+      </c>
+      <c r="E155" t="s">
+        <v>29</v>
+      </c>
+      <c r="F155" t="s">
+        <v>8</v>
+      </c>
+      <c r="G155" t="s">
+        <v>17</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B156" t="s">
+        <v>351</v>
+      </c>
+      <c r="C156" t="s">
+        <v>352</v>
+      </c>
+      <c r="D156" t="s">
+        <v>27</v>
+      </c>
+      <c r="E156" t="s">
+        <v>31</v>
+      </c>
+      <c r="F156" t="s">
+        <v>323</v>
+      </c>
+      <c r="G156" t="s">
+        <v>17</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B157" t="s">
+        <v>353</v>
+      </c>
+      <c r="C157" t="s">
+        <v>354</v>
+      </c>
+      <c r="D157" t="s">
+        <v>41</v>
+      </c>
+      <c r="E157" t="s">
+        <v>31</v>
+      </c>
+      <c r="F157" t="s">
+        <v>7</v>
+      </c>
+      <c r="G157" t="s">
+        <v>17</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B158" t="s">
+        <v>355</v>
+      </c>
+      <c r="C158" t="s">
+        <v>356</v>
+      </c>
+      <c r="D158" t="s">
+        <v>38</v>
+      </c>
+      <c r="E158" t="s">
+        <v>31</v>
+      </c>
+      <c r="F158" t="s">
+        <v>7</v>
+      </c>
+      <c r="G158" t="s">
+        <v>19</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B159" t="s">
+        <v>357</v>
+      </c>
+      <c r="C159" t="s">
+        <v>358</v>
+      </c>
+      <c r="D159" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" t="s">
+        <v>31</v>
+      </c>
+      <c r="F159" t="s">
+        <v>7</v>
+      </c>
+      <c r="G159" t="s">
+        <v>18</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B160" t="s">
+        <v>359</v>
+      </c>
+      <c r="C160" t="s">
+        <v>360</v>
+      </c>
+      <c r="D160" t="s">
+        <v>12</v>
+      </c>
+      <c r="E160" t="s">
+        <v>29</v>
+      </c>
+      <c r="F160" t="s">
+        <v>7</v>
+      </c>
+      <c r="G160" t="s">
+        <v>17</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B161" t="s">
+        <v>361</v>
+      </c>
+      <c r="C161" t="s">
+        <v>362</v>
+      </c>
+      <c r="D161" t="s">
+        <v>20</v>
+      </c>
+      <c r="E161" t="s">
+        <v>29</v>
+      </c>
+      <c r="F161" t="s">
+        <v>8</v>
+      </c>
+      <c r="G161" t="s">
+        <v>18</v>
+      </c>
+      <c r="H161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B162" t="s">
+        <v>363</v>
+      </c>
+      <c r="C162" t="s">
+        <v>364</v>
+      </c>
+      <c r="D162" t="s">
+        <v>41</v>
+      </c>
+      <c r="E162" t="s">
+        <v>31</v>
+      </c>
+      <c r="F162" t="s">
+        <v>7</v>
+      </c>
+      <c r="G162" t="s">
+        <v>17</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B163" t="s">
+        <v>365</v>
+      </c>
+      <c r="C163" t="s">
+        <v>366</v>
+      </c>
+      <c r="D163" t="s">
+        <v>6</v>
+      </c>
+      <c r="E163" t="s">
+        <v>29</v>
+      </c>
+      <c r="F163" t="s">
+        <v>8</v>
+      </c>
+      <c r="G163" t="s">
+        <v>19</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B164" t="s">
+        <v>367</v>
+      </c>
+      <c r="C164" t="s">
+        <v>368</v>
+      </c>
+      <c r="D164" t="s">
+        <v>26</v>
+      </c>
+      <c r="E164" t="s">
+        <v>29</v>
+      </c>
+      <c r="F164" t="s">
+        <v>8</v>
+      </c>
+      <c r="G164" t="s">
+        <v>19</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B165" t="s">
+        <v>369</v>
+      </c>
+      <c r="C165" t="s">
+        <v>370</v>
+      </c>
+      <c r="D165" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165" t="s">
+        <v>29</v>
+      </c>
+      <c r="F165" t="s">
+        <v>8</v>
+      </c>
+      <c r="G165" t="s">
+        <v>17</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B166" t="s">
+        <v>371</v>
+      </c>
+      <c r="C166" t="s">
+        <v>372</v>
+      </c>
+      <c r="D166" t="s">
+        <v>6</v>
+      </c>
+      <c r="E166" t="s">
+        <v>29</v>
+      </c>
+      <c r="F166" t="s">
+        <v>8</v>
+      </c>
+      <c r="G166" t="s">
+        <v>17</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B167" t="s">
+        <v>373</v>
+      </c>
+      <c r="C167" t="s">
+        <v>374</v>
+      </c>
+      <c r="D167" t="s">
+        <v>32</v>
+      </c>
+      <c r="E167" t="s">
+        <v>31</v>
+      </c>
+      <c r="F167" t="s">
+        <v>7</v>
+      </c>
+      <c r="G167" t="s">
+        <v>17</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B168" t="s">
+        <v>375</v>
+      </c>
+      <c r="C168" t="s">
+        <v>376</v>
+      </c>
+      <c r="D168" t="s">
+        <v>14</v>
+      </c>
+      <c r="E168" t="s">
+        <v>29</v>
+      </c>
+      <c r="F168" t="s">
+        <v>8</v>
+      </c>
+      <c r="G168" t="s">
+        <v>19</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B169" t="s">
+        <v>377</v>
+      </c>
+      <c r="C169" t="s">
+        <v>378</v>
+      </c>
+      <c r="D169" t="s">
+        <v>27</v>
+      </c>
+      <c r="E169" t="s">
+        <v>31</v>
+      </c>
+      <c r="F169" t="s">
+        <v>323</v>
+      </c>
+      <c r="G169" t="s">
+        <v>18</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B170" t="s">
+        <v>379</v>
+      </c>
+      <c r="C170" t="s">
+        <v>380</v>
+      </c>
+      <c r="D170" t="s">
+        <v>15</v>
+      </c>
+      <c r="E170" t="s">
+        <v>29</v>
+      </c>
+      <c r="F170" t="s">
+        <v>8</v>
+      </c>
+      <c r="G170" t="s">
+        <v>17</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B171" t="s">
+        <v>381</v>
+      </c>
+      <c r="C171" t="s">
+        <v>382</v>
+      </c>
+      <c r="D171" t="s">
+        <v>13</v>
+      </c>
+      <c r="E171" t="s">
+        <v>29</v>
+      </c>
+      <c r="F171" t="s">
+        <v>8</v>
+      </c>
+      <c r="G171" t="s">
+        <v>17</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B172" t="s">
+        <v>383</v>
+      </c>
+      <c r="C172" t="s">
+        <v>384</v>
+      </c>
+      <c r="D172" t="s">
+        <v>27</v>
+      </c>
+      <c r="E172" t="s">
+        <v>31</v>
+      </c>
+      <c r="F172" t="s">
+        <v>323</v>
+      </c>
+      <c r="G172" t="s">
+        <v>36</v>
+      </c>
+      <c r="H172" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B173" t="s">
+        <v>385</v>
+      </c>
+      <c r="C173" t="s">
+        <v>386</v>
+      </c>
+      <c r="D173" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" t="s">
+        <v>31</v>
+      </c>
+      <c r="F173" t="s">
+        <v>7</v>
+      </c>
+      <c r="G173" t="s">
+        <v>19</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B174" t="s">
+        <v>387</v>
+      </c>
+      <c r="C174" t="s">
+        <v>388</v>
+      </c>
+      <c r="D174" t="s">
+        <v>42</v>
+      </c>
+      <c r="E174" t="s">
+        <v>29</v>
+      </c>
+      <c r="F174" t="s">
+        <v>8</v>
+      </c>
+      <c r="G174" t="s">
+        <v>17</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B175" t="s">
+        <v>389</v>
+      </c>
+      <c r="C175" t="s">
+        <v>390</v>
+      </c>
+      <c r="D175" t="s">
+        <v>14</v>
+      </c>
+      <c r="E175" t="s">
+        <v>29</v>
+      </c>
+      <c r="F175" t="s">
+        <v>8</v>
+      </c>
+      <c r="G175" t="s">
+        <v>19</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B176" t="s">
+        <v>391</v>
+      </c>
+      <c r="C176" t="s">
+        <v>392</v>
+      </c>
+      <c r="D176" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" t="s">
+        <v>29</v>
+      </c>
+      <c r="F176" t="s">
+        <v>8</v>
+      </c>
+      <c r="G176" t="s">
+        <v>17</v>
+      </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B177" t="s">
+        <v>393</v>
+      </c>
+      <c r="C177" t="s">
+        <v>394</v>
+      </c>
+      <c r="D177" t="s">
+        <v>14</v>
+      </c>
+      <c r="E177" t="s">
+        <v>29</v>
+      </c>
+      <c r="F177" t="s">
+        <v>8</v>
+      </c>
+      <c r="G177" t="s">
+        <v>17</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B178" t="s">
+        <v>395</v>
+      </c>
+      <c r="C178" t="s">
+        <v>396</v>
+      </c>
+      <c r="D178" t="s">
+        <v>13</v>
+      </c>
+      <c r="E178" t="s">
+        <v>29</v>
+      </c>
+      <c r="F178" t="s">
+        <v>8</v>
+      </c>
+      <c r="G178" t="s">
+        <v>17</v>
+      </c>
+      <c r="H178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B179" t="s">
+        <v>397</v>
+      </c>
+      <c r="C179" t="s">
+        <v>398</v>
+      </c>
+      <c r="D179" t="s">
+        <v>23</v>
+      </c>
+      <c r="E179" t="s">
+        <v>31</v>
+      </c>
+      <c r="F179" t="s">
+        <v>7</v>
+      </c>
+      <c r="G179" t="s">
+        <v>18</v>
+      </c>
+      <c r="H179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B180" t="s">
+        <v>399</v>
+      </c>
+      <c r="C180" t="s">
+        <v>400</v>
+      </c>
+      <c r="D180" t="s">
+        <v>42</v>
+      </c>
+      <c r="E180" t="s">
+        <v>29</v>
+      </c>
+      <c r="F180" t="s">
+        <v>8</v>
+      </c>
+      <c r="G180" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B181" t="s">
+        <v>401</v>
+      </c>
+      <c r="C181" t="s">
+        <v>402</v>
+      </c>
+      <c r="D181" t="s">
+        <v>35</v>
+      </c>
+      <c r="E181" t="s">
+        <v>31</v>
+      </c>
+      <c r="F181" t="s">
+        <v>7</v>
+      </c>
+      <c r="G181" t="s">
+        <v>19</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B182" t="s">
+        <v>403</v>
+      </c>
+      <c r="C182" t="s">
+        <v>404</v>
+      </c>
+      <c r="D182" t="s">
+        <v>42</v>
+      </c>
+      <c r="E182" t="s">
+        <v>29</v>
+      </c>
+      <c r="F182" t="s">
+        <v>8</v>
+      </c>
+      <c r="G182" t="s">
+        <v>17</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B183" t="s">
+        <v>405</v>
+      </c>
+      <c r="C183" t="s">
+        <v>406</v>
+      </c>
+      <c r="D183" t="s">
+        <v>23</v>
+      </c>
+      <c r="E183" t="s">
+        <v>31</v>
+      </c>
+      <c r="F183" t="s">
+        <v>7</v>
+      </c>
+      <c r="G183" t="s">
+        <v>17</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B184" t="s">
+        <v>407</v>
+      </c>
+      <c r="C184" t="s">
+        <v>408</v>
+      </c>
+      <c r="D184" t="s">
+        <v>26</v>
+      </c>
+      <c r="E184" t="s">
+        <v>29</v>
+      </c>
+      <c r="F184" t="s">
+        <v>8</v>
+      </c>
+      <c r="G184" t="s">
+        <v>17</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B185" t="s">
+        <v>409</v>
+      </c>
+      <c r="C185" t="s">
+        <v>410</v>
+      </c>
+      <c r="D185" t="s">
+        <v>23</v>
+      </c>
+      <c r="E185" t="s">
+        <v>31</v>
+      </c>
+      <c r="F185" t="s">
+        <v>7</v>
+      </c>
+      <c r="G185" t="s">
+        <v>17</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B186" t="s">
+        <v>411</v>
+      </c>
+      <c r="C186" t="s">
+        <v>412</v>
+      </c>
+      <c r="D186" t="s">
+        <v>14</v>
+      </c>
+      <c r="E186" t="s">
+        <v>29</v>
+      </c>
+      <c r="F186" t="s">
+        <v>8</v>
+      </c>
+      <c r="G186" t="s">
+        <v>17</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B187" t="s">
+        <v>413</v>
+      </c>
+      <c r="C187" t="s">
+        <v>414</v>
+      </c>
+      <c r="D187" t="s">
+        <v>6</v>
+      </c>
+      <c r="E187" t="s">
+        <v>29</v>
+      </c>
+      <c r="F187" t="s">
+        <v>8</v>
+      </c>
+      <c r="G187" t="s">
+        <v>17</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B188" t="s">
+        <v>415</v>
+      </c>
+      <c r="C188" t="s">
+        <v>416</v>
+      </c>
+      <c r="D188" t="s">
+        <v>22</v>
+      </c>
+      <c r="E188" t="s">
+        <v>31</v>
+      </c>
+      <c r="F188" t="s">
+        <v>7</v>
+      </c>
+      <c r="G188" t="s">
+        <v>17</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B189" t="s">
+        <v>417</v>
+      </c>
+      <c r="C189" t="s">
+        <v>418</v>
+      </c>
+      <c r="D189" t="s">
+        <v>11</v>
+      </c>
+      <c r="E189" t="s">
+        <v>29</v>
+      </c>
+      <c r="F189" t="s">
+        <v>8</v>
+      </c>
+      <c r="G189" t="s">
+        <v>17</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B190" t="s">
+        <v>419</v>
+      </c>
+      <c r="C190" t="s">
+        <v>420</v>
+      </c>
+      <c r="D190" t="s">
+        <v>42</v>
+      </c>
+      <c r="E190" t="s">
+        <v>29</v>
+      </c>
+      <c r="F190" t="s">
+        <v>8</v>
+      </c>
+      <c r="G190" t="s">
+        <v>17</v>
+      </c>
+      <c r="H190">
         <v>0</v>
       </c>
     </row>

--- a/first-atlas/producao_2026-05.xlsx
+++ b/first-atlas/producao_2026-05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8E84E7-7C18-4387-B374-4D3D6B076743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E04CDD-23C0-4F5C-BD0B-B45418B403C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13740" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="675">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -1305,6 +1305,765 @@
   </si>
   <si>
     <t>Ata de eleicao da diretoria atualizada e registrado no orgao competente&lt;br&gt;&lt;br&gt;Estatuto social atualizado e registrado no orgao competente</t>
+  </si>
+  <si>
+    <t>38711291000107</t>
+  </si>
+  <si>
+    <t>LONDRI - KIT INDUSTRIA E COMERCIO DE FERRAGENS LTDA</t>
+  </si>
+  <si>
+    <t>29403208000133</t>
+  </si>
+  <si>
+    <t>JULIO MACHADO SOARES NETO</t>
+  </si>
+  <si>
+    <t>14198330000148</t>
+  </si>
+  <si>
+    <t>HR REPRESENTACOES, CONSULTORIA E PESQUISA LTDA</t>
+  </si>
+  <si>
+    <t>64712643000140</t>
+  </si>
+  <si>
+    <t>FG PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>63896606000177</t>
+  </si>
+  <si>
+    <t>DJ&amp;A PREMOLDADOS E TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>56012911000193</t>
+  </si>
+  <si>
+    <t>CAIQUE PAULO AIRES DA SILVA E OUTROS</t>
+  </si>
+  <si>
+    <t>40115084000123</t>
+  </si>
+  <si>
+    <t>JOAO PRADO E JOAO GODOY TRANSPORTE E LOGISTICA LTDA</t>
+  </si>
+  <si>
+    <t>63233341000127</t>
+  </si>
+  <si>
+    <t>GOLDEN GLOBAL GRUOP INOVA SIMPLES (I.S.)</t>
+  </si>
+  <si>
+    <t>24190868000160</t>
+  </si>
+  <si>
+    <t>CENTRO DE REABILITACAO INTEGRADA DOUTOR ASSIS FILIPE ALBUQUERQUE LTDA</t>
+  </si>
+  <si>
+    <t>35266398000278</t>
+  </si>
+  <si>
+    <t>PAVTERRA TERRAPLENAGEM LTDA</t>
+  </si>
+  <si>
+    <t>00905533000112</t>
+  </si>
+  <si>
+    <t>REALPLAN - PLANEJAMENTO E CONSTRUCOES LTDA</t>
+  </si>
+  <si>
+    <t>INVÁLIDA</t>
+  </si>
+  <si>
+    <t>31500248000145</t>
+  </si>
+  <si>
+    <t>AUTO TECH MECANICA AUTOMOTIVA LTDA</t>
+  </si>
+  <si>
+    <t>18800574000100</t>
+  </si>
+  <si>
+    <t>ROQUE R. ROCHA LTDA</t>
+  </si>
+  <si>
+    <t>07710555000176</t>
+  </si>
+  <si>
+    <t>CLUBE DE MAES E CRECHE ESCOLA COMUNITARIA RENASCER</t>
+  </si>
+  <si>
+    <t>31414041000158</t>
+  </si>
+  <si>
+    <t>LOSANGELES MARACAJA CANUTO</t>
+  </si>
+  <si>
+    <t>36532103000140</t>
+  </si>
+  <si>
+    <t>LETS RANKING SERVICOS E SOLUCOES EM TI LTDA</t>
+  </si>
+  <si>
+    <t>62791906000129</t>
+  </si>
+  <si>
+    <t>PEPPLOW &amp; PEREIRA COMERCIO DE PNEUS E ACESSORIOS LTDA</t>
+  </si>
+  <si>
+    <t>36420509000130</t>
+  </si>
+  <si>
+    <t>SIDNEY JAIR MENDES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>55664810000134</t>
+  </si>
+  <si>
+    <t>K M SOUSA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Mensageria</t>
+  </si>
+  <si>
+    <t>64929065000107</t>
+  </si>
+  <si>
+    <t>FORBODY ACADEMIA FITNESS LTDA</t>
+  </si>
+  <si>
+    <t>16359515000112</t>
+  </si>
+  <si>
+    <t>PAIAIA COMUNICACAO LTDA</t>
+  </si>
+  <si>
+    <t>64016374000188</t>
+  </si>
+  <si>
+    <t>64.016.374 ANA KATARINA FERREIRA DE LIMA</t>
+  </si>
+  <si>
+    <t>29060203000155</t>
+  </si>
+  <si>
+    <t>ADRIANO MACHADO CONSULTORIA</t>
+  </si>
+  <si>
+    <t>56949328000103</t>
+  </si>
+  <si>
+    <t>56.949.328 ISRAEL SOUSA SANTOS</t>
+  </si>
+  <si>
+    <t>18665956000178</t>
+  </si>
+  <si>
+    <t>PIZZARIA BIG HOUSE LTDA</t>
+  </si>
+  <si>
+    <t>20741033000108</t>
+  </si>
+  <si>
+    <t>CONDOTTA COMERCIO DE BATERIAS E ACESSORIOS AUTOMOTIVOS LTDA</t>
+  </si>
+  <si>
+    <t>28331279000105</t>
+  </si>
+  <si>
+    <t>ELETROKASA LTDA</t>
+  </si>
+  <si>
+    <t>36781165000195</t>
+  </si>
+  <si>
+    <t>JOAO VITOR SANTOS NOGUEIRA</t>
+  </si>
+  <si>
+    <t>36655797000102</t>
+  </si>
+  <si>
+    <t>LUIZ FERNANDO FRANZNER</t>
+  </si>
+  <si>
+    <t>50866610000140</t>
+  </si>
+  <si>
+    <t>50.866.610 SEBASTIAO GONCALVES DE QUEIROZ</t>
+  </si>
+  <si>
+    <t>13945323000108</t>
+  </si>
+  <si>
+    <t>ERIKA ACADEMIA PERSONALIZADA LTDA</t>
+  </si>
+  <si>
+    <t>26295556000146</t>
+  </si>
+  <si>
+    <t>MARCIO JARDEL DE CASTRO</t>
+  </si>
+  <si>
+    <t>51174735000172</t>
+  </si>
+  <si>
+    <t>BS &amp; AS CONFEITARIA LTDA</t>
+  </si>
+  <si>
+    <t>59098502000140</t>
+  </si>
+  <si>
+    <t>ALYNE RACHEL MOREIRA FERNANDES ESTRELA LTDA</t>
+  </si>
+  <si>
+    <t>64277065000161</t>
+  </si>
+  <si>
+    <t>Phablo Henrique Montalvao Manchini de Oliveira</t>
+  </si>
+  <si>
+    <t>51274659000177</t>
+  </si>
+  <si>
+    <t>JOSIVALDO DA CRUZ ARAUJO</t>
+  </si>
+  <si>
+    <t>Julia Tamiris Ramos Machado</t>
+  </si>
+  <si>
+    <t>53269872000116</t>
+  </si>
+  <si>
+    <t>CB REFRIGERACAO GELATO LTDA</t>
+  </si>
+  <si>
+    <t>40118312000119</t>
+  </si>
+  <si>
+    <t>VIA NORDESTE REPRESENTACOES LTDA</t>
+  </si>
+  <si>
+    <t>02013394000148</t>
+  </si>
+  <si>
+    <t>LCP QUEIROZ LTDA</t>
+  </si>
+  <si>
+    <t>61880041000104</t>
+  </si>
+  <si>
+    <t>HIPER 1.99 COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>29294426000187</t>
+  </si>
+  <si>
+    <t>EDSON RIBEIRO</t>
+  </si>
+  <si>
+    <t>22770524000102</t>
+  </si>
+  <si>
+    <t>NILO MANUTENCAO E RECUPERACAO DE MATERIAIS LTDA</t>
+  </si>
+  <si>
+    <t>34186835000108</t>
+  </si>
+  <si>
+    <t>LIMPA FOSSA E DESENTUPIDORA IDEAL LTDA</t>
+  </si>
+  <si>
+    <t>66184861000185</t>
+  </si>
+  <si>
+    <t>NEO ENDO LTDA</t>
+  </si>
+  <si>
+    <t>57417275000142</t>
+  </si>
+  <si>
+    <t>57.417.275 DAVID RODRIGUES NASCIMENTO</t>
+  </si>
+  <si>
+    <t>18718785000106</t>
+  </si>
+  <si>
+    <t>LUCIANO CHAVES DIAS</t>
+  </si>
+  <si>
+    <t>26708097000185</t>
+  </si>
+  <si>
+    <t>ROGER CHAVES MACHADO</t>
+  </si>
+  <si>
+    <t>51784210000159</t>
+  </si>
+  <si>
+    <t>JS6 HOLDING PARTICIPACOES LTDA</t>
+  </si>
+  <si>
+    <t>LEAD MANUAL</t>
+  </si>
+  <si>
+    <t>66132660000134</t>
+  </si>
+  <si>
+    <t>RJMC CONSULT LTDA</t>
+  </si>
+  <si>
+    <t>15590982000196</t>
+  </si>
+  <si>
+    <t>GARCIA UTILIDADES DO LAR LTDA</t>
+  </si>
+  <si>
+    <t>47228748000100</t>
+  </si>
+  <si>
+    <t>PALOMA BERGMANN MARTINS MANUTENCAO ELETRICA LTDA</t>
+  </si>
+  <si>
+    <t>41429733000123</t>
+  </si>
+  <si>
+    <t>LAUDINEI SILVA AVELINO SERRALHERIA E PRESTACAO DE SERVICOS</t>
+  </si>
+  <si>
+    <t>37934933000166</t>
+  </si>
+  <si>
+    <t>C H C NASCIMENTO</t>
+  </si>
+  <si>
+    <t>28609926000106</t>
+  </si>
+  <si>
+    <t>PATRICIA LETICIA COSTA DE SOUZA</t>
+  </si>
+  <si>
+    <t>32521283000103</t>
+  </si>
+  <si>
+    <t>ARIEL GUSTAVO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>62798968000162</t>
+  </si>
+  <si>
+    <t>S L PADRAO GESSO LTDA</t>
+  </si>
+  <si>
+    <t>11407190000182</t>
+  </si>
+  <si>
+    <t>MARINA CENTER CAR LTDA</t>
+  </si>
+  <si>
+    <t>54067696000100</t>
+  </si>
+  <si>
+    <t>ADENIR DE LIMA MOURA LTDA</t>
+  </si>
+  <si>
+    <t>44215683000170</t>
+  </si>
+  <si>
+    <t>MIQUEIAS ANDRE COSTA</t>
+  </si>
+  <si>
+    <t>61973653000141</t>
+  </si>
+  <si>
+    <t>TKS COMERCIO E DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>18986452000150</t>
+  </si>
+  <si>
+    <t>EDNALDO AUTO TOPCAR LTDA</t>
+  </si>
+  <si>
+    <t>24250107000156</t>
+  </si>
+  <si>
+    <t>JOSE ROBERIO GONCALVES</t>
+  </si>
+  <si>
+    <t>33175404000175</t>
+  </si>
+  <si>
+    <t>P2W INSTALACOES ELETRICAS E REFORMAS EM GERAL LTDA</t>
+  </si>
+  <si>
+    <t>37657041000165</t>
+  </si>
+  <si>
+    <t>SERMAQ MOTORES E MAQUINAS LTDA</t>
+  </si>
+  <si>
+    <t>14691119000162</t>
+  </si>
+  <si>
+    <t>DS LOPES COMERCIO DE VIDROS E PORTOES LTDA</t>
+  </si>
+  <si>
+    <t>31859608000108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIAGO STEFENON PAESE </t>
+  </si>
+  <si>
+    <t>00330246000121</t>
+  </si>
+  <si>
+    <t>FERNANDO APARECIDO PEREIRA LEITE</t>
+  </si>
+  <si>
+    <t>62034648000136</t>
+  </si>
+  <si>
+    <t>LEANDRO DE CARVALHO ROSARIO</t>
+  </si>
+  <si>
+    <t>66109121000184</t>
+  </si>
+  <si>
+    <t>S B DE FARIAS LTDA</t>
+  </si>
+  <si>
+    <t>48858558000139</t>
+  </si>
+  <si>
+    <t>48.858.558 ANA BEATRIZ CAMPOS</t>
+  </si>
+  <si>
+    <t>22324405000118</t>
+  </si>
+  <si>
+    <t>PHILIP GOMES BRAZ SOBRINHO</t>
+  </si>
+  <si>
+    <t>14026859000184</t>
+  </si>
+  <si>
+    <t>TIK CHAVES CARIMBOS E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>03296405000107</t>
+  </si>
+  <si>
+    <t>EDSON JOSE DA SILVA ACESSORIOS LTDA</t>
+  </si>
+  <si>
+    <t>46877350000131</t>
+  </si>
+  <si>
+    <t>BRUNA A CARNEIRO DA CUNHA RESTAURANTE LTDA</t>
+  </si>
+  <si>
+    <t>38396085000141</t>
+  </si>
+  <si>
+    <t>DANGER COMUNICACAO E MARKETING LTDA</t>
+  </si>
+  <si>
+    <t>09466879000136</t>
+  </si>
+  <si>
+    <t>HEBER MARTINS DE AGUIAR</t>
+  </si>
+  <si>
+    <t>50655189000129</t>
+  </si>
+  <si>
+    <t>CUECAS NOVO GAROTO P S MOTA LTDA</t>
+  </si>
+  <si>
+    <t>04659222000171</t>
+  </si>
+  <si>
+    <t>HIDRAU &amp; GAS LTDA</t>
+  </si>
+  <si>
+    <t>63409192000104</t>
+  </si>
+  <si>
+    <t>ALUTOM ESQUADRIAS E VIDROS LTDA</t>
+  </si>
+  <si>
+    <t>61306208000128</t>
+  </si>
+  <si>
+    <t>AILTO RODRIGUES DE SOUSA</t>
+  </si>
+  <si>
+    <t>56423323000142</t>
+  </si>
+  <si>
+    <t>GARAGEM 27 - CENTRO AUTOMOTIVO LTDA</t>
+  </si>
+  <si>
+    <t>41515646000199</t>
+  </si>
+  <si>
+    <t>POTENCIAL MUNDIAL INSTALACOES ELETRICAS LTDA</t>
+  </si>
+  <si>
+    <t>41602738000106</t>
+  </si>
+  <si>
+    <t>AMAZON NAUTILUS LTDA</t>
+  </si>
+  <si>
+    <t>66136594000170</t>
+  </si>
+  <si>
+    <t>E F DE MOURA JUNIOR DISK MOURA</t>
+  </si>
+  <si>
+    <t>54232474000198</t>
+  </si>
+  <si>
+    <t>JK PASTELARIA LTDA</t>
+  </si>
+  <si>
+    <t>48091867000126</t>
+  </si>
+  <si>
+    <t>48.091.867 MIKE BRAGA MATOS ALVES</t>
+  </si>
+  <si>
+    <t>51778768000121</t>
+  </si>
+  <si>
+    <t>CLEBSON HENRIQUE MOURA DA SILVA</t>
+  </si>
+  <si>
+    <t>53015290000103</t>
+  </si>
+  <si>
+    <t>JOSE RENATO BOLDRINI LORENZINI</t>
+  </si>
+  <si>
+    <t>61882292000128</t>
+  </si>
+  <si>
+    <t>A DE J CARDOSO NETO</t>
+  </si>
+  <si>
+    <t>49331165000135</t>
+  </si>
+  <si>
+    <t>49.331.165 GLICIA FERREIRA ARAUJO COSTA</t>
+  </si>
+  <si>
+    <t>48172560000150</t>
+  </si>
+  <si>
+    <t>48.172.560 JOSE RAIMUNDO BERNARDES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>51652377000166</t>
+  </si>
+  <si>
+    <t>51.652.377 WALDEIR ROSA DE JESUS</t>
+  </si>
+  <si>
+    <t>34566226000176</t>
+  </si>
+  <si>
+    <t>SANDRO VERAO DOS SANTOS PERFURACAO DE POCOS</t>
+  </si>
+  <si>
+    <t>10221860000109</t>
+  </si>
+  <si>
+    <t>J B C AGENCIA DE VIAGENS E TURISMO LTDA</t>
+  </si>
+  <si>
+    <t>64404438000118</t>
+  </si>
+  <si>
+    <t>CJP COMERCIO E REPRESENTACAO LTDA</t>
+  </si>
+  <si>
+    <t>60884346000121</t>
+  </si>
+  <si>
+    <t>AGROVIA BRASIL COMERCIO IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t>45589254000125</t>
+  </si>
+  <si>
+    <t>COMPETERE ENGENHARIA LTDA</t>
+  </si>
+  <si>
+    <t>13432464000208</t>
+  </si>
+  <si>
+    <t>START INVESTIMENTOS E PARTICIPACOES LTDA</t>
+  </si>
+  <si>
+    <t>60724917000160</t>
+  </si>
+  <si>
+    <t>RENATA MARTINS BRUNHARA DA SILVA</t>
+  </si>
+  <si>
+    <t>55681616000167</t>
+  </si>
+  <si>
+    <t>DVN TRANSPORTE EXECUTIVO LTDA</t>
+  </si>
+  <si>
+    <t>62527704000174</t>
+  </si>
+  <si>
+    <t>MASTER REVENDA VEICULOS LTDA</t>
+  </si>
+  <si>
+    <t>64729271000165</t>
+  </si>
+  <si>
+    <t>ANIMA INDUSTRIA &amp; COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>24887055000123</t>
+  </si>
+  <si>
+    <t>E L S CONSTRUCOES LTDA</t>
+  </si>
+  <si>
+    <t>24538995000107</t>
+  </si>
+  <si>
+    <t>AGNUS TOUR VIAGEM E TURISMO LTDA</t>
+  </si>
+  <si>
+    <t>65481222000119</t>
+  </si>
+  <si>
+    <t>C H ALVES DA ROCHA PRESTADORA DE SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>61347622000185</t>
+  </si>
+  <si>
+    <t>NUBIA PEREZ TURISMO LTDA</t>
+  </si>
+  <si>
+    <t>47124031000118</t>
+  </si>
+  <si>
+    <t>ENILDA RITA DA SILVA E CIA LTDA</t>
+  </si>
+  <si>
+    <t>54694238000193</t>
+  </si>
+  <si>
+    <t>OUSADIA EMPREITEIRA DE OBRAS LTDA</t>
+  </si>
+  <si>
+    <t>46371839000137</t>
+  </si>
+  <si>
+    <t>W. RIBEIRO DE ALMEIDA LTDA</t>
+  </si>
+  <si>
+    <t>61199999000134</t>
+  </si>
+  <si>
+    <t>E M DA SILVA BARBOSA</t>
+  </si>
+  <si>
+    <t>31368678000155</t>
+  </si>
+  <si>
+    <t>ANTONIO LUCIANO FILHO</t>
+  </si>
+  <si>
+    <t>62473581000136</t>
+  </si>
+  <si>
+    <t>AC IMPORTS LTDA</t>
+  </si>
+  <si>
+    <t>23997611000151</t>
+  </si>
+  <si>
+    <t>JOELMA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>51969027000128</t>
+  </si>
+  <si>
+    <t>METALURGICA ACO FORTE LTDA</t>
+  </si>
+  <si>
+    <t>57325065000124</t>
+  </si>
+  <si>
+    <t>ESPACO CULTURAL W&amp;R LTDA</t>
+  </si>
+  <si>
+    <t>48704626000105</t>
+  </si>
+  <si>
+    <t>DOUGLAS VINICIUS JERONIMO CLARO</t>
+  </si>
+  <si>
+    <t>53734344000190</t>
+  </si>
+  <si>
+    <t>SOLUCAO DE CREDITO BNCRED LTDA</t>
+  </si>
+  <si>
+    <t>40000624000123</t>
+  </si>
+  <si>
+    <t>FLORINALDO ROSAN DA SILVA LTDA</t>
+  </si>
+  <si>
+    <t>64154686000158</t>
+  </si>
+  <si>
+    <t>MASA MAIKE ARAUJO SOLUCOES AGRICOLAS</t>
+  </si>
+  <si>
+    <t>34056336000198</t>
+  </si>
+  <si>
+    <t>FABIO SANTOS DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>18110512000176</t>
+  </si>
+  <si>
+    <t>PARANA ROTULOS E ETIQUETAS LTDA</t>
+  </si>
+  <si>
+    <t>65741540000171</t>
+  </si>
+  <si>
+    <t>BELEZA PLENA IMPORTS LTDA</t>
+  </si>
+  <si>
+    <t>Deve ser encaminhado uma nova procuracao publica ou uma procuracao assinada via gov.br pelo GERMANO CAMPOS PINTO, ja que a recepcionada o outorgante nao seria a empresa, outorgante deve ser a empresa G C P GREEN CARBON PROCESSING ENERGY LTDA. A procuracao dar poderes para abrir e encerrar contas, deve ser ajustado dando poderes para abrir e movimentar contas. O prazo da procuracao esta com a vigencia acima de 3 anos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato social da empresa HR REPRESENTACOES, CONSULTORIA E PESQUISA LTDA, atualizado e registrado no orgao competente. Esse documento contem informacoes como os dados dos socios, a atividade exercida pela empresa, o capital social e as regras de administracao, definindo os direitos e deveres dos socios e comprovando a existencia legal da empresa.&lt;br&gt;&lt;br&gt;Caso a representacao seja em conjunto sera preciso encaminhar a procuracao com poderes para abrir e movimentar contas, o documento deve ser assinado pelos representantes legais nomeados no contrato social, assinada digitalmente GOV.br ou procuracao publica. Em caso de assinatura digital, devera ser encaminhado o documento em formato PDF, para validacao das assinaturas e protocolo de autenticidade.&lt;br&gt;&lt;br&gt;Para garantir a seguranca e a validade do processo, a foto enviada nao pode conter terceiros. Pedimos gentilmente que envie uma nova foto apenas com voce, conforme as orientacoes. </t>
+  </si>
+  <si>
+    <t>Procuracao da empresa FG PRODUTOS HOSPITALARES LTDA. Identificamos que a representacao da sua empresa e realizada em conjunto pelos representantes nomeados na clausula de administracao do contrato social e, por esse motivo, e necessario que os demais representantes tambem assinem a procuracao via gov e em formato PDF. ( A procuracao esta sendo enviada com dados de outra empresa: Servicos de Enfermagem FG Ltda, por favor preencher outra procuracao com os dados da empresa FG Produtos Hospitalares Ltda )</t>
+  </si>
+  <si>
+    <t>Procuracao com poderes de abrir e movimentar conta corrente junto a instituicoes financeiras com mandato vigente e devidamente assinada&lt;br&gt;&lt;br&gt;Certificado de Inova simples</t>
+  </si>
+  <si>
+    <t>Ata de eleicao da empresa , atualizado e registrada no orgao competente. Esse documento formaliza a eleicao e/ou nomeacao dos representantes legais e administradores, informando cargos, prazos de mandato e poderes de representacao, comprovando quem esta autorizado a agir em nome da entidade. A recepcionada nao esta te elegendo.&lt;br&gt;&lt;br&gt;Estatuto social atualizado e registrado no orgao competente</t>
   </si>
 </sst>
 </file>
@@ -1677,7 +2436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H312"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1722,22 +2481,22 @@
         <v>46146</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>422</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>423</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1748,13 +2507,13 @@
         <v>46146</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>424</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>425</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
         <v>29</v>
@@ -1763,10 +2522,10 @@
         <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H3" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1774,13 +2533,13 @@
         <v>46146</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>426</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>427</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
@@ -1789,10 +2548,10 @@
         <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1800,25 +2559,25 @@
         <v>46146</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>428</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>429</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="H5" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1826,25 +2585,25 @@
         <v>46146</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>430</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>431</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1852,25 +2611,25 @@
         <v>46146</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>432</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>433</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1878,13 +2637,13 @@
         <v>46146</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>434</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>435</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
         <v>29</v>
@@ -1893,10 +2652,10 @@
         <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1904,13 +2663,13 @@
         <v>46146</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>436</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>437</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
         <v>29</v>
@@ -1919,10 +2678,10 @@
         <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="H9" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1930,22 +2689,22 @@
         <v>46146</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>438</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>439</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
         <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1956,25 +2715,25 @@
         <v>46146</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>440</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>441</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1982,22 +2741,22 @@
         <v>46146</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>442</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>443</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>444</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2008,25 +2767,25 @@
         <v>46146</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>445</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>446</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -2034,22 +2793,22 @@
         <v>46146</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>447</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>448</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2060,25 +2819,25 @@
         <v>46146</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>449</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>450</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H15" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -2086,13 +2845,13 @@
         <v>46146</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>451</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>452</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
@@ -2101,7 +2860,7 @@
         <v>8</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2112,25 +2871,25 @@
         <v>46146</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>453</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>454</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -2138,10 +2897,10 @@
         <v>46146</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
         <v>20</v>
@@ -2153,7 +2912,7 @@
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2164,10 +2923,10 @@
         <v>46146</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
@@ -2179,7 +2938,7 @@
         <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -2190,19 +2949,19 @@
         <v>46146</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G20" t="s">
         <v>17</v>
@@ -2216,13 +2975,13 @@
         <v>46146</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
@@ -2242,13 +3001,13 @@
         <v>46146</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
@@ -2268,19 +3027,19 @@
         <v>46146</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" t="s">
         <v>17</v>
@@ -2294,13 +3053,13 @@
         <v>46146</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E24" t="s">
         <v>29</v>
@@ -2309,7 +3068,7 @@
         <v>8</v>
       </c>
       <c r="G24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -2320,13 +3079,13 @@
         <v>46146</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E25" t="s">
         <v>29</v>
@@ -2335,7 +3094,7 @@
         <v>8</v>
       </c>
       <c r="G25" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -2346,22 +3105,22 @@
         <v>46146</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E26" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F26" t="s">
         <v>8</v>
       </c>
       <c r="G26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2372,22 +3131,22 @@
         <v>46146</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F27" t="s">
         <v>8</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -2398,13 +3157,13 @@
         <v>46146</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" t="s">
         <v>29</v>
@@ -2424,22 +3183,22 @@
         <v>46146</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E29" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2450,13 +3209,13 @@
         <v>46146</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E30" t="s">
         <v>31</v>
@@ -2476,22 +3235,22 @@
         <v>46146</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F31" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G31" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -2502,10 +3261,10 @@
         <v>46146</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -2528,10 +3287,10 @@
         <v>46146</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
@@ -2554,13 +3313,13 @@
         <v>46146</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E34" t="s">
         <v>29</v>
@@ -2569,7 +3328,7 @@
         <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2580,13 +3339,13 @@
         <v>46146</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E35" t="s">
         <v>29</v>
@@ -2595,7 +3354,7 @@
         <v>8</v>
       </c>
       <c r="G35" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -2606,13 +3365,13 @@
         <v>46146</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E36" t="s">
         <v>31</v>
@@ -2632,19 +3391,19 @@
         <v>46146</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>39</v>
       </c>
       <c r="C37" t="s">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E37" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F37" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G37" t="s">
         <v>17</v>
@@ -2658,13 +3417,13 @@
         <v>46146</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E38" t="s">
         <v>29</v>
@@ -2673,10 +3432,10 @@
         <v>8</v>
       </c>
       <c r="G38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H38" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -2684,19 +3443,19 @@
         <v>46146</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="D39" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E39" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G39" t="s">
         <v>17</v>
@@ -2710,13 +3469,13 @@
         <v>46146</v>
       </c>
       <c r="B40" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
         <v>29</v>
@@ -2725,7 +3484,7 @@
         <v>8</v>
       </c>
       <c r="G40" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2736,13 +3495,13 @@
         <v>46146</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E41" t="s">
         <v>29</v>
@@ -2751,7 +3510,7 @@
         <v>8</v>
       </c>
       <c r="G41" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2762,13 +3521,13 @@
         <v>46146</v>
       </c>
       <c r="B42" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="C42" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="D42" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E42" t="s">
         <v>29</v>
@@ -2777,7 +3536,7 @@
         <v>8</v>
       </c>
       <c r="G42" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2788,16 +3547,16 @@
         <v>46146</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C43" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E43" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F43" t="s">
         <v>8</v>
@@ -2814,13 +3573,13 @@
         <v>46146</v>
       </c>
       <c r="B44" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="C44" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="D44" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E44" t="s">
         <v>29</v>
@@ -2829,7 +3588,7 @@
         <v>8</v>
       </c>
       <c r="G44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -2840,19 +3599,19 @@
         <v>46146</v>
       </c>
       <c r="B45" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C45" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="D45" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E45" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F45" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G45" t="s">
         <v>17</v>
@@ -2866,19 +3625,19 @@
         <v>46146</v>
       </c>
       <c r="B46" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="C46" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="D46" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E46" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G46" t="s">
         <v>17</v>
@@ -2892,13 +3651,13 @@
         <v>46146</v>
       </c>
       <c r="B47" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="C47" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="D47" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E47" t="s">
         <v>31</v>
@@ -2918,13 +3677,13 @@
         <v>46146</v>
       </c>
       <c r="B48" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="C48" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="D48" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E48" t="s">
         <v>29</v>
@@ -2933,7 +3692,7 @@
         <v>8</v>
       </c>
       <c r="G48" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -2944,13 +3703,13 @@
         <v>46146</v>
       </c>
       <c r="B49" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="C49" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="D49" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E49" t="s">
         <v>29</v>
@@ -2970,13 +3729,13 @@
         <v>46146</v>
       </c>
       <c r="B50" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="D50" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E50" t="s">
         <v>29</v>
@@ -2996,13 +3755,13 @@
         <v>46146</v>
       </c>
       <c r="B51" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="C51" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E51" t="s">
         <v>29</v>
@@ -3022,19 +3781,19 @@
         <v>46146</v>
       </c>
       <c r="B52" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="C52" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="D52" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E52" t="s">
         <v>31</v>
       </c>
       <c r="F52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G52" t="s">
         <v>17</v>
@@ -3048,22 +3807,25 @@
         <v>46146</v>
       </c>
       <c r="B53" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="C53" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="D53" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E53" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -3071,13 +3833,13 @@
         <v>46146</v>
       </c>
       <c r="B54" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="C54" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="D54" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E54" t="s">
         <v>29</v>
@@ -3086,10 +3848,10 @@
         <v>8</v>
       </c>
       <c r="G54" t="s">
-        <v>17</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="H54" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -3097,13 +3859,13 @@
         <v>46146</v>
       </c>
       <c r="B55" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="C55" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E55" t="s">
         <v>29</v>
@@ -3123,16 +3885,16 @@
         <v>46146</v>
       </c>
       <c r="B56" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="C56" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="D56" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F56" t="s">
         <v>8</v>
@@ -3149,13 +3911,13 @@
         <v>46146</v>
       </c>
       <c r="B57" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="C57" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="D57" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E57" t="s">
         <v>29</v>
@@ -3164,7 +3926,7 @@
         <v>8</v>
       </c>
       <c r="G57" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -3175,13 +3937,13 @@
         <v>46146</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="C58" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E58" t="s">
         <v>29</v>
@@ -3190,7 +3952,7 @@
         <v>8</v>
       </c>
       <c r="G58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -3201,19 +3963,19 @@
         <v>46146</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="C59" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="D59" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E59" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F59" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G59" t="s">
         <v>17</v>
@@ -3227,13 +3989,13 @@
         <v>46146</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="C60" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="D60" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E60" t="s">
         <v>29</v>
@@ -3242,7 +4004,7 @@
         <v>8</v>
       </c>
       <c r="G60" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -3253,10 +4015,10 @@
         <v>46146</v>
       </c>
       <c r="B61" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="C61" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="D61" t="s">
         <v>35</v>
@@ -3265,7 +4027,7 @@
         <v>31</v>
       </c>
       <c r="F61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G61" t="s">
         <v>17</v>
@@ -3279,10 +4041,10 @@
         <v>46146</v>
       </c>
       <c r="B62" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="C62" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="D62" t="s">
         <v>14</v>
@@ -3305,19 +4067,19 @@
         <v>46146</v>
       </c>
       <c r="B63" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="C63" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="D63" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E63" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G63" t="s">
         <v>17</v>
@@ -3331,16 +4093,16 @@
         <v>46146</v>
       </c>
       <c r="B64" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="C64" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="D64" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E64" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F64" t="s">
         <v>8</v>
@@ -3357,22 +4119,22 @@
         <v>46146</v>
       </c>
       <c r="B65" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="C65" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F65" t="s">
         <v>8</v>
       </c>
       <c r="G65" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -3383,10 +4145,10 @@
         <v>46146</v>
       </c>
       <c r="B66" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="C66" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="D66" t="s">
         <v>13</v>
@@ -3409,13 +4171,13 @@
         <v>46146</v>
       </c>
       <c r="B67" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="C67" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="D67" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E67" t="s">
         <v>29</v>
@@ -3435,22 +4197,22 @@
         <v>46146</v>
       </c>
       <c r="B68" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="C68" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="D68" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="E68" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F68" t="s">
         <v>8</v>
       </c>
       <c r="G68" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -3458,16 +4220,16 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B69" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="C69" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="D69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E69" t="s">
         <v>29</v>
@@ -3476,24 +4238,21 @@
         <v>8</v>
       </c>
       <c r="G69" t="s">
-        <v>17</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B70" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="C70" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="D70" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E70" t="s">
         <v>29</v>
@@ -3510,16 +4269,16 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B71" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="C71" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="D71" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E71" t="s">
         <v>29</v>
@@ -3536,13 +4295,13 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B72" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="C72" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="D72" t="s">
         <v>23</v>
@@ -3551,7 +4310,7 @@
         <v>31</v>
       </c>
       <c r="F72" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G72" t="s">
         <v>17</v>
@@ -3562,16 +4321,16 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B73" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="C73" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="D73" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E73" t="s">
         <v>29</v>
@@ -3580,7 +4339,7 @@
         <v>8</v>
       </c>
       <c r="G73" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -3588,25 +4347,25 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B74" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="C74" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="D74" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E74" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F74" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="G74" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -3614,22 +4373,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B75" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="C75" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="D75" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E75" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F75" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G75" t="s">
         <v>17</v>
@@ -3640,22 +4399,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B76" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="C76" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="D76" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F76" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="G76" t="s">
         <v>17</v>
@@ -3666,25 +4425,25 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B77" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="C77" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D77" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E77" t="s">
         <v>31</v>
       </c>
       <c r="F77" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G77" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -3692,13 +4451,13 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B78" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="C78" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="D78" t="s">
         <v>14</v>
@@ -3718,16 +4477,16 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B79" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="C79" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="D79" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E79" t="s">
         <v>29</v>
@@ -3744,25 +4503,25 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B80" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="C80" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="D80" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E80" t="s">
         <v>31</v>
       </c>
       <c r="F80" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G80" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -3770,25 +4529,25 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B81" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="C81" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="D81" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E81" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F81" t="s">
         <v>8</v>
       </c>
       <c r="G81" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -3796,22 +4555,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B82" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="C82" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="D82" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E82" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F82" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G82" t="s">
         <v>17</v>
@@ -3822,16 +4581,16 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B83" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="C83" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D83" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E83" t="s">
         <v>29</v>
@@ -3848,16 +4607,16 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B84" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="C84" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D84" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E84" t="s">
         <v>29</v>
@@ -3866,7 +4625,7 @@
         <v>8</v>
       </c>
       <c r="G84" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -3877,13 +4636,13 @@
         <v>46147</v>
       </c>
       <c r="B85" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="C85" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="D85" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E85" t="s">
         <v>29</v>
@@ -3892,7 +4651,7 @@
         <v>8</v>
       </c>
       <c r="G85" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -3903,19 +4662,19 @@
         <v>46147</v>
       </c>
       <c r="B86" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="C86" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="D86" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="E86" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F86" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G86" t="s">
         <v>17</v>
@@ -3929,19 +4688,19 @@
         <v>46147</v>
       </c>
       <c r="B87" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="C87" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="D87" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E87" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F87" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G87" t="s">
         <v>17</v>
@@ -3955,13 +4714,13 @@
         <v>46147</v>
       </c>
       <c r="B88" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="C88" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="D88" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E88" t="s">
         <v>31</v>
@@ -3981,13 +4740,13 @@
         <v>46147</v>
       </c>
       <c r="B89" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="C89" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="D89" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E89" t="s">
         <v>29</v>
@@ -4007,22 +4766,22 @@
         <v>46147</v>
       </c>
       <c r="B90" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="C90" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="D90" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E90" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F90" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="G90" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -4033,19 +4792,19 @@
         <v>46147</v>
       </c>
       <c r="B91" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="C91" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="D91" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E91" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F91" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="G91" t="s">
         <v>17</v>
@@ -4059,19 +4818,19 @@
         <v>46147</v>
       </c>
       <c r="B92" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="C92" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="D92" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E92" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F92" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="G92" t="s">
         <v>17</v>
@@ -4085,22 +4844,22 @@
         <v>46147</v>
       </c>
       <c r="B93" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="C93" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="D93" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E93" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F93" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G93" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -4111,22 +4870,22 @@
         <v>46147</v>
       </c>
       <c r="B94" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="C94" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="D94" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E94" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F94" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G94" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -4137,19 +4896,19 @@
         <v>46147</v>
       </c>
       <c r="B95" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="C95" t="s">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="D95" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E95" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F95" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G95" t="s">
         <v>17</v>
@@ -4163,13 +4922,13 @@
         <v>46147</v>
       </c>
       <c r="B96" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="C96" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="D96" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="E96" t="s">
         <v>31</v>
@@ -4189,13 +4948,13 @@
         <v>46147</v>
       </c>
       <c r="B97" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="C97" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="D97" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E97" t="s">
         <v>29</v>
@@ -4204,7 +4963,7 @@
         <v>8</v>
       </c>
       <c r="G97" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -4215,25 +4974,25 @@
         <v>46147</v>
       </c>
       <c r="B98" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="C98" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="D98" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E98" t="s">
         <v>31</v>
       </c>
       <c r="F98" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G98" t="s">
-        <v>36</v>
-      </c>
-      <c r="H98" t="s">
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -4241,13 +5000,13 @@
         <v>46147</v>
       </c>
       <c r="B99" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="C99" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="D99" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E99" t="s">
         <v>29</v>
@@ -4267,13 +5026,13 @@
         <v>46147</v>
       </c>
       <c r="B100" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="C100" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="D100" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E100" t="s">
         <v>29</v>
@@ -4282,7 +5041,7 @@
         <v>8</v>
       </c>
       <c r="G100" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -4293,22 +5052,22 @@
         <v>46147</v>
       </c>
       <c r="B101" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="C101" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="D101" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E101" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F101" t="s">
         <v>8</v>
       </c>
       <c r="G101" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -4319,13 +5078,13 @@
         <v>46147</v>
       </c>
       <c r="B102" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="C102" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D102" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="E102" t="s">
         <v>31</v>
@@ -4345,22 +5104,22 @@
         <v>46147</v>
       </c>
       <c r="B103" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="C103" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="D103" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E103" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F103" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G103" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H103">
         <v>0</v>
@@ -4371,13 +5130,13 @@
         <v>46147</v>
       </c>
       <c r="B104" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="C104" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="D104" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E104" t="s">
         <v>31</v>
@@ -4386,7 +5145,7 @@
         <v>7</v>
       </c>
       <c r="G104" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -4397,13 +5156,13 @@
         <v>46147</v>
       </c>
       <c r="B105" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="C105" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="D105" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E105" t="s">
         <v>29</v>
@@ -4423,10 +5182,10 @@
         <v>46147</v>
       </c>
       <c r="B106" t="s">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="C106" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="D106" t="s">
         <v>11</v>
@@ -4438,7 +5197,7 @@
         <v>8</v>
       </c>
       <c r="G106" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -4449,13 +5208,13 @@
         <v>46147</v>
       </c>
       <c r="B107" t="s">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="C107" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="D107" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E107" t="s">
         <v>29</v>
@@ -4475,22 +5234,22 @@
         <v>46147</v>
       </c>
       <c r="B108" t="s">
-        <v>253</v>
+        <v>221</v>
       </c>
       <c r="C108" t="s">
-        <v>254</v>
+        <v>222</v>
       </c>
       <c r="D108" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E108" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F108" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G108" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -4501,22 +5260,22 @@
         <v>46147</v>
       </c>
       <c r="B109" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="C109" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="D109" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E109" t="s">
         <v>29</v>
       </c>
       <c r="F109" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G109" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -4527,19 +5286,19 @@
         <v>46147</v>
       </c>
       <c r="B110" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="C110" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="D110" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E110" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F110" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G110" t="s">
         <v>17</v>
@@ -4553,19 +5312,19 @@
         <v>46147</v>
       </c>
       <c r="B111" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="C111" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="D111" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E111" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F111" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G111" t="s">
         <v>17</v>
@@ -4579,13 +5338,13 @@
         <v>46147</v>
       </c>
       <c r="B112" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D112" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E112" t="s">
         <v>29</v>
@@ -4594,7 +5353,7 @@
         <v>8</v>
       </c>
       <c r="G112" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H112">
         <v>0</v>
@@ -4605,25 +5364,25 @@
         <v>46147</v>
       </c>
       <c r="B113" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="C113" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="D113" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E113" t="s">
         <v>31</v>
       </c>
       <c r="F113" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G113" t="s">
-        <v>19</v>
-      </c>
-      <c r="H113">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H113" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -4631,13 +5390,13 @@
         <v>46147</v>
       </c>
       <c r="B114" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="C114" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="D114" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E114" t="s">
         <v>29</v>
@@ -4646,7 +5405,7 @@
         <v>8</v>
       </c>
       <c r="G114" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H114">
         <v>0</v>
@@ -4657,22 +5416,22 @@
         <v>46147</v>
       </c>
       <c r="B115" t="s">
-        <v>267</v>
+        <v>237</v>
       </c>
       <c r="C115" t="s">
-        <v>268</v>
+        <v>238</v>
       </c>
       <c r="D115" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E115" t="s">
         <v>29</v>
       </c>
       <c r="F115" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G115" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H115">
         <v>0</v>
@@ -4683,19 +5442,19 @@
         <v>46147</v>
       </c>
       <c r="B116" t="s">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="C116" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="D116" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="E116" t="s">
         <v>31</v>
       </c>
       <c r="F116" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G116" t="s">
         <v>17</v>
@@ -4709,13 +5468,13 @@
         <v>46147</v>
       </c>
       <c r="B117" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="C117" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="D117" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E117" t="s">
         <v>31</v>
@@ -4735,22 +5494,22 @@
         <v>46147</v>
       </c>
       <c r="B118" t="s">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="C118" t="s">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="D118" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E118" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F118" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G118" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H118">
         <v>0</v>
@@ -4761,22 +5520,22 @@
         <v>46147</v>
       </c>
       <c r="B119" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="C119" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="D119" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="E119" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F119" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G119" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H119">
         <v>0</v>
@@ -4787,13 +5546,13 @@
         <v>46147</v>
       </c>
       <c r="B120" t="s">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="C120" t="s">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="D120" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E120" t="s">
         <v>29</v>
@@ -4813,22 +5572,22 @@
         <v>46147</v>
       </c>
       <c r="B121" t="s">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="C121" t="s">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="D121" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E121" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F121" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G121" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H121">
         <v>0</v>
@@ -4839,22 +5598,22 @@
         <v>46147</v>
       </c>
       <c r="B122" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="C122" t="s">
-        <v>282</v>
+        <v>252</v>
       </c>
       <c r="D122" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E122" t="s">
         <v>29</v>
       </c>
       <c r="F122" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G122" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H122">
         <v>0</v>
@@ -4865,22 +5624,25 @@
         <v>46147</v>
       </c>
       <c r="B123" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="C123" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="D123" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E123" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F123" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G123" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="H123" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -4888,22 +5650,22 @@
         <v>46147</v>
       </c>
       <c r="B124" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="C124" t="s">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="D124" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="E124" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F124" t="s">
         <v>7</v>
       </c>
       <c r="G124" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H124">
         <v>0</v>
@@ -4914,19 +5676,19 @@
         <v>46147</v>
       </c>
       <c r="B125" t="s">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="C125" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="D125" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E125" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F125" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G125" t="s">
         <v>17</v>
@@ -4940,13 +5702,13 @@
         <v>46147</v>
       </c>
       <c r="B126" t="s">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="D126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E126" t="s">
         <v>29</v>
@@ -4966,16 +5728,16 @@
         <v>46147</v>
       </c>
       <c r="B127" t="s">
-        <v>291</v>
+        <v>261</v>
       </c>
       <c r="C127" t="s">
-        <v>292</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="E127" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F127" t="s">
         <v>8</v>
@@ -4992,13 +5754,13 @@
         <v>46147</v>
       </c>
       <c r="B128" t="s">
-        <v>293</v>
+        <v>263</v>
       </c>
       <c r="C128" t="s">
-        <v>294</v>
+        <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="E128" t="s">
         <v>31</v>
@@ -5007,7 +5769,7 @@
         <v>7</v>
       </c>
       <c r="G128" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -5018,13 +5780,13 @@
         <v>46147</v>
       </c>
       <c r="B129" t="s">
-        <v>295</v>
+        <v>265</v>
       </c>
       <c r="C129" t="s">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="D129" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E129" t="s">
         <v>29</v>
@@ -5044,13 +5806,13 @@
         <v>46147</v>
       </c>
       <c r="B130" t="s">
-        <v>297</v>
+        <v>267</v>
       </c>
       <c r="C130" t="s">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="D130" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E130" t="s">
         <v>29</v>
@@ -5059,7 +5821,7 @@
         <v>7</v>
       </c>
       <c r="G130" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H130">
         <v>0</v>
@@ -5070,13 +5832,13 @@
         <v>46147</v>
       </c>
       <c r="B131" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="C131" t="s">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="D131" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E131" t="s">
         <v>31</v>
@@ -5096,19 +5858,19 @@
         <v>46147</v>
       </c>
       <c r="B132" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="C132" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="D132" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E132" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F132" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G132" t="s">
         <v>17</v>
@@ -5122,22 +5884,22 @@
         <v>46147</v>
       </c>
       <c r="B133" t="s">
-        <v>303</v>
+        <v>273</v>
       </c>
       <c r="C133" t="s">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="D133" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F133" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G133" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -5148,13 +5910,13 @@
         <v>46147</v>
       </c>
       <c r="B134" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="C134" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="D134" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E134" t="s">
         <v>29</v>
@@ -5163,7 +5925,7 @@
         <v>8</v>
       </c>
       <c r="G134" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -5174,10 +5936,10 @@
         <v>46147</v>
       </c>
       <c r="B135" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="C135" t="s">
-        <v>308</v>
+        <v>278</v>
       </c>
       <c r="D135" t="s">
         <v>11</v>
@@ -5200,19 +5962,19 @@
         <v>46147</v>
       </c>
       <c r="B136" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="C136" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="D136" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F136" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G136" t="s">
         <v>19</v>
@@ -5223,25 +5985,25 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B137" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="C137" t="s">
-        <v>312</v>
+        <v>282</v>
       </c>
       <c r="D137" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E137" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F137" t="s">
         <v>7</v>
       </c>
       <c r="G137" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -5249,48 +6011,45 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B138" t="s">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="C138" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="D138" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E138" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F138" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G138" t="s">
-        <v>17</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B139" t="s">
-        <v>315</v>
+        <v>285</v>
       </c>
       <c r="C139" t="s">
-        <v>316</v>
+        <v>286</v>
       </c>
       <c r="D139" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="E139" t="s">
         <v>31</v>
       </c>
       <c r="F139" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G139" t="s">
         <v>17</v>
@@ -5301,16 +6060,16 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B140" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="C140" t="s">
-        <v>318</v>
+        <v>288</v>
       </c>
       <c r="D140" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E140" t="s">
         <v>31</v>
@@ -5327,22 +6086,22 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B141" t="s">
-        <v>319</v>
+        <v>289</v>
       </c>
       <c r="C141" t="s">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="D141" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E141" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F141" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G141" t="s">
         <v>17</v>
@@ -5353,19 +6112,19 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B142" t="s">
-        <v>321</v>
+        <v>291</v>
       </c>
       <c r="C142" t="s">
-        <v>322</v>
+        <v>292</v>
       </c>
       <c r="D142" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E142" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F142" t="s">
         <v>8</v>
@@ -5379,25 +6138,25 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B143" t="s">
-        <v>324</v>
+        <v>293</v>
       </c>
       <c r="C143" t="s">
-        <v>325</v>
+        <v>294</v>
       </c>
       <c r="D143" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="E143" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F143" t="s">
         <v>7</v>
       </c>
       <c r="G143" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -5405,45 +6164,45 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B144" t="s">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="C144" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="D144" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="E144" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F144" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G144" t="s">
-        <v>36</v>
-      </c>
-      <c r="H144" t="s">
-        <v>421</v>
+        <v>33</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B145" t="s">
-        <v>328</v>
+        <v>297</v>
       </c>
       <c r="C145" t="s">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="D145" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E145" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F145" t="s">
         <v>7</v>
@@ -5457,25 +6216,25 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B146" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="C146" t="s">
-        <v>331</v>
+        <v>300</v>
       </c>
       <c r="D146" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E146" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F146" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G146" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -5483,16 +6242,16 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B147" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="C147" t="s">
-        <v>333</v>
+        <v>302</v>
       </c>
       <c r="D147" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E147" t="s">
         <v>29</v>
@@ -5501,21 +6260,24 @@
         <v>8</v>
       </c>
       <c r="G147" t="s">
-        <v>334</v>
+        <v>17</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B148" t="s">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="C148" t="s">
-        <v>336</v>
+        <v>304</v>
       </c>
       <c r="D148" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E148" t="s">
         <v>29</v>
@@ -5532,16 +6294,16 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B149" t="s">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="C149" t="s">
-        <v>338</v>
+        <v>306</v>
       </c>
       <c r="D149" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E149" t="s">
         <v>29</v>
@@ -5550,7 +6312,7 @@
         <v>8</v>
       </c>
       <c r="G149" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H149">
         <v>0</v>
@@ -5558,25 +6320,25 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B150" t="s">
-        <v>339</v>
+        <v>307</v>
       </c>
       <c r="C150" t="s">
-        <v>340</v>
+        <v>308</v>
       </c>
       <c r="D150" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E150" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F150" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G150" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -5584,13 +6346,13 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B151" t="s">
-        <v>341</v>
+        <v>309</v>
       </c>
       <c r="C151" t="s">
-        <v>342</v>
+        <v>310</v>
       </c>
       <c r="D151" t="s">
         <v>6</v>
@@ -5602,7 +6364,7 @@
         <v>8</v>
       </c>
       <c r="G151" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -5613,19 +6375,19 @@
         <v>46148</v>
       </c>
       <c r="B152" t="s">
-        <v>343</v>
+        <v>311</v>
       </c>
       <c r="C152" t="s">
-        <v>344</v>
+        <v>312</v>
       </c>
       <c r="D152" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E152" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F152" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G152" t="s">
         <v>17</v>
@@ -5639,13 +6401,13 @@
         <v>46148</v>
       </c>
       <c r="B153" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="C153" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="D153" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E153" t="s">
         <v>29</v>
@@ -5665,19 +6427,19 @@
         <v>46148</v>
       </c>
       <c r="B154" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="C154" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="D154" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E154" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F154" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G154" t="s">
         <v>17</v>
@@ -5691,19 +6453,19 @@
         <v>46148</v>
       </c>
       <c r="B155" t="s">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="C155" t="s">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="D155" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="E155" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F155" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G155" t="s">
         <v>17</v>
@@ -5717,19 +6479,19 @@
         <v>46148</v>
       </c>
       <c r="B156" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C156" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="D156" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E156" t="s">
         <v>31</v>
       </c>
       <c r="F156" t="s">
-        <v>323</v>
+        <v>7</v>
       </c>
       <c r="G156" t="s">
         <v>17</v>
@@ -5743,19 +6505,19 @@
         <v>46148</v>
       </c>
       <c r="B157" t="s">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="C157" t="s">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="D157" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F157" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G157" t="s">
         <v>17</v>
@@ -5769,22 +6531,22 @@
         <v>46148</v>
       </c>
       <c r="B158" t="s">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="C158" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="D158" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="E158" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F158" t="s">
         <v>7</v>
       </c>
       <c r="G158" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H158">
         <v>0</v>
@@ -5795,10 +6557,10 @@
         <v>46148</v>
       </c>
       <c r="B159" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="C159" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="D159" t="s">
         <v>9</v>
@@ -5810,10 +6572,10 @@
         <v>7</v>
       </c>
       <c r="G159" t="s">
-        <v>18</v>
-      </c>
-      <c r="H159">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H159" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -5821,16 +6583,16 @@
         <v>46148</v>
       </c>
       <c r="B160" t="s">
-        <v>359</v>
+        <v>328</v>
       </c>
       <c r="C160" t="s">
-        <v>360</v>
+        <v>329</v>
       </c>
       <c r="D160" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E160" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F160" t="s">
         <v>7</v>
@@ -5847,13 +6609,13 @@
         <v>46148</v>
       </c>
       <c r="B161" t="s">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="C161" t="s">
-        <v>362</v>
+        <v>331</v>
       </c>
       <c r="D161" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E161" t="s">
         <v>29</v>
@@ -5862,7 +6624,7 @@
         <v>8</v>
       </c>
       <c r="G161" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H161">
         <v>0</v>
@@ -5873,25 +6635,22 @@
         <v>46148</v>
       </c>
       <c r="B162" t="s">
-        <v>363</v>
+        <v>332</v>
       </c>
       <c r="C162" t="s">
-        <v>364</v>
+        <v>333</v>
       </c>
       <c r="D162" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E162" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F162" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G162" t="s">
-        <v>17</v>
-      </c>
-      <c r="H162">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -5899,13 +6658,13 @@
         <v>46148</v>
       </c>
       <c r="B163" t="s">
-        <v>365</v>
+        <v>335</v>
       </c>
       <c r="C163" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="D163" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E163" t="s">
         <v>29</v>
@@ -5925,13 +6684,13 @@
         <v>46148</v>
       </c>
       <c r="B164" t="s">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="C164" t="s">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="D164" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E164" t="s">
         <v>29</v>
@@ -5940,7 +6699,7 @@
         <v>8</v>
       </c>
       <c r="G164" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H164">
         <v>0</v>
@@ -5951,22 +6710,22 @@
         <v>46148</v>
       </c>
       <c r="B165" t="s">
-        <v>369</v>
+        <v>339</v>
       </c>
       <c r="C165" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="D165" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E165" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F165" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G165" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H165">
         <v>0</v>
@@ -5977,10 +6736,10 @@
         <v>46148</v>
       </c>
       <c r="B166" t="s">
-        <v>371</v>
+        <v>341</v>
       </c>
       <c r="C166" t="s">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="D166" t="s">
         <v>6</v>
@@ -6003,19 +6762,19 @@
         <v>46148</v>
       </c>
       <c r="B167" t="s">
-        <v>373</v>
+        <v>343</v>
       </c>
       <c r="C167" t="s">
-        <v>374</v>
+        <v>344</v>
       </c>
       <c r="D167" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E167" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F167" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G167" t="s">
         <v>17</v>
@@ -6029,13 +6788,13 @@
         <v>46148</v>
       </c>
       <c r="B168" t="s">
-        <v>375</v>
+        <v>345</v>
       </c>
       <c r="C168" t="s">
-        <v>376</v>
+        <v>346</v>
       </c>
       <c r="D168" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E168" t="s">
         <v>29</v>
@@ -6044,7 +6803,7 @@
         <v>8</v>
       </c>
       <c r="G168" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H168">
         <v>0</v>
@@ -6055,22 +6814,22 @@
         <v>46148</v>
       </c>
       <c r="B169" t="s">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="C169" t="s">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="D169" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E169" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F169" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="G169" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H169">
         <v>0</v>
@@ -6081,13 +6840,13 @@
         <v>46148</v>
       </c>
       <c r="B170" t="s">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="C170" t="s">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="D170" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E170" t="s">
         <v>29</v>
@@ -6107,19 +6866,19 @@
         <v>46148</v>
       </c>
       <c r="B171" t="s">
-        <v>381</v>
+        <v>351</v>
       </c>
       <c r="C171" t="s">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="D171" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E171" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F171" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="G171" t="s">
         <v>17</v>
@@ -6133,25 +6892,25 @@
         <v>46148</v>
       </c>
       <c r="B172" t="s">
-        <v>383</v>
+        <v>353</v>
       </c>
       <c r="C172" t="s">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="D172" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E172" t="s">
         <v>31</v>
       </c>
       <c r="F172" t="s">
-        <v>323</v>
+        <v>7</v>
       </c>
       <c r="G172" t="s">
-        <v>36</v>
-      </c>
-      <c r="H172" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -6159,13 +6918,13 @@
         <v>46148</v>
       </c>
       <c r="B173" t="s">
-        <v>385</v>
+        <v>355</v>
       </c>
       <c r="C173" t="s">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="D173" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E173" t="s">
         <v>31</v>
@@ -6185,22 +6944,22 @@
         <v>46148</v>
       </c>
       <c r="B174" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="C174" t="s">
-        <v>388</v>
+        <v>358</v>
       </c>
       <c r="D174" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="E174" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F174" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G174" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H174">
         <v>0</v>
@@ -6211,22 +6970,22 @@
         <v>46148</v>
       </c>
       <c r="B175" t="s">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="C175" t="s">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="D175" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E175" t="s">
         <v>29</v>
       </c>
       <c r="F175" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G175" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H175">
         <v>0</v>
@@ -6237,13 +6996,13 @@
         <v>46148</v>
       </c>
       <c r="B176" t="s">
-        <v>391</v>
+        <v>361</v>
       </c>
       <c r="C176" t="s">
-        <v>392</v>
+        <v>362</v>
       </c>
       <c r="D176" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E176" t="s">
         <v>29</v>
@@ -6252,7 +7011,7 @@
         <v>8</v>
       </c>
       <c r="G176" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H176">
         <v>0</v>
@@ -6263,19 +7022,19 @@
         <v>46148</v>
       </c>
       <c r="B177" t="s">
-        <v>393</v>
+        <v>363</v>
       </c>
       <c r="C177" t="s">
-        <v>394</v>
+        <v>364</v>
       </c>
       <c r="D177" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E177" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F177" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G177" t="s">
         <v>17</v>
@@ -6289,13 +7048,13 @@
         <v>46148</v>
       </c>
       <c r="B178" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="C178" t="s">
-        <v>396</v>
+        <v>366</v>
       </c>
       <c r="D178" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E178" t="s">
         <v>29</v>
@@ -6304,7 +7063,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H178">
         <v>0</v>
@@ -6315,22 +7074,22 @@
         <v>46148</v>
       </c>
       <c r="B179" t="s">
-        <v>397</v>
+        <v>367</v>
       </c>
       <c r="C179" t="s">
-        <v>398</v>
+        <v>368</v>
       </c>
       <c r="D179" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E179" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F179" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G179" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H179">
         <v>0</v>
@@ -6341,13 +7100,13 @@
         <v>46148</v>
       </c>
       <c r="B180" t="s">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="C180" t="s">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="D180" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E180" t="s">
         <v>29</v>
@@ -6356,7 +7115,10 @@
         <v>8</v>
       </c>
       <c r="G180" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -6364,22 +7126,22 @@
         <v>46148</v>
       </c>
       <c r="B181" t="s">
-        <v>401</v>
+        <v>371</v>
       </c>
       <c r="C181" t="s">
-        <v>402</v>
+        <v>372</v>
       </c>
       <c r="D181" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="E181" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F181" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G181" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H181">
         <v>0</v>
@@ -6390,19 +7152,19 @@
         <v>46148</v>
       </c>
       <c r="B182" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="C182" t="s">
-        <v>404</v>
+        <v>374</v>
       </c>
       <c r="D182" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E182" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G182" t="s">
         <v>17</v>
@@ -6416,22 +7178,22 @@
         <v>46148</v>
       </c>
       <c r="B183" t="s">
-        <v>405</v>
+        <v>375</v>
       </c>
       <c r="C183" t="s">
-        <v>406</v>
+        <v>376</v>
       </c>
       <c r="D183" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E183" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F183" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G183" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H183">
         <v>0</v>
@@ -6442,22 +7204,22 @@
         <v>46148</v>
       </c>
       <c r="B184" t="s">
-        <v>407</v>
+        <v>377</v>
       </c>
       <c r="C184" t="s">
-        <v>408</v>
+        <v>378</v>
       </c>
       <c r="D184" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E184" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F184" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="G184" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H184">
         <v>0</v>
@@ -6468,19 +7230,19 @@
         <v>46148</v>
       </c>
       <c r="B185" t="s">
-        <v>409</v>
+        <v>379</v>
       </c>
       <c r="C185" t="s">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="D185" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E185" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F185" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G185" t="s">
         <v>17</v>
@@ -6494,13 +7256,13 @@
         <v>46148</v>
       </c>
       <c r="B186" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="C186" t="s">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="D186" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E186" t="s">
         <v>29</v>
@@ -6520,39 +7282,39 @@
         <v>46148</v>
       </c>
       <c r="B187" t="s">
-        <v>413</v>
+        <v>383</v>
       </c>
       <c r="C187" t="s">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="D187" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="E187" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F187" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="G187" t="s">
-        <v>17</v>
-      </c>
-      <c r="H187">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H187" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="B188" t="s">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="C188" t="s">
-        <v>416</v>
+        <v>386</v>
       </c>
       <c r="D188" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E188" t="s">
         <v>31</v>
@@ -6561,7 +7323,7 @@
         <v>7</v>
       </c>
       <c r="G188" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H188">
         <v>0</v>
@@ -6569,16 +7331,16 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="B189" t="s">
-        <v>417</v>
+        <v>387</v>
       </c>
       <c r="C189" t="s">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="D189" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="E189" t="s">
         <v>29</v>
@@ -6587,7 +7349,7 @@
         <v>8</v>
       </c>
       <c r="G189" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H189">
         <v>0</v>
@@ -6595,27 +7357,3187 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B190" t="s">
+        <v>389</v>
+      </c>
+      <c r="C190" t="s">
+        <v>390</v>
+      </c>
+      <c r="D190" t="s">
+        <v>14</v>
+      </c>
+      <c r="E190" t="s">
+        <v>29</v>
+      </c>
+      <c r="F190" t="s">
+        <v>8</v>
+      </c>
+      <c r="G190" t="s">
+        <v>19</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B191" t="s">
+        <v>391</v>
+      </c>
+      <c r="C191" t="s">
+        <v>392</v>
+      </c>
+      <c r="D191" t="s">
+        <v>11</v>
+      </c>
+      <c r="E191" t="s">
+        <v>29</v>
+      </c>
+      <c r="F191" t="s">
+        <v>8</v>
+      </c>
+      <c r="G191" t="s">
+        <v>17</v>
+      </c>
+      <c r="H191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B192" t="s">
+        <v>393</v>
+      </c>
+      <c r="C192" t="s">
+        <v>394</v>
+      </c>
+      <c r="D192" t="s">
+        <v>14</v>
+      </c>
+      <c r="E192" t="s">
+        <v>29</v>
+      </c>
+      <c r="F192" t="s">
+        <v>8</v>
+      </c>
+      <c r="G192" t="s">
+        <v>17</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B193" t="s">
+        <v>395</v>
+      </c>
+      <c r="C193" t="s">
+        <v>396</v>
+      </c>
+      <c r="D193" t="s">
+        <v>13</v>
+      </c>
+      <c r="E193" t="s">
+        <v>29</v>
+      </c>
+      <c r="F193" t="s">
+        <v>8</v>
+      </c>
+      <c r="G193" t="s">
+        <v>17</v>
+      </c>
+      <c r="H193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B194" t="s">
+        <v>397</v>
+      </c>
+      <c r="C194" t="s">
+        <v>398</v>
+      </c>
+      <c r="D194" t="s">
+        <v>23</v>
+      </c>
+      <c r="E194" t="s">
+        <v>31</v>
+      </c>
+      <c r="F194" t="s">
+        <v>7</v>
+      </c>
+      <c r="G194" t="s">
+        <v>33</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B195" t="s">
+        <v>399</v>
+      </c>
+      <c r="C195" t="s">
+        <v>400</v>
+      </c>
+      <c r="D195" t="s">
+        <v>42</v>
+      </c>
+      <c r="E195" t="s">
+        <v>29</v>
+      </c>
+      <c r="F195" t="s">
+        <v>8</v>
+      </c>
+      <c r="G195" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B196" t="s">
+        <v>401</v>
+      </c>
+      <c r="C196" t="s">
+        <v>402</v>
+      </c>
+      <c r="D196" t="s">
+        <v>35</v>
+      </c>
+      <c r="E196" t="s">
+        <v>31</v>
+      </c>
+      <c r="F196" t="s">
+        <v>7</v>
+      </c>
+      <c r="G196" t="s">
+        <v>19</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B197" t="s">
+        <v>403</v>
+      </c>
+      <c r="C197" t="s">
+        <v>404</v>
+      </c>
+      <c r="D197" t="s">
+        <v>42</v>
+      </c>
+      <c r="E197" t="s">
+        <v>29</v>
+      </c>
+      <c r="F197" t="s">
+        <v>8</v>
+      </c>
+      <c r="G197" t="s">
+        <v>17</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B198" t="s">
+        <v>405</v>
+      </c>
+      <c r="C198" t="s">
+        <v>406</v>
+      </c>
+      <c r="D198" t="s">
+        <v>23</v>
+      </c>
+      <c r="E198" t="s">
+        <v>31</v>
+      </c>
+      <c r="F198" t="s">
+        <v>7</v>
+      </c>
+      <c r="G198" t="s">
+        <v>17</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B199" t="s">
+        <v>407</v>
+      </c>
+      <c r="C199" t="s">
+        <v>408</v>
+      </c>
+      <c r="D199" t="s">
+        <v>26</v>
+      </c>
+      <c r="E199" t="s">
+        <v>29</v>
+      </c>
+      <c r="F199" t="s">
+        <v>8</v>
+      </c>
+      <c r="G199" t="s">
+        <v>17</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B200" t="s">
+        <v>409</v>
+      </c>
+      <c r="C200" t="s">
+        <v>410</v>
+      </c>
+      <c r="D200" t="s">
+        <v>23</v>
+      </c>
+      <c r="E200" t="s">
+        <v>31</v>
+      </c>
+      <c r="F200" t="s">
+        <v>7</v>
+      </c>
+      <c r="G200" t="s">
+        <v>17</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B201" t="s">
+        <v>411</v>
+      </c>
+      <c r="C201" t="s">
+        <v>412</v>
+      </c>
+      <c r="D201" t="s">
+        <v>14</v>
+      </c>
+      <c r="E201" t="s">
+        <v>29</v>
+      </c>
+      <c r="F201" t="s">
+        <v>8</v>
+      </c>
+      <c r="G201" t="s">
+        <v>17</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B202" t="s">
+        <v>413</v>
+      </c>
+      <c r="C202" t="s">
+        <v>414</v>
+      </c>
+      <c r="D202" t="s">
+        <v>6</v>
+      </c>
+      <c r="E202" t="s">
+        <v>29</v>
+      </c>
+      <c r="F202" t="s">
+        <v>8</v>
+      </c>
+      <c r="G202" t="s">
+        <v>17</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" s="1">
         <v>46149</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B203" t="s">
+        <v>415</v>
+      </c>
+      <c r="C203" t="s">
+        <v>416</v>
+      </c>
+      <c r="D203" t="s">
+        <v>22</v>
+      </c>
+      <c r="E203" t="s">
+        <v>31</v>
+      </c>
+      <c r="F203" t="s">
+        <v>7</v>
+      </c>
+      <c r="G203" t="s">
+        <v>17</v>
+      </c>
+      <c r="H203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B204" t="s">
+        <v>417</v>
+      </c>
+      <c r="C204" t="s">
+        <v>418</v>
+      </c>
+      <c r="D204" t="s">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>29</v>
+      </c>
+      <c r="F204" t="s">
+        <v>8</v>
+      </c>
+      <c r="G204" t="s">
+        <v>17</v>
+      </c>
+      <c r="H204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B205" t="s">
         <v>419</v>
       </c>
-      <c r="C190" t="s">
+      <c r="C205" t="s">
         <v>420</v>
       </c>
-      <c r="D190" t="s">
+      <c r="D205" t="s">
         <v>42</v>
       </c>
-      <c r="E190" t="s">
-        <v>29</v>
-      </c>
-      <c r="F190" t="s">
-        <v>8</v>
-      </c>
-      <c r="G190" t="s">
-        <v>17</v>
-      </c>
-      <c r="H190">
+      <c r="E205" t="s">
+        <v>29</v>
+      </c>
+      <c r="F205" t="s">
+        <v>8</v>
+      </c>
+      <c r="G205" t="s">
+        <v>17</v>
+      </c>
+      <c r="H205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B206" t="s">
+        <v>455</v>
+      </c>
+      <c r="C206" t="s">
+        <v>456</v>
+      </c>
+      <c r="D206" t="s">
+        <v>12</v>
+      </c>
+      <c r="E206" t="s">
+        <v>29</v>
+      </c>
+      <c r="F206" t="s">
+        <v>7</v>
+      </c>
+      <c r="G206" t="s">
+        <v>17</v>
+      </c>
+      <c r="H206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B207" t="s">
+        <v>457</v>
+      </c>
+      <c r="C207" t="s">
+        <v>458</v>
+      </c>
+      <c r="D207" t="s">
+        <v>6</v>
+      </c>
+      <c r="E207" t="s">
+        <v>29</v>
+      </c>
+      <c r="F207" t="s">
+        <v>8</v>
+      </c>
+      <c r="G207" t="s">
+        <v>17</v>
+      </c>
+      <c r="H207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B208" t="s">
+        <v>459</v>
+      </c>
+      <c r="C208" t="s">
+        <v>460</v>
+      </c>
+      <c r="D208" t="s">
+        <v>27</v>
+      </c>
+      <c r="E208" t="s">
+        <v>31</v>
+      </c>
+      <c r="F208" t="s">
+        <v>461</v>
+      </c>
+      <c r="G208" t="s">
+        <v>19</v>
+      </c>
+      <c r="H208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B209" t="s">
+        <v>462</v>
+      </c>
+      <c r="C209" t="s">
+        <v>463</v>
+      </c>
+      <c r="D209" t="s">
+        <v>14</v>
+      </c>
+      <c r="E209" t="s">
+        <v>29</v>
+      </c>
+      <c r="F209" t="s">
+        <v>8</v>
+      </c>
+      <c r="G209" t="s">
+        <v>18</v>
+      </c>
+      <c r="H209" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B210" t="s">
+        <v>464</v>
+      </c>
+      <c r="C210" t="s">
+        <v>465</v>
+      </c>
+      <c r="D210" t="s">
+        <v>42</v>
+      </c>
+      <c r="E210" t="s">
+        <v>29</v>
+      </c>
+      <c r="F210" t="s">
+        <v>8</v>
+      </c>
+      <c r="G210" t="s">
+        <v>33</v>
+      </c>
+      <c r="H210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B211" t="s">
+        <v>466</v>
+      </c>
+      <c r="C211" t="s">
+        <v>467</v>
+      </c>
+      <c r="D211" t="s">
+        <v>15</v>
+      </c>
+      <c r="E211" t="s">
+        <v>29</v>
+      </c>
+      <c r="F211" t="s">
+        <v>8</v>
+      </c>
+      <c r="G211" t="s">
+        <v>17</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B212" t="s">
+        <v>468</v>
+      </c>
+      <c r="C212" t="s">
+        <v>469</v>
+      </c>
+      <c r="D212" t="s">
+        <v>20</v>
+      </c>
+      <c r="E212" t="s">
+        <v>29</v>
+      </c>
+      <c r="F212" t="s">
+        <v>8</v>
+      </c>
+      <c r="G212" t="s">
+        <v>17</v>
+      </c>
+      <c r="H212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B213" t="s">
+        <v>470</v>
+      </c>
+      <c r="C213" t="s">
+        <v>471</v>
+      </c>
+      <c r="D213" t="s">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>29</v>
+      </c>
+      <c r="F213" t="s">
+        <v>8</v>
+      </c>
+      <c r="G213" t="s">
+        <v>17</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B214" t="s">
+        <v>472</v>
+      </c>
+      <c r="C214" t="s">
+        <v>473</v>
+      </c>
+      <c r="D214" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" t="s">
+        <v>29</v>
+      </c>
+      <c r="F214" t="s">
+        <v>8</v>
+      </c>
+      <c r="G214" t="s">
+        <v>17</v>
+      </c>
+      <c r="H214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B215" t="s">
+        <v>474</v>
+      </c>
+      <c r="C215" t="s">
+        <v>475</v>
+      </c>
+      <c r="D215" t="s">
+        <v>26</v>
+      </c>
+      <c r="E215" t="s">
+        <v>29</v>
+      </c>
+      <c r="F215" t="s">
+        <v>8</v>
+      </c>
+      <c r="G215" t="s">
+        <v>17</v>
+      </c>
+      <c r="H215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B216" t="s">
+        <v>476</v>
+      </c>
+      <c r="C216" t="s">
+        <v>477</v>
+      </c>
+      <c r="D216" t="s">
+        <v>15</v>
+      </c>
+      <c r="E216" t="s">
+        <v>29</v>
+      </c>
+      <c r="F216" t="s">
+        <v>8</v>
+      </c>
+      <c r="G216" t="s">
+        <v>17</v>
+      </c>
+      <c r="H216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B217" t="s">
+        <v>478</v>
+      </c>
+      <c r="C217" t="s">
+        <v>479</v>
+      </c>
+      <c r="D217" t="s">
+        <v>15</v>
+      </c>
+      <c r="E217" t="s">
+        <v>29</v>
+      </c>
+      <c r="F217" t="s">
+        <v>8</v>
+      </c>
+      <c r="G217" t="s">
+        <v>19</v>
+      </c>
+      <c r="H217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B218" t="s">
+        <v>480</v>
+      </c>
+      <c r="C218" t="s">
+        <v>481</v>
+      </c>
+      <c r="D218" t="s">
+        <v>41</v>
+      </c>
+      <c r="E218" t="s">
+        <v>31</v>
+      </c>
+      <c r="F218" t="s">
+        <v>7</v>
+      </c>
+      <c r="G218" t="s">
+        <v>17</v>
+      </c>
+      <c r="H218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B219" t="s">
+        <v>482</v>
+      </c>
+      <c r="C219" t="s">
+        <v>483</v>
+      </c>
+      <c r="D219" t="s">
+        <v>27</v>
+      </c>
+      <c r="E219" t="s">
+        <v>31</v>
+      </c>
+      <c r="F219" t="s">
+        <v>461</v>
+      </c>
+      <c r="G219" t="s">
+        <v>19</v>
+      </c>
+      <c r="H219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B220" t="s">
+        <v>484</v>
+      </c>
+      <c r="C220" t="s">
+        <v>485</v>
+      </c>
+      <c r="D220" t="s">
+        <v>6</v>
+      </c>
+      <c r="E220" t="s">
+        <v>29</v>
+      </c>
+      <c r="F220" t="s">
+        <v>8</v>
+      </c>
+      <c r="G220" t="s">
+        <v>17</v>
+      </c>
+      <c r="H220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B221" t="s">
+        <v>486</v>
+      </c>
+      <c r="C221" t="s">
+        <v>487</v>
+      </c>
+      <c r="D221" t="s">
+        <v>12</v>
+      </c>
+      <c r="E221" t="s">
+        <v>29</v>
+      </c>
+      <c r="F221" t="s">
+        <v>7</v>
+      </c>
+      <c r="G221" t="s">
+        <v>17</v>
+      </c>
+      <c r="H221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B222" t="s">
+        <v>488</v>
+      </c>
+      <c r="C222" t="s">
+        <v>489</v>
+      </c>
+      <c r="D222" t="s">
+        <v>26</v>
+      </c>
+      <c r="E222" t="s">
+        <v>29</v>
+      </c>
+      <c r="F222" t="s">
+        <v>8</v>
+      </c>
+      <c r="G222" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B223" t="s">
+        <v>490</v>
+      </c>
+      <c r="C223" t="s">
+        <v>491</v>
+      </c>
+      <c r="D223" t="s">
+        <v>15</v>
+      </c>
+      <c r="E223" t="s">
+        <v>29</v>
+      </c>
+      <c r="F223" t="s">
+        <v>8</v>
+      </c>
+      <c r="G223" t="s">
+        <v>17</v>
+      </c>
+      <c r="H223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B224" t="s">
+        <v>492</v>
+      </c>
+      <c r="C224" t="s">
+        <v>493</v>
+      </c>
+      <c r="D224" t="s">
+        <v>12</v>
+      </c>
+      <c r="E224" t="s">
+        <v>29</v>
+      </c>
+      <c r="F224" t="s">
+        <v>7</v>
+      </c>
+      <c r="G224" t="s">
+        <v>17</v>
+      </c>
+      <c r="H224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B225" t="s">
+        <v>494</v>
+      </c>
+      <c r="C225" t="s">
+        <v>495</v>
+      </c>
+      <c r="D225" t="s">
+        <v>496</v>
+      </c>
+      <c r="E225" t="s">
+        <v>31</v>
+      </c>
+      <c r="F225" t="s">
+        <v>8</v>
+      </c>
+      <c r="G225" t="s">
+        <v>33</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B226" t="s">
+        <v>497</v>
+      </c>
+      <c r="C226" t="s">
+        <v>498</v>
+      </c>
+      <c r="D226" t="s">
+        <v>26</v>
+      </c>
+      <c r="E226" t="s">
+        <v>29</v>
+      </c>
+      <c r="F226" t="s">
+        <v>8</v>
+      </c>
+      <c r="G226" t="s">
+        <v>17</v>
+      </c>
+      <c r="H226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B227" t="s">
+        <v>499</v>
+      </c>
+      <c r="C227" t="s">
+        <v>500</v>
+      </c>
+      <c r="D227" t="s">
+        <v>21</v>
+      </c>
+      <c r="E227" t="s">
+        <v>29</v>
+      </c>
+      <c r="F227" t="s">
+        <v>8</v>
+      </c>
+      <c r="G227" t="s">
+        <v>17</v>
+      </c>
+      <c r="H227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B228" t="s">
+        <v>501</v>
+      </c>
+      <c r="C228" t="s">
+        <v>502</v>
+      </c>
+      <c r="D228" t="s">
+        <v>9</v>
+      </c>
+      <c r="E228" t="s">
+        <v>31</v>
+      </c>
+      <c r="F228" t="s">
+        <v>7</v>
+      </c>
+      <c r="G228" t="s">
+        <v>33</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B229" t="s">
+        <v>503</v>
+      </c>
+      <c r="C229" t="s">
+        <v>504</v>
+      </c>
+      <c r="D229" t="s">
+        <v>6</v>
+      </c>
+      <c r="E229" t="s">
+        <v>29</v>
+      </c>
+      <c r="F229" t="s">
+        <v>8</v>
+      </c>
+      <c r="G229" t="s">
+        <v>17</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B230" t="s">
+        <v>505</v>
+      </c>
+      <c r="C230" t="s">
+        <v>506</v>
+      </c>
+      <c r="D230" t="s">
+        <v>15</v>
+      </c>
+      <c r="E230" t="s">
+        <v>29</v>
+      </c>
+      <c r="F230" t="s">
+        <v>8</v>
+      </c>
+      <c r="G230" t="s">
+        <v>17</v>
+      </c>
+      <c r="H230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B231" t="s">
+        <v>507</v>
+      </c>
+      <c r="C231" t="s">
+        <v>508</v>
+      </c>
+      <c r="D231" t="s">
+        <v>21</v>
+      </c>
+      <c r="E231" t="s">
+        <v>29</v>
+      </c>
+      <c r="F231" t="s">
+        <v>8</v>
+      </c>
+      <c r="G231" t="s">
+        <v>17</v>
+      </c>
+      <c r="H231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B232" t="s">
+        <v>509</v>
+      </c>
+      <c r="C232" t="s">
+        <v>510</v>
+      </c>
+      <c r="D232" t="s">
+        <v>13</v>
+      </c>
+      <c r="E232" t="s">
+        <v>29</v>
+      </c>
+      <c r="F232" t="s">
+        <v>8</v>
+      </c>
+      <c r="G232" t="s">
+        <v>17</v>
+      </c>
+      <c r="H232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B233" t="s">
+        <v>511</v>
+      </c>
+      <c r="C233" t="s">
+        <v>512</v>
+      </c>
+      <c r="D233" t="s">
+        <v>21</v>
+      </c>
+      <c r="E233" t="s">
+        <v>29</v>
+      </c>
+      <c r="F233" t="s">
+        <v>8</v>
+      </c>
+      <c r="G233" t="s">
+        <v>17</v>
+      </c>
+      <c r="H233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B234" t="s">
+        <v>513</v>
+      </c>
+      <c r="C234" t="s">
+        <v>514</v>
+      </c>
+      <c r="D234" t="s">
+        <v>27</v>
+      </c>
+      <c r="E234" t="s">
+        <v>31</v>
+      </c>
+      <c r="F234" t="s">
+        <v>461</v>
+      </c>
+      <c r="G234" t="s">
+        <v>17</v>
+      </c>
+      <c r="H234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B235" t="s">
+        <v>515</v>
+      </c>
+      <c r="C235" t="s">
+        <v>516</v>
+      </c>
+      <c r="D235" t="s">
+        <v>35</v>
+      </c>
+      <c r="E235" t="s">
+        <v>31</v>
+      </c>
+      <c r="F235" t="s">
+        <v>7</v>
+      </c>
+      <c r="G235" t="s">
+        <v>17</v>
+      </c>
+      <c r="H235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B236" t="s">
+        <v>517</v>
+      </c>
+      <c r="C236" t="s">
+        <v>518</v>
+      </c>
+      <c r="D236" t="s">
+        <v>11</v>
+      </c>
+      <c r="E236" t="s">
+        <v>29</v>
+      </c>
+      <c r="F236" t="s">
+        <v>8</v>
+      </c>
+      <c r="G236" t="s">
+        <v>17</v>
+      </c>
+      <c r="H236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B237" t="s">
+        <v>519</v>
+      </c>
+      <c r="C237" t="s">
+        <v>520</v>
+      </c>
+      <c r="D237" t="s">
+        <v>35</v>
+      </c>
+      <c r="E237" t="s">
+        <v>31</v>
+      </c>
+      <c r="F237" t="s">
+        <v>521</v>
+      </c>
+      <c r="G237" t="s">
+        <v>17</v>
+      </c>
+      <c r="H237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B238" t="s">
+        <v>522</v>
+      </c>
+      <c r="C238" t="s">
+        <v>523</v>
+      </c>
+      <c r="D238" t="s">
+        <v>14</v>
+      </c>
+      <c r="E238" t="s">
+        <v>29</v>
+      </c>
+      <c r="F238" t="s">
+        <v>8</v>
+      </c>
+      <c r="G238" t="s">
+        <v>17</v>
+      </c>
+      <c r="H238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B239" t="s">
+        <v>524</v>
+      </c>
+      <c r="C239" t="s">
+        <v>525</v>
+      </c>
+      <c r="D239" t="s">
+        <v>9</v>
+      </c>
+      <c r="E239" t="s">
+        <v>31</v>
+      </c>
+      <c r="F239" t="s">
+        <v>7</v>
+      </c>
+      <c r="G239" t="s">
+        <v>17</v>
+      </c>
+      <c r="H239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B240" t="s">
+        <v>526</v>
+      </c>
+      <c r="C240" t="s">
+        <v>527</v>
+      </c>
+      <c r="D240" t="s">
+        <v>27</v>
+      </c>
+      <c r="E240" t="s">
+        <v>31</v>
+      </c>
+      <c r="F240" t="s">
+        <v>461</v>
+      </c>
+      <c r="G240" t="s">
+        <v>19</v>
+      </c>
+      <c r="H240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B241" t="s">
+        <v>528</v>
+      </c>
+      <c r="C241" t="s">
+        <v>529</v>
+      </c>
+      <c r="D241" t="s">
+        <v>38</v>
+      </c>
+      <c r="E241" t="s">
+        <v>31</v>
+      </c>
+      <c r="F241" t="s">
+        <v>7</v>
+      </c>
+      <c r="G241" t="s">
+        <v>19</v>
+      </c>
+      <c r="H241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B242" t="s">
+        <v>530</v>
+      </c>
+      <c r="C242" t="s">
+        <v>531</v>
+      </c>
+      <c r="D242" t="s">
+        <v>11</v>
+      </c>
+      <c r="E242" t="s">
+        <v>29</v>
+      </c>
+      <c r="F242" t="s">
+        <v>8</v>
+      </c>
+      <c r="G242" t="s">
+        <v>19</v>
+      </c>
+      <c r="H242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B243" t="s">
+        <v>532</v>
+      </c>
+      <c r="C243" t="s">
+        <v>533</v>
+      </c>
+      <c r="D243" t="s">
+        <v>38</v>
+      </c>
+      <c r="E243" t="s">
+        <v>31</v>
+      </c>
+      <c r="F243" t="s">
+        <v>7</v>
+      </c>
+      <c r="G243" t="s">
+        <v>17</v>
+      </c>
+      <c r="H243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B244" t="s">
+        <v>534</v>
+      </c>
+      <c r="C244" t="s">
+        <v>535</v>
+      </c>
+      <c r="D244" t="s">
+        <v>21</v>
+      </c>
+      <c r="E244" t="s">
+        <v>29</v>
+      </c>
+      <c r="F244" t="s">
+        <v>8</v>
+      </c>
+      <c r="G244" t="s">
+        <v>17</v>
+      </c>
+      <c r="H244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B245" t="s">
+        <v>536</v>
+      </c>
+      <c r="C245" t="s">
+        <v>537</v>
+      </c>
+      <c r="D245" t="s">
+        <v>22</v>
+      </c>
+      <c r="E245" t="s">
+        <v>31</v>
+      </c>
+      <c r="F245" t="s">
+        <v>7</v>
+      </c>
+      <c r="G245" t="s">
+        <v>18</v>
+      </c>
+      <c r="H245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B246" t="s">
+        <v>538</v>
+      </c>
+      <c r="C246" t="s">
+        <v>539</v>
+      </c>
+      <c r="D246" t="s">
+        <v>32</v>
+      </c>
+      <c r="E246" t="s">
+        <v>31</v>
+      </c>
+      <c r="F246" t="s">
+        <v>7</v>
+      </c>
+      <c r="G246" t="s">
+        <v>17</v>
+      </c>
+      <c r="H246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B247" t="s">
+        <v>540</v>
+      </c>
+      <c r="C247" t="s">
+        <v>541</v>
+      </c>
+      <c r="D247" t="s">
+        <v>23</v>
+      </c>
+      <c r="E247" t="s">
+        <v>31</v>
+      </c>
+      <c r="F247" t="s">
+        <v>7</v>
+      </c>
+      <c r="G247" t="s">
+        <v>17</v>
+      </c>
+      <c r="H247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B248" t="s">
+        <v>542</v>
+      </c>
+      <c r="C248" t="s">
+        <v>543</v>
+      </c>
+      <c r="D248" t="s">
+        <v>15</v>
+      </c>
+      <c r="E248" t="s">
+        <v>29</v>
+      </c>
+      <c r="F248" t="s">
+        <v>8</v>
+      </c>
+      <c r="G248" t="s">
+        <v>17</v>
+      </c>
+      <c r="H248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B249" t="s">
+        <v>544</v>
+      </c>
+      <c r="C249" t="s">
+        <v>545</v>
+      </c>
+      <c r="D249" t="s">
+        <v>14</v>
+      </c>
+      <c r="E249" t="s">
+        <v>29</v>
+      </c>
+      <c r="F249" t="s">
+        <v>8</v>
+      </c>
+      <c r="G249" t="s">
+        <v>19</v>
+      </c>
+      <c r="H249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B250" t="s">
+        <v>546</v>
+      </c>
+      <c r="C250" t="s">
+        <v>547</v>
+      </c>
+      <c r="D250" t="s">
+        <v>13</v>
+      </c>
+      <c r="E250" t="s">
+        <v>29</v>
+      </c>
+      <c r="F250" t="s">
+        <v>8</v>
+      </c>
+      <c r="G250" t="s">
+        <v>17</v>
+      </c>
+      <c r="H250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B251" t="s">
+        <v>548</v>
+      </c>
+      <c r="C251" t="s">
+        <v>549</v>
+      </c>
+      <c r="D251" t="s">
+        <v>26</v>
+      </c>
+      <c r="E251" t="s">
+        <v>29</v>
+      </c>
+      <c r="F251" t="s">
+        <v>8</v>
+      </c>
+      <c r="G251" t="s">
+        <v>17</v>
+      </c>
+      <c r="H251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A252" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B252" t="s">
+        <v>550</v>
+      </c>
+      <c r="C252" t="s">
+        <v>551</v>
+      </c>
+      <c r="D252" t="s">
+        <v>15</v>
+      </c>
+      <c r="E252" t="s">
+        <v>29</v>
+      </c>
+      <c r="F252" t="s">
+        <v>8</v>
+      </c>
+      <c r="G252" t="s">
+        <v>19</v>
+      </c>
+      <c r="H252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A253" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B253" t="s">
+        <v>552</v>
+      </c>
+      <c r="C253" t="s">
+        <v>553</v>
+      </c>
+      <c r="D253" t="s">
+        <v>13</v>
+      </c>
+      <c r="E253" t="s">
+        <v>29</v>
+      </c>
+      <c r="F253" t="s">
+        <v>8</v>
+      </c>
+      <c r="G253" t="s">
+        <v>17</v>
+      </c>
+      <c r="H253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A254" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B254" t="s">
+        <v>554</v>
+      </c>
+      <c r="C254" t="s">
+        <v>555</v>
+      </c>
+      <c r="D254" t="s">
+        <v>21</v>
+      </c>
+      <c r="E254" t="s">
+        <v>29</v>
+      </c>
+      <c r="F254" t="s">
+        <v>8</v>
+      </c>
+      <c r="G254" t="s">
+        <v>17</v>
+      </c>
+      <c r="H254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A255" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B255" t="s">
+        <v>556</v>
+      </c>
+      <c r="C255" t="s">
+        <v>557</v>
+      </c>
+      <c r="D255" t="s">
+        <v>12</v>
+      </c>
+      <c r="E255" t="s">
+        <v>31</v>
+      </c>
+      <c r="F255" t="s">
+        <v>7</v>
+      </c>
+      <c r="G255" t="s">
+        <v>17</v>
+      </c>
+      <c r="H255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A256" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B256" t="s">
+        <v>558</v>
+      </c>
+      <c r="C256" t="s">
+        <v>559</v>
+      </c>
+      <c r="D256" t="s">
+        <v>25</v>
+      </c>
+      <c r="E256" t="s">
+        <v>30</v>
+      </c>
+      <c r="F256" t="s">
+        <v>34</v>
+      </c>
+      <c r="G256" t="s">
+        <v>17</v>
+      </c>
+      <c r="H256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B257" t="s">
+        <v>560</v>
+      </c>
+      <c r="C257" t="s">
+        <v>561</v>
+      </c>
+      <c r="D257" t="s">
+        <v>25</v>
+      </c>
+      <c r="E257" t="s">
+        <v>30</v>
+      </c>
+      <c r="F257" t="s">
+        <v>34</v>
+      </c>
+      <c r="G257" t="s">
+        <v>17</v>
+      </c>
+      <c r="H257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B258" t="s">
+        <v>562</v>
+      </c>
+      <c r="C258" t="s">
+        <v>563</v>
+      </c>
+      <c r="D258" t="s">
+        <v>22</v>
+      </c>
+      <c r="E258" t="s">
+        <v>31</v>
+      </c>
+      <c r="F258" t="s">
+        <v>7</v>
+      </c>
+      <c r="G258" t="s">
+        <v>17</v>
+      </c>
+      <c r="H258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A259" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B259" t="s">
+        <v>564</v>
+      </c>
+      <c r="C259" t="s">
+        <v>565</v>
+      </c>
+      <c r="D259" t="s">
+        <v>15</v>
+      </c>
+      <c r="E259" t="s">
+        <v>29</v>
+      </c>
+      <c r="F259" t="s">
+        <v>7</v>
+      </c>
+      <c r="G259" t="s">
+        <v>19</v>
+      </c>
+      <c r="H259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A260" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B260" t="s">
+        <v>566</v>
+      </c>
+      <c r="C260" t="s">
+        <v>567</v>
+      </c>
+      <c r="D260" t="s">
+        <v>12</v>
+      </c>
+      <c r="E260" t="s">
+        <v>29</v>
+      </c>
+      <c r="F260" t="s">
+        <v>7</v>
+      </c>
+      <c r="G260" t="s">
+        <v>33</v>
+      </c>
+      <c r="H260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A261" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B261" t="s">
+        <v>568</v>
+      </c>
+      <c r="C261" t="s">
+        <v>569</v>
+      </c>
+      <c r="D261" t="s">
+        <v>20</v>
+      </c>
+      <c r="E261" t="s">
+        <v>29</v>
+      </c>
+      <c r="F261" t="s">
+        <v>8</v>
+      </c>
+      <c r="G261" t="s">
+        <v>17</v>
+      </c>
+      <c r="H261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A262" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B262" t="s">
+        <v>225</v>
+      </c>
+      <c r="C262" t="s">
+        <v>226</v>
+      </c>
+      <c r="D262" t="s">
+        <v>9</v>
+      </c>
+      <c r="E262" t="s">
+        <v>31</v>
+      </c>
+      <c r="F262" t="s">
+        <v>7</v>
+      </c>
+      <c r="G262" t="s">
+        <v>17</v>
+      </c>
+      <c r="H262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A263" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B263" t="s">
+        <v>570</v>
+      </c>
+      <c r="C263" t="s">
+        <v>571</v>
+      </c>
+      <c r="D263" t="s">
+        <v>15</v>
+      </c>
+      <c r="E263" t="s">
+        <v>29</v>
+      </c>
+      <c r="F263" t="s">
+        <v>8</v>
+      </c>
+      <c r="G263" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A264" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B264" t="s">
+        <v>572</v>
+      </c>
+      <c r="C264" t="s">
+        <v>573</v>
+      </c>
+      <c r="D264" t="s">
+        <v>22</v>
+      </c>
+      <c r="E264" t="s">
+        <v>31</v>
+      </c>
+      <c r="F264" t="s">
+        <v>7</v>
+      </c>
+      <c r="G264" t="s">
+        <v>17</v>
+      </c>
+      <c r="H264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A265" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B265" t="s">
+        <v>574</v>
+      </c>
+      <c r="C265" t="s">
+        <v>575</v>
+      </c>
+      <c r="D265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E265" t="s">
+        <v>29</v>
+      </c>
+      <c r="F265" t="s">
+        <v>8</v>
+      </c>
+      <c r="G265" t="s">
+        <v>17</v>
+      </c>
+      <c r="H265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A266" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B266" t="s">
+        <v>576</v>
+      </c>
+      <c r="C266" t="s">
+        <v>577</v>
+      </c>
+      <c r="D266" t="s">
+        <v>14</v>
+      </c>
+      <c r="E266" t="s">
+        <v>29</v>
+      </c>
+      <c r="F266" t="s">
+        <v>8</v>
+      </c>
+      <c r="G266" t="s">
+        <v>19</v>
+      </c>
+      <c r="H266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A267" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B267" t="s">
+        <v>578</v>
+      </c>
+      <c r="C267" t="s">
+        <v>579</v>
+      </c>
+      <c r="D267" t="s">
+        <v>13</v>
+      </c>
+      <c r="E267" t="s">
+        <v>29</v>
+      </c>
+      <c r="F267" t="s">
+        <v>8</v>
+      </c>
+      <c r="G267" t="s">
+        <v>17</v>
+      </c>
+      <c r="H267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A268" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B268" t="s">
+        <v>580</v>
+      </c>
+      <c r="C268" t="s">
+        <v>581</v>
+      </c>
+      <c r="D268" t="s">
+        <v>15</v>
+      </c>
+      <c r="E268" t="s">
+        <v>29</v>
+      </c>
+      <c r="F268" t="s">
+        <v>8</v>
+      </c>
+      <c r="G268" t="s">
+        <v>17</v>
+      </c>
+      <c r="H268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A269" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B269" t="s">
+        <v>582</v>
+      </c>
+      <c r="C269" t="s">
+        <v>583</v>
+      </c>
+      <c r="D269" t="s">
+        <v>12</v>
+      </c>
+      <c r="E269" t="s">
+        <v>29</v>
+      </c>
+      <c r="F269" t="s">
+        <v>7</v>
+      </c>
+      <c r="G269" t="s">
+        <v>19</v>
+      </c>
+      <c r="H269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A270" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B270" t="s">
+        <v>584</v>
+      </c>
+      <c r="C270" t="s">
+        <v>585</v>
+      </c>
+      <c r="D270" t="s">
+        <v>6</v>
+      </c>
+      <c r="E270" t="s">
+        <v>29</v>
+      </c>
+      <c r="F270" t="s">
+        <v>8</v>
+      </c>
+      <c r="G270" t="s">
+        <v>17</v>
+      </c>
+      <c r="H270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B271" t="s">
+        <v>586</v>
+      </c>
+      <c r="C271" t="s">
+        <v>587</v>
+      </c>
+      <c r="D271" t="s">
+        <v>32</v>
+      </c>
+      <c r="E271" t="s">
+        <v>31</v>
+      </c>
+      <c r="F271" t="s">
+        <v>7</v>
+      </c>
+      <c r="G271" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A272" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B272" t="s">
+        <v>588</v>
+      </c>
+      <c r="C272" t="s">
+        <v>589</v>
+      </c>
+      <c r="D272" t="s">
+        <v>13</v>
+      </c>
+      <c r="E272" t="s">
+        <v>29</v>
+      </c>
+      <c r="F272" t="s">
+        <v>8</v>
+      </c>
+      <c r="G272" t="s">
+        <v>17</v>
+      </c>
+      <c r="H272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A273" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B273" t="s">
+        <v>590</v>
+      </c>
+      <c r="C273" t="s">
+        <v>591</v>
+      </c>
+      <c r="D273" t="s">
+        <v>11</v>
+      </c>
+      <c r="E273" t="s">
+        <v>29</v>
+      </c>
+      <c r="F273" t="s">
+        <v>8</v>
+      </c>
+      <c r="G273" t="s">
+        <v>17</v>
+      </c>
+      <c r="H273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A274" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B274" t="s">
+        <v>592</v>
+      </c>
+      <c r="C274" t="s">
+        <v>593</v>
+      </c>
+      <c r="D274" t="s">
+        <v>6</v>
+      </c>
+      <c r="E274" t="s">
+        <v>29</v>
+      </c>
+      <c r="F274" t="s">
+        <v>8</v>
+      </c>
+      <c r="G274" t="s">
+        <v>17</v>
+      </c>
+      <c r="H274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A275" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B275" t="s">
+        <v>594</v>
+      </c>
+      <c r="C275" t="s">
+        <v>595</v>
+      </c>
+      <c r="D275" t="s">
+        <v>35</v>
+      </c>
+      <c r="E275" t="s">
+        <v>31</v>
+      </c>
+      <c r="F275" t="s">
+        <v>7</v>
+      </c>
+      <c r="G275" t="s">
+        <v>17</v>
+      </c>
+      <c r="H275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A276" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B276" t="s">
+        <v>596</v>
+      </c>
+      <c r="C276" t="s">
+        <v>597</v>
+      </c>
+      <c r="D276" t="s">
+        <v>13</v>
+      </c>
+      <c r="E276" t="s">
+        <v>29</v>
+      </c>
+      <c r="F276" t="s">
+        <v>8</v>
+      </c>
+      <c r="G276" t="s">
+        <v>17</v>
+      </c>
+      <c r="H276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A277" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B277" t="s">
+        <v>598</v>
+      </c>
+      <c r="C277" t="s">
+        <v>599</v>
+      </c>
+      <c r="D277" t="s">
+        <v>22</v>
+      </c>
+      <c r="E277" t="s">
+        <v>31</v>
+      </c>
+      <c r="F277" t="s">
+        <v>7</v>
+      </c>
+      <c r="G277" t="s">
+        <v>17</v>
+      </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A278" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B278" t="s">
+        <v>600</v>
+      </c>
+      <c r="C278" t="s">
+        <v>601</v>
+      </c>
+      <c r="D278" t="s">
+        <v>496</v>
+      </c>
+      <c r="E278" t="s">
+        <v>31</v>
+      </c>
+      <c r="F278" t="s">
+        <v>8</v>
+      </c>
+      <c r="G278" t="s">
+        <v>17</v>
+      </c>
+      <c r="H278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A279" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B279" t="s">
+        <v>602</v>
+      </c>
+      <c r="C279" t="s">
+        <v>603</v>
+      </c>
+      <c r="D279" t="s">
+        <v>14</v>
+      </c>
+      <c r="E279" t="s">
+        <v>29</v>
+      </c>
+      <c r="F279" t="s">
+        <v>8</v>
+      </c>
+      <c r="G279" t="s">
+        <v>17</v>
+      </c>
+      <c r="H279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A280" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B280" t="s">
+        <v>604</v>
+      </c>
+      <c r="C280" t="s">
+        <v>605</v>
+      </c>
+      <c r="D280" t="s">
+        <v>26</v>
+      </c>
+      <c r="E280" t="s">
+        <v>29</v>
+      </c>
+      <c r="F280" t="s">
+        <v>8</v>
+      </c>
+      <c r="G280" t="s">
+        <v>19</v>
+      </c>
+      <c r="H280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A281" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B281" t="s">
+        <v>606</v>
+      </c>
+      <c r="C281" t="s">
+        <v>607</v>
+      </c>
+      <c r="D281" t="s">
+        <v>38</v>
+      </c>
+      <c r="E281" t="s">
+        <v>31</v>
+      </c>
+      <c r="F281" t="s">
+        <v>7</v>
+      </c>
+      <c r="G281" t="s">
+        <v>17</v>
+      </c>
+      <c r="H281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A282" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B282" t="s">
+        <v>608</v>
+      </c>
+      <c r="C282" t="s">
+        <v>609</v>
+      </c>
+      <c r="D282" t="s">
+        <v>23</v>
+      </c>
+      <c r="E282" t="s">
+        <v>31</v>
+      </c>
+      <c r="F282" t="s">
+        <v>7</v>
+      </c>
+      <c r="G282" t="s">
+        <v>17</v>
+      </c>
+      <c r="H282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A283" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B283" t="s">
+        <v>610</v>
+      </c>
+      <c r="C283" t="s">
+        <v>611</v>
+      </c>
+      <c r="D283" t="s">
+        <v>9</v>
+      </c>
+      <c r="E283" t="s">
+        <v>31</v>
+      </c>
+      <c r="F283" t="s">
+        <v>7</v>
+      </c>
+      <c r="G283" t="s">
+        <v>17</v>
+      </c>
+      <c r="H283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A284" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B284" t="s">
+        <v>612</v>
+      </c>
+      <c r="C284" t="s">
+        <v>613</v>
+      </c>
+      <c r="D284" t="s">
+        <v>9</v>
+      </c>
+      <c r="E284" t="s">
+        <v>31</v>
+      </c>
+      <c r="F284" t="s">
+        <v>7</v>
+      </c>
+      <c r="G284" t="s">
+        <v>18</v>
+      </c>
+      <c r="H284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A285" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B285" t="s">
+        <v>614</v>
+      </c>
+      <c r="C285" t="s">
+        <v>615</v>
+      </c>
+      <c r="D285" t="s">
+        <v>6</v>
+      </c>
+      <c r="E285" t="s">
+        <v>29</v>
+      </c>
+      <c r="F285" t="s">
+        <v>8</v>
+      </c>
+      <c r="G285" t="s">
+        <v>17</v>
+      </c>
+      <c r="H285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A286" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B286" t="s">
+        <v>616</v>
+      </c>
+      <c r="C286" t="s">
+        <v>617</v>
+      </c>
+      <c r="D286" t="s">
+        <v>22</v>
+      </c>
+      <c r="E286" t="s">
+        <v>31</v>
+      </c>
+      <c r="F286" t="s">
+        <v>7</v>
+      </c>
+      <c r="G286" t="s">
+        <v>17</v>
+      </c>
+      <c r="H286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A287" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B287" t="s">
+        <v>618</v>
+      </c>
+      <c r="C287" t="s">
+        <v>619</v>
+      </c>
+      <c r="D287" t="s">
+        <v>27</v>
+      </c>
+      <c r="E287" t="s">
+        <v>31</v>
+      </c>
+      <c r="F287" t="s">
+        <v>7</v>
+      </c>
+      <c r="G287" t="s">
+        <v>17</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A288" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B288" t="s">
+        <v>620</v>
+      </c>
+      <c r="C288" t="s">
+        <v>621</v>
+      </c>
+      <c r="D288" t="s">
+        <v>26</v>
+      </c>
+      <c r="E288" t="s">
+        <v>29</v>
+      </c>
+      <c r="F288" t="s">
+        <v>8</v>
+      </c>
+      <c r="G288" t="s">
+        <v>17</v>
+      </c>
+      <c r="H288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A289" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B289" t="s">
+        <v>622</v>
+      </c>
+      <c r="C289" t="s">
+        <v>623</v>
+      </c>
+      <c r="D289" t="s">
+        <v>23</v>
+      </c>
+      <c r="E289" t="s">
+        <v>31</v>
+      </c>
+      <c r="F289" t="s">
+        <v>7</v>
+      </c>
+      <c r="G289" t="s">
+        <v>17</v>
+      </c>
+      <c r="H289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A290" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B290" t="s">
+        <v>624</v>
+      </c>
+      <c r="C290" t="s">
+        <v>625</v>
+      </c>
+      <c r="D290" t="s">
+        <v>42</v>
+      </c>
+      <c r="E290" t="s">
+        <v>29</v>
+      </c>
+      <c r="F290" t="s">
+        <v>8</v>
+      </c>
+      <c r="G290" t="s">
+        <v>17</v>
+      </c>
+      <c r="H290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A291" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B291" t="s">
+        <v>626</v>
+      </c>
+      <c r="C291" t="s">
+        <v>627</v>
+      </c>
+      <c r="D291" t="s">
+        <v>23</v>
+      </c>
+      <c r="E291" t="s">
+        <v>31</v>
+      </c>
+      <c r="F291" t="s">
+        <v>7</v>
+      </c>
+      <c r="G291" t="s">
+        <v>19</v>
+      </c>
+      <c r="H291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A292" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B292" t="s">
+        <v>628</v>
+      </c>
+      <c r="C292" t="s">
+        <v>629</v>
+      </c>
+      <c r="D292" t="s">
+        <v>26</v>
+      </c>
+      <c r="E292" t="s">
+        <v>29</v>
+      </c>
+      <c r="F292" t="s">
+        <v>8</v>
+      </c>
+      <c r="G292" t="s">
+        <v>17</v>
+      </c>
+      <c r="H292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A293" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B293" t="s">
+        <v>630</v>
+      </c>
+      <c r="C293" t="s">
+        <v>631</v>
+      </c>
+      <c r="D293" t="s">
+        <v>42</v>
+      </c>
+      <c r="E293" t="s">
+        <v>29</v>
+      </c>
+      <c r="F293" t="s">
+        <v>8</v>
+      </c>
+      <c r="G293" t="s">
+        <v>33</v>
+      </c>
+      <c r="H293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A294" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B294" t="s">
+        <v>632</v>
+      </c>
+      <c r="C294" t="s">
+        <v>633</v>
+      </c>
+      <c r="D294" t="s">
+        <v>9</v>
+      </c>
+      <c r="E294" t="s">
+        <v>31</v>
+      </c>
+      <c r="F294" t="s">
+        <v>7</v>
+      </c>
+      <c r="G294" t="s">
+        <v>19</v>
+      </c>
+      <c r="H294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A295" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B295" t="s">
+        <v>634</v>
+      </c>
+      <c r="C295" t="s">
+        <v>635</v>
+      </c>
+      <c r="D295" t="s">
+        <v>13</v>
+      </c>
+      <c r="E295" t="s">
+        <v>29</v>
+      </c>
+      <c r="F295" t="s">
+        <v>8</v>
+      </c>
+      <c r="G295" t="s">
+        <v>17</v>
+      </c>
+      <c r="H295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A296" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B296" t="s">
+        <v>636</v>
+      </c>
+      <c r="C296" t="s">
+        <v>637</v>
+      </c>
+      <c r="D296" t="s">
+        <v>20</v>
+      </c>
+      <c r="E296" t="s">
+        <v>29</v>
+      </c>
+      <c r="F296" t="s">
+        <v>8</v>
+      </c>
+      <c r="G296" t="s">
+        <v>18</v>
+      </c>
+      <c r="H296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A297" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B297" t="s">
+        <v>638</v>
+      </c>
+      <c r="C297" t="s">
+        <v>639</v>
+      </c>
+      <c r="D297" t="s">
+        <v>15</v>
+      </c>
+      <c r="E297" t="s">
+        <v>29</v>
+      </c>
+      <c r="F297" t="s">
+        <v>8</v>
+      </c>
+      <c r="G297" t="s">
+        <v>36</v>
+      </c>
+      <c r="H297" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A298" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B298" t="s">
+        <v>640</v>
+      </c>
+      <c r="C298" t="s">
+        <v>641</v>
+      </c>
+      <c r="D298" t="s">
+        <v>11</v>
+      </c>
+      <c r="E298" t="s">
+        <v>29</v>
+      </c>
+      <c r="F298" t="s">
+        <v>8</v>
+      </c>
+      <c r="G298" t="s">
+        <v>19</v>
+      </c>
+      <c r="H298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A299" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B299" t="s">
+        <v>642</v>
+      </c>
+      <c r="C299" t="s">
+        <v>643</v>
+      </c>
+      <c r="D299" t="s">
+        <v>11</v>
+      </c>
+      <c r="E299" t="s">
+        <v>29</v>
+      </c>
+      <c r="F299" t="s">
+        <v>8</v>
+      </c>
+      <c r="G299" t="s">
+        <v>17</v>
+      </c>
+      <c r="H299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A300" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B300" t="s">
+        <v>644</v>
+      </c>
+      <c r="C300" t="s">
+        <v>645</v>
+      </c>
+      <c r="D300" t="s">
+        <v>22</v>
+      </c>
+      <c r="E300" t="s">
+        <v>31</v>
+      </c>
+      <c r="F300" t="s">
+        <v>7</v>
+      </c>
+      <c r="G300" t="s">
+        <v>17</v>
+      </c>
+      <c r="H300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A301" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B301" t="s">
+        <v>646</v>
+      </c>
+      <c r="C301" t="s">
+        <v>647</v>
+      </c>
+      <c r="D301" t="s">
+        <v>20</v>
+      </c>
+      <c r="E301" t="s">
+        <v>29</v>
+      </c>
+      <c r="F301" t="s">
+        <v>8</v>
+      </c>
+      <c r="G301" t="s">
+        <v>17</v>
+      </c>
+      <c r="H301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A302" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B302" t="s">
+        <v>648</v>
+      </c>
+      <c r="C302" t="s">
+        <v>649</v>
+      </c>
+      <c r="D302" t="s">
+        <v>6</v>
+      </c>
+      <c r="E302" t="s">
+        <v>29</v>
+      </c>
+      <c r="F302" t="s">
+        <v>8</v>
+      </c>
+      <c r="G302" t="s">
+        <v>19</v>
+      </c>
+      <c r="H302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A303" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B303" t="s">
+        <v>650</v>
+      </c>
+      <c r="C303" t="s">
+        <v>651</v>
+      </c>
+      <c r="D303" t="s">
+        <v>496</v>
+      </c>
+      <c r="E303" t="s">
+        <v>31</v>
+      </c>
+      <c r="F303" t="s">
+        <v>8</v>
+      </c>
+      <c r="G303" t="s">
+        <v>19</v>
+      </c>
+      <c r="H303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A304" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B304" t="s">
+        <v>652</v>
+      </c>
+      <c r="C304" t="s">
+        <v>653</v>
+      </c>
+      <c r="D304" t="s">
+        <v>42</v>
+      </c>
+      <c r="E304" t="s">
+        <v>29</v>
+      </c>
+      <c r="F304" t="s">
+        <v>8</v>
+      </c>
+      <c r="G304" t="s">
+        <v>17</v>
+      </c>
+      <c r="H304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A305" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B305" t="s">
+        <v>654</v>
+      </c>
+      <c r="C305" t="s">
+        <v>655</v>
+      </c>
+      <c r="D305" t="s">
+        <v>12</v>
+      </c>
+      <c r="E305" t="s">
+        <v>29</v>
+      </c>
+      <c r="F305" t="s">
+        <v>7</v>
+      </c>
+      <c r="G305" t="s">
+        <v>17</v>
+      </c>
+      <c r="H305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A306" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B306" t="s">
+        <v>656</v>
+      </c>
+      <c r="C306" t="s">
+        <v>657</v>
+      </c>
+      <c r="D306" t="s">
+        <v>27</v>
+      </c>
+      <c r="E306" t="s">
+        <v>31</v>
+      </c>
+      <c r="F306" t="s">
+        <v>7</v>
+      </c>
+      <c r="G306" t="s">
+        <v>17</v>
+      </c>
+      <c r="H306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A307" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B307" t="s">
+        <v>658</v>
+      </c>
+      <c r="C307" t="s">
+        <v>659</v>
+      </c>
+      <c r="D307" t="s">
+        <v>14</v>
+      </c>
+      <c r="E307" t="s">
+        <v>29</v>
+      </c>
+      <c r="F307" t="s">
+        <v>8</v>
+      </c>
+      <c r="G307" t="s">
+        <v>17</v>
+      </c>
+      <c r="H307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A308" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B308" t="s">
+        <v>660</v>
+      </c>
+      <c r="C308" t="s">
+        <v>661</v>
+      </c>
+      <c r="D308" t="s">
+        <v>26</v>
+      </c>
+      <c r="E308" t="s">
+        <v>29</v>
+      </c>
+      <c r="F308" t="s">
+        <v>8</v>
+      </c>
+      <c r="G308" t="s">
+        <v>17</v>
+      </c>
+      <c r="H308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A309" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B309" t="s">
+        <v>662</v>
+      </c>
+      <c r="C309" t="s">
+        <v>663</v>
+      </c>
+      <c r="D309" t="s">
+        <v>11</v>
+      </c>
+      <c r="E309" t="s">
+        <v>29</v>
+      </c>
+      <c r="F309" t="s">
+        <v>8</v>
+      </c>
+      <c r="G309" t="s">
+        <v>17</v>
+      </c>
+      <c r="H309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A310" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B310" t="s">
+        <v>664</v>
+      </c>
+      <c r="C310" t="s">
+        <v>665</v>
+      </c>
+      <c r="D310" t="s">
+        <v>13</v>
+      </c>
+      <c r="E310" t="s">
+        <v>29</v>
+      </c>
+      <c r="F310" t="s">
+        <v>8</v>
+      </c>
+      <c r="G310" t="s">
+        <v>17</v>
+      </c>
+      <c r="H310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A311" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B311" t="s">
+        <v>666</v>
+      </c>
+      <c r="C311" t="s">
+        <v>667</v>
+      </c>
+      <c r="D311" t="s">
+        <v>25</v>
+      </c>
+      <c r="E311" t="s">
+        <v>30</v>
+      </c>
+      <c r="F311" t="s">
+        <v>8</v>
+      </c>
+      <c r="G311" t="s">
+        <v>17</v>
+      </c>
+      <c r="H311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A312" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B312" t="s">
+        <v>668</v>
+      </c>
+      <c r="C312" t="s">
+        <v>669</v>
+      </c>
+      <c r="D312" t="s">
+        <v>27</v>
+      </c>
+      <c r="E312" t="s">
+        <v>31</v>
+      </c>
+      <c r="F312" t="s">
+        <v>7</v>
+      </c>
+      <c r="G312" t="s">
+        <v>17</v>
+      </c>
+      <c r="H312">
         <v>0</v>
       </c>
     </row>

--- a/first-atlas/producao_2026-05.xlsx
+++ b/first-atlas/producao_2026-05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E04CDD-23C0-4F5C-BD0B-B45418B403C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EB977C-B35E-42B4-8927-B0A0F2BD0856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13740" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2333" uniqueCount="819">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -2064,6 +2064,438 @@
   </si>
   <si>
     <t>Ata de eleicao da empresa , atualizado e registrada no orgao competente. Esse documento formaliza a eleicao e/ou nomeacao dos representantes legais e administradores, informando cargos, prazos de mandato e poderes de representacao, comprovando quem esta autorizado a agir em nome da entidade. A recepcionada nao esta te elegendo.&lt;br&gt;&lt;br&gt;Estatuto social atualizado e registrado no orgao competente</t>
+  </si>
+  <si>
+    <t>08686454000170</t>
+  </si>
+  <si>
+    <t>A SANTOS REPRESENTACOES E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>28699004000129</t>
+  </si>
+  <si>
+    <t>JRA AMERICANA TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>44588228000110</t>
+  </si>
+  <si>
+    <t>ROBERVAL DE LIMA SILVA</t>
+  </si>
+  <si>
+    <t>41142482000100</t>
+  </si>
+  <si>
+    <t>41.142.482 RODRIGO DE OLIVEIRA RIBEIRO</t>
+  </si>
+  <si>
+    <t>33470666000162</t>
+  </si>
+  <si>
+    <t>FABIANA PAULA LIMA DANTAS</t>
+  </si>
+  <si>
+    <t>44331988000147</t>
+  </si>
+  <si>
+    <t>PEDRO FELLIPE BRITO MIRANDA MENDES</t>
+  </si>
+  <si>
+    <t>50127340000156</t>
+  </si>
+  <si>
+    <t>GIGIANE ROSVANIA TORQUATO LTDA</t>
+  </si>
+  <si>
+    <t>52787529000109</t>
+  </si>
+  <si>
+    <t>VOZ NO PAPEL EDITORIAL LTDA</t>
+  </si>
+  <si>
+    <t>63119180000145</t>
+  </si>
+  <si>
+    <t>ECG EVENTOS LTDA</t>
+  </si>
+  <si>
+    <t>31474600000115</t>
+  </si>
+  <si>
+    <t>FERRARI LOG TRANSPORTES DE CARGA LTDA</t>
+  </si>
+  <si>
+    <t>24254368000144</t>
+  </si>
+  <si>
+    <t>ALEXANDRE MOZZER XAVIER</t>
+  </si>
+  <si>
+    <t>41996674000175</t>
+  </si>
+  <si>
+    <t>41.996.674 DIONATAN OLIVEIRA SACRAMENTO</t>
+  </si>
+  <si>
+    <t>39956006000172</t>
+  </si>
+  <si>
+    <t>ALEXANDRE CORREA SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+  </si>
+  <si>
+    <t>53594370000160</t>
+  </si>
+  <si>
+    <t>SAO PAULO CLUBE</t>
+  </si>
+  <si>
+    <t>36309290000105</t>
+  </si>
+  <si>
+    <t>36.309.290 ROBSON DE JESUS</t>
+  </si>
+  <si>
+    <t>63866486000165</t>
+  </si>
+  <si>
+    <t>BRUNO RAFACHINI SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+  </si>
+  <si>
+    <t>37380279000196</t>
+  </si>
+  <si>
+    <t>37.380.279 AILTON BERTO CORREIA</t>
+  </si>
+  <si>
+    <t>35458810000170</t>
+  </si>
+  <si>
+    <t>LEONARDO FERREIRA CARVALHO SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>48698751000150</t>
+  </si>
+  <si>
+    <t>48.698.751 MARICHEILA TAVARES BEZERRA</t>
+  </si>
+  <si>
+    <t>20212782000130</t>
+  </si>
+  <si>
+    <t>STUDIO LUCIANA DUARTE LTDA</t>
+  </si>
+  <si>
+    <t>62488018000131</t>
+  </si>
+  <si>
+    <t>MUNDO DAS RACOES LTDA</t>
+  </si>
+  <si>
+    <t>21059633000145</t>
+  </si>
+  <si>
+    <t>PAULO HENRIQUE SILVA COMERCIO &amp; CIA LTDA</t>
+  </si>
+  <si>
+    <t>59464795000131</t>
+  </si>
+  <si>
+    <t>JRP TRANSPORTE LTDA</t>
+  </si>
+  <si>
+    <t>58325117000125</t>
+  </si>
+  <si>
+    <t>PAZ E BARRETO EMPREENDIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>40452974000120</t>
+  </si>
+  <si>
+    <t>40.452.974 RICARDO HENRIQUE MASSOLA MULLER</t>
+  </si>
+  <si>
+    <t>57744941000157</t>
+  </si>
+  <si>
+    <t>DENIS FRANCISCO DE SOUZA</t>
+  </si>
+  <si>
+    <t>65623994000148</t>
+  </si>
+  <si>
+    <t>MINIMERCADO BURITI LTDA</t>
+  </si>
+  <si>
+    <t>65216564000101</t>
+  </si>
+  <si>
+    <t>HRT ENGENHARIA E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>30730889000123</t>
+  </si>
+  <si>
+    <t>DEMIVALDO ALEXANDRE BELAO E OUTRO</t>
+  </si>
+  <si>
+    <t>28222262000110</t>
+  </si>
+  <si>
+    <t>SOUSA ASSESSORIA &amp; CONSULTORIA DO TRABALHO LTDA</t>
+  </si>
+  <si>
+    <t>43527843000153</t>
+  </si>
+  <si>
+    <t>HARMONIZA AMBIENTES PLANEJADOS LTDA</t>
+  </si>
+  <si>
+    <t>30589197000107</t>
+  </si>
+  <si>
+    <t>P M L COMERCIO E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>48052673000111</t>
+  </si>
+  <si>
+    <t>CLINICA VETERINARIA CLUBE DOS BICHOS LTDA</t>
+  </si>
+  <si>
+    <t>54481500000111</t>
+  </si>
+  <si>
+    <t>MARCOS AMARAL AFONSO DE MORAES LTDA</t>
+  </si>
+  <si>
+    <t>16815038000152</t>
+  </si>
+  <si>
+    <t>JOGER ELETRICA E MECANICA LTDA</t>
+  </si>
+  <si>
+    <t>41939756000188</t>
+  </si>
+  <si>
+    <t>PROTEGE VISTORIA AUTOMOTIVA CEILANDIA LTDA</t>
+  </si>
+  <si>
+    <t>46728399000122</t>
+  </si>
+  <si>
+    <t>DENICE S.DOS SANTOS</t>
+  </si>
+  <si>
+    <t>62202000000121</t>
+  </si>
+  <si>
+    <t>MERCADO LIVIA LTDA</t>
+  </si>
+  <si>
+    <t>18499470000107</t>
+  </si>
+  <si>
+    <t>R C DA COSTA TERCEIRO - CONFECCOES</t>
+  </si>
+  <si>
+    <t>21859907000180</t>
+  </si>
+  <si>
+    <t>GLOBAL ASSISTENCIA ELETRONICA LTDA</t>
+  </si>
+  <si>
+    <t>41912101000116</t>
+  </si>
+  <si>
+    <t>E. DA ROCHA GUTIERRES</t>
+  </si>
+  <si>
+    <t>02093839000147</t>
+  </si>
+  <si>
+    <t>R A DE SOUZA LTDA</t>
+  </si>
+  <si>
+    <t>50676662000154</t>
+  </si>
+  <si>
+    <t>50.676.662 STALLIN JEAN BARBOSA</t>
+  </si>
+  <si>
+    <t>37925399000121</t>
+  </si>
+  <si>
+    <t>MARIA SOLEDADE DE SANTANA SANTOS</t>
+  </si>
+  <si>
+    <t>50648399000190</t>
+  </si>
+  <si>
+    <t>C F SERVICOS E CONSTRUCOES LTDA</t>
+  </si>
+  <si>
+    <t>22958849000105</t>
+  </si>
+  <si>
+    <t>LUIZ DA SILVA NASCIMENTO TRANSPORTE</t>
+  </si>
+  <si>
+    <t>24773006000160</t>
+  </si>
+  <si>
+    <t>HV SERVICOS DE DESPACHOS LTDA</t>
+  </si>
+  <si>
+    <t>53279953000105</t>
+  </si>
+  <si>
+    <t>J W DOS SANTOS JUNIOR SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>63489141000130</t>
+  </si>
+  <si>
+    <t>63.489.141 JOSE HUMBERG CARVALHO DA CRUZ</t>
+  </si>
+  <si>
+    <t>49686849000150</t>
+  </si>
+  <si>
+    <t>ALEXANDRE DE SOUZA PRO RETOQUE</t>
+  </si>
+  <si>
+    <t>23827225000111</t>
+  </si>
+  <si>
+    <t>NP4 TELECOM LTDA</t>
+  </si>
+  <si>
+    <t>44435746000101</t>
+  </si>
+  <si>
+    <t>44.435.746 ULISSES GOGLIANO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>07697015000108</t>
+  </si>
+  <si>
+    <t>J. RIBEIRO DE LIMA NETO PANIFICADORA LTDA</t>
+  </si>
+  <si>
+    <t>10434552000161</t>
+  </si>
+  <si>
+    <t>SOPHIA GAS LTDA</t>
+  </si>
+  <si>
+    <t>51913129000121</t>
+  </si>
+  <si>
+    <t>PONTA DO MUTA CHOPPERIA E SUSHI BAR LTDA</t>
+  </si>
+  <si>
+    <t>27707570000172</t>
+  </si>
+  <si>
+    <t>ARIANE ALVES DA SILVA</t>
+  </si>
+  <si>
+    <t>35700436000178</t>
+  </si>
+  <si>
+    <t>ANTONIO FLAVIO DE ARAUJO SOARES RESTAURANTE</t>
+  </si>
+  <si>
+    <t>62933215000112</t>
+  </si>
+  <si>
+    <t>AVILAGSENGE LTDA</t>
+  </si>
+  <si>
+    <t>48489396000109</t>
+  </si>
+  <si>
+    <t>MILTON PEREIRA PINTO</t>
+  </si>
+  <si>
+    <t>32431662000102</t>
+  </si>
+  <si>
+    <t>L.M AGRONEGOCIO LTDA</t>
+  </si>
+  <si>
+    <t>35812995000170</t>
+  </si>
+  <si>
+    <t>DOSVALDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>45569186000132</t>
+  </si>
+  <si>
+    <t>R. SENATORI MANUTENCAO E SERVICOS</t>
+  </si>
+  <si>
+    <t>27532208000108</t>
+  </si>
+  <si>
+    <t>EJ SERVICOS ELETRICOS LTDA</t>
+  </si>
+  <si>
+    <t>15507878000195</t>
+  </si>
+  <si>
+    <t>CLEYTON JOSE AZEVEDO CAMPOS</t>
+  </si>
+  <si>
+    <t>65126692000164</t>
+  </si>
+  <si>
+    <t>P. REGINA BATISTA LEITE LTDA</t>
+  </si>
+  <si>
+    <t>35639853000152</t>
+  </si>
+  <si>
+    <t>RODNEY LEONARDO DE CARVALHO OLIVEIRA</t>
+  </si>
+  <si>
+    <t>58857592000142</t>
+  </si>
+  <si>
+    <t>RO ESTETICA AVANCADA LTDA</t>
+  </si>
+  <si>
+    <t>08754125000119</t>
+  </si>
+  <si>
+    <t>ATHOS ATENDIMENTO HOLISTICO EM SAUDE LTDA</t>
+  </si>
+  <si>
+    <t>30145401000109</t>
+  </si>
+  <si>
+    <t>MINI MERCADO E PADARIA DO BRUNO LTDA</t>
+  </si>
+  <si>
+    <t>48234674000187</t>
+  </si>
+  <si>
+    <t>JOAO MARCOS DA SILVA</t>
+  </si>
+  <si>
+    <t>37086003000108</t>
+  </si>
+  <si>
+    <t>DANIELLE CRISTINE BERRUTTI DA SILVA</t>
+  </si>
+  <si>
+    <t>39257454000188</t>
+  </si>
+  <si>
+    <t>PATRIOTAS SOUVENIR LTDA</t>
   </si>
 </sst>
 </file>
@@ -2436,11 +2868,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:H312"/>
+  <dimension ref="A1:H385"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
     <col min="3" max="3" width="57.28515625" customWidth="1"/>
     <col min="4" max="4" width="32.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
@@ -2496,7 +2928,7 @@
         <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>444</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -2689,25 +3121,25 @@
         <v>46146</v>
       </c>
       <c r="B10" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H10" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2715,13 +3147,13 @@
         <v>46146</v>
       </c>
       <c r="B11" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C11" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
         <v>31</v>
@@ -2730,10 +3162,10 @@
         <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" t="s">
-        <v>37</v>
+        <v>444</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2741,25 +3173,25 @@
         <v>46146</v>
       </c>
       <c r="B12" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C12" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
         <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>444</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -2767,25 +3199,25 @@
         <v>46146</v>
       </c>
       <c r="B13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -2793,25 +3225,25 @@
         <v>46146</v>
       </c>
       <c r="B14" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C14" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H14" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -2819,25 +3251,25 @@
         <v>46146</v>
       </c>
       <c r="B15" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C15" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" t="s">
-        <v>674</v>
+        <v>18</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -2845,25 +3277,25 @@
         <v>46146</v>
       </c>
       <c r="B16" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C16" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -2871,25 +3303,25 @@
         <v>46146</v>
       </c>
       <c r="B17" t="s">
-        <v>453</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>454</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" t="s">
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -2897,13 +3329,13 @@
         <v>46146</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
@@ -2923,13 +3355,13 @@
         <v>46146</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
         <v>29</v>
@@ -2949,10 +3381,10 @@
         <v>46146</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
@@ -2975,10 +3407,10 @@
         <v>46146</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
@@ -3001,13 +3433,13 @@
         <v>46146</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
@@ -3027,13 +3459,13 @@
         <v>46146</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
@@ -3053,13 +3485,13 @@
         <v>46146</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E24" t="s">
         <v>29</v>
@@ -3079,16 +3511,16 @@
         <v>46146</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E25" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F25" t="s">
         <v>8</v>
@@ -3105,22 +3537,22 @@
         <v>46146</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F26" t="s">
         <v>8</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -3131,13 +3563,13 @@
         <v>46146</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E27" t="s">
         <v>29</v>
@@ -3146,7 +3578,7 @@
         <v>8</v>
       </c>
       <c r="G27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -3157,22 +3589,22 @@
         <v>46146</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E28" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -3183,13 +3615,13 @@
         <v>46146</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
         <v>31</v>
@@ -3198,7 +3630,7 @@
         <v>7</v>
       </c>
       <c r="G29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -3209,22 +3641,22 @@
         <v>46146</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G30" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -3235,13 +3667,13 @@
         <v>46146</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E31" t="s">
         <v>29</v>
@@ -3250,7 +3682,7 @@
         <v>8</v>
       </c>
       <c r="G31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -3261,13 +3693,13 @@
         <v>46146</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E32" t="s">
         <v>29</v>
@@ -3287,13 +3719,13 @@
         <v>46146</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
         <v>29</v>
@@ -3302,7 +3734,7 @@
         <v>8</v>
       </c>
       <c r="G33" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -3313,13 +3745,13 @@
         <v>46146</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
         <v>29</v>
@@ -3328,7 +3760,7 @@
         <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -3339,22 +3771,22 @@
         <v>46146</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E35" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -3365,19 +3797,19 @@
         <v>46146</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E36" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F36" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G36" t="s">
         <v>17</v>
@@ -3391,13 +3823,13 @@
         <v>46146</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E37" t="s">
         <v>29</v>
@@ -3417,19 +3849,19 @@
         <v>46146</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E38" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G38" t="s">
         <v>17</v>
@@ -3443,22 +3875,22 @@
         <v>46146</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D39" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F39" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G39" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -3469,13 +3901,13 @@
         <v>46146</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E40" t="s">
         <v>29</v>
@@ -3484,7 +3916,7 @@
         <v>8</v>
       </c>
       <c r="G40" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -3495,13 +3927,13 @@
         <v>46146</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E41" t="s">
         <v>29</v>
@@ -3510,7 +3942,7 @@
         <v>8</v>
       </c>
       <c r="G41" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -3521,22 +3953,22 @@
         <v>46146</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E42" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F42" t="s">
         <v>8</v>
       </c>
       <c r="G42" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -3547,16 +3979,16 @@
         <v>46146</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D43" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F43" t="s">
         <v>8</v>
@@ -3573,13 +4005,13 @@
         <v>46146</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E44" t="s">
         <v>29</v>
@@ -3599,19 +4031,19 @@
         <v>46146</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E45" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G45" t="s">
         <v>17</v>
@@ -3625,13 +4057,13 @@
         <v>46146</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C46" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D46" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
         <v>31</v>
@@ -3651,19 +4083,19 @@
         <v>46146</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C47" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D47" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F47" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G47" t="s">
         <v>17</v>
@@ -3677,13 +4109,13 @@
         <v>46146</v>
       </c>
       <c r="B48" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E48" t="s">
         <v>29</v>
@@ -3703,13 +4135,13 @@
         <v>46146</v>
       </c>
       <c r="B49" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C49" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D49" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E49" t="s">
         <v>29</v>
@@ -3729,13 +4161,13 @@
         <v>46146</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C50" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E50" t="s">
         <v>29</v>
@@ -3755,19 +4187,19 @@
         <v>46146</v>
       </c>
       <c r="B51" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C51" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="E51" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G51" t="s">
         <v>17</v>
@@ -3781,13 +4213,13 @@
         <v>46146</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C52" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D52" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E52" t="s">
         <v>31</v>
@@ -3807,25 +4239,25 @@
         <v>46146</v>
       </c>
       <c r="B53" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D53" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F53" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G53" t="s">
-        <v>17</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="H53" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -3833,13 +4265,13 @@
         <v>46146</v>
       </c>
       <c r="B54" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C54" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E54" t="s">
         <v>29</v>
@@ -3848,10 +4280,10 @@
         <v>8</v>
       </c>
       <c r="G54" t="s">
-        <v>18</v>
-      </c>
-      <c r="H54" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -3859,13 +4291,13 @@
         <v>46146</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C55" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E55" t="s">
         <v>29</v>
@@ -3885,10 +4317,10 @@
         <v>46146</v>
       </c>
       <c r="B56" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C56" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D56" t="s">
         <v>12</v>
@@ -3911,13 +4343,13 @@
         <v>46146</v>
       </c>
       <c r="B57" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C57" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D57" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E57" t="s">
         <v>29</v>
@@ -3937,13 +4369,13 @@
         <v>46146</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D58" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E58" t="s">
         <v>29</v>
@@ -3963,13 +4395,13 @@
         <v>46146</v>
       </c>
       <c r="B59" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C59" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D59" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E59" t="s">
         <v>29</v>
@@ -3978,7 +4410,7 @@
         <v>8</v>
       </c>
       <c r="G59" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -3989,22 +4421,22 @@
         <v>46146</v>
       </c>
       <c r="B60" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D60" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E60" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G60" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -4015,19 +4447,19 @@
         <v>46146</v>
       </c>
       <c r="B61" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C61" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D61" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F61" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G61" t="s">
         <v>17</v>
@@ -4041,19 +4473,19 @@
         <v>46146</v>
       </c>
       <c r="B62" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C62" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D62" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="E62" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F62" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G62" t="s">
         <v>17</v>
@@ -4067,22 +4499,22 @@
         <v>46146</v>
       </c>
       <c r="B63" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C63" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D63" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E63" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F63" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G63" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -4093,13 +4525,13 @@
         <v>46146</v>
       </c>
       <c r="B64" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C64" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D64" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E64" t="s">
         <v>29</v>
@@ -4108,7 +4540,7 @@
         <v>8</v>
       </c>
       <c r="G64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -4119,13 +4551,13 @@
         <v>46146</v>
       </c>
       <c r="B65" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C65" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D65" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E65" t="s">
         <v>29</v>
@@ -4145,13 +4577,13 @@
         <v>46146</v>
       </c>
       <c r="B66" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C66" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D66" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E66" t="s">
         <v>29</v>
@@ -4171,16 +4603,16 @@
         <v>46146</v>
       </c>
       <c r="B67" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C67" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D67" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="E67" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F67" t="s">
         <v>8</v>
@@ -4197,25 +4629,22 @@
         <v>46146</v>
       </c>
       <c r="B68" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C68" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D68" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E68" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F68" t="s">
         <v>8</v>
       </c>
       <c r="G68" t="s">
-        <v>17</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -4223,13 +4652,13 @@
         <v>46146</v>
       </c>
       <c r="B69" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C69" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D69" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E69" t="s">
         <v>29</v>
@@ -4238,7 +4667,10 @@
         <v>8</v>
       </c>
       <c r="G69" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -4246,13 +4678,13 @@
         <v>46146</v>
       </c>
       <c r="B70" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C70" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D70" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E70" t="s">
         <v>29</v>
@@ -4272,16 +4704,16 @@
         <v>46146</v>
       </c>
       <c r="B71" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C71" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E71" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F71" t="s">
         <v>8</v>
@@ -4298,22 +4730,22 @@
         <v>46146</v>
       </c>
       <c r="B72" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C72" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D72" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E72" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F72" t="s">
         <v>8</v>
       </c>
       <c r="G72" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -4324,13 +4756,13 @@
         <v>46146</v>
       </c>
       <c r="B73" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C73" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D73" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E73" t="s">
         <v>29</v>
@@ -4339,7 +4771,7 @@
         <v>8</v>
       </c>
       <c r="G73" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -4350,22 +4782,22 @@
         <v>46146</v>
       </c>
       <c r="B74" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C74" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D74" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E74" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G74" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -4376,19 +4808,19 @@
         <v>46146</v>
       </c>
       <c r="B75" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C75" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D75" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E75" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F75" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G75" t="s">
         <v>17</v>
@@ -4402,16 +4834,16 @@
         <v>46146</v>
       </c>
       <c r="B76" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C76" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D76" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E76" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F76" t="s">
         <v>8</v>
@@ -4428,16 +4860,16 @@
         <v>46146</v>
       </c>
       <c r="B77" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C77" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D77" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E77" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F77" t="s">
         <v>8</v>
@@ -4454,13 +4886,13 @@
         <v>46146</v>
       </c>
       <c r="B78" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C78" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D78" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E78" t="s">
         <v>29</v>
@@ -4480,22 +4912,22 @@
         <v>46146</v>
       </c>
       <c r="B79" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C79" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D79" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E79" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F79" t="s">
         <v>8</v>
       </c>
       <c r="G79" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -4506,13 +4938,13 @@
         <v>46146</v>
       </c>
       <c r="B80" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C80" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D80" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E80" t="s">
         <v>31</v>
@@ -4521,7 +4953,7 @@
         <v>8</v>
       </c>
       <c r="G80" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -4532,22 +4964,22 @@
         <v>46146</v>
       </c>
       <c r="B81" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C81" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D81" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E81" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F81" t="s">
         <v>8</v>
       </c>
       <c r="G81" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -4558,13 +4990,13 @@
         <v>46146</v>
       </c>
       <c r="B82" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C82" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D82" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E82" t="s">
         <v>29</v>
@@ -4584,13 +5016,13 @@
         <v>46146</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C83" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D83" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E83" t="s">
         <v>29</v>
@@ -4599,7 +5031,7 @@
         <v>8</v>
       </c>
       <c r="G83" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H83">
         <v>0</v>
@@ -4607,13 +5039,13 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B84" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C84" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D84" t="s">
         <v>12</v>
@@ -4625,7 +5057,7 @@
         <v>8</v>
       </c>
       <c r="G84" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -4636,13 +5068,13 @@
         <v>46147</v>
       </c>
       <c r="B85" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C85" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E85" t="s">
         <v>29</v>
@@ -4662,10 +5094,10 @@
         <v>46147</v>
       </c>
       <c r="B86" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C86" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D86" t="s">
         <v>11</v>
@@ -4688,19 +5120,19 @@
         <v>46147</v>
       </c>
       <c r="B87" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C87" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D87" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E87" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F87" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G87" t="s">
         <v>17</v>
@@ -4714,19 +5146,19 @@
         <v>46147</v>
       </c>
       <c r="B88" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C88" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D88" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E88" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F88" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G88" t="s">
         <v>17</v>
@@ -4740,19 +5172,19 @@
         <v>46147</v>
       </c>
       <c r="B89" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C89" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D89" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E89" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F89" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="G89" t="s">
         <v>17</v>
@@ -4766,10 +5198,10 @@
         <v>46147</v>
       </c>
       <c r="B90" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C90" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D90" t="s">
         <v>25</v>
@@ -4792,10 +5224,10 @@
         <v>46147</v>
       </c>
       <c r="B91" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C91" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D91" t="s">
         <v>25</v>
@@ -4818,22 +5250,22 @@
         <v>46147</v>
       </c>
       <c r="B92" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C92" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D92" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E92" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F92" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -4844,22 +5276,22 @@
         <v>46147</v>
       </c>
       <c r="B93" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C93" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D93" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E93" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F93" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G93" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -4870,10 +5302,10 @@
         <v>46147</v>
       </c>
       <c r="B94" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C94" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D94" t="s">
         <v>14</v>
@@ -4896,19 +5328,19 @@
         <v>46147</v>
       </c>
       <c r="B95" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C95" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D95" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E95" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F95" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G95" t="s">
         <v>17</v>
@@ -4922,19 +5354,19 @@
         <v>46147</v>
       </c>
       <c r="B96" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C96" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D96" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E96" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F96" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G96" t="s">
         <v>17</v>
@@ -4948,19 +5380,19 @@
         <v>46147</v>
       </c>
       <c r="B97" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C97" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D97" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E97" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F97" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G97" t="s">
         <v>17</v>
@@ -4974,19 +5406,19 @@
         <v>46147</v>
       </c>
       <c r="B98" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C98" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D98" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E98" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F98" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G98" t="s">
         <v>17</v>
@@ -5000,13 +5432,13 @@
         <v>46147</v>
       </c>
       <c r="B99" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C99" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D99" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E99" t="s">
         <v>29</v>
@@ -5015,7 +5447,7 @@
         <v>8</v>
       </c>
       <c r="G99" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -5026,13 +5458,13 @@
         <v>46147</v>
       </c>
       <c r="B100" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C100" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D100" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E100" t="s">
         <v>29</v>
@@ -5052,22 +5484,22 @@
         <v>46147</v>
       </c>
       <c r="B101" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C101" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D101" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E101" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F101" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G101" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -5078,13 +5510,13 @@
         <v>46147</v>
       </c>
       <c r="B102" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C102" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D102" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E102" t="s">
         <v>31</v>
@@ -5104,13 +5536,13 @@
         <v>46147</v>
       </c>
       <c r="B103" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C103" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D103" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E103" t="s">
         <v>31</v>
@@ -5130,19 +5562,19 @@
         <v>46147</v>
       </c>
       <c r="B104" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C104" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D104" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E104" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F104" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G104" t="s">
         <v>17</v>
@@ -5156,10 +5588,10 @@
         <v>46147</v>
       </c>
       <c r="B105" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C105" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D105" t="s">
         <v>11</v>
@@ -5171,7 +5603,7 @@
         <v>8</v>
       </c>
       <c r="G105" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -5182,10 +5614,10 @@
         <v>46147</v>
       </c>
       <c r="B106" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C106" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D106" t="s">
         <v>11</v>
@@ -5197,7 +5629,7 @@
         <v>8</v>
       </c>
       <c r="G106" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -5208,19 +5640,19 @@
         <v>46147</v>
       </c>
       <c r="B107" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C107" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D107" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E107" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F107" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G107" t="s">
         <v>17</v>
@@ -5234,19 +5666,19 @@
         <v>46147</v>
       </c>
       <c r="B108" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C108" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D108" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E108" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F108" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G108" t="s">
         <v>17</v>
@@ -5260,19 +5692,19 @@
         <v>46147</v>
       </c>
       <c r="B109" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C109" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D109" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E109" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F109" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G109" t="s">
         <v>17</v>
@@ -5286,13 +5718,13 @@
         <v>46147</v>
       </c>
       <c r="B110" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C110" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D110" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E110" t="s">
         <v>31</v>
@@ -5312,22 +5744,22 @@
         <v>46147</v>
       </c>
       <c r="B111" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C111" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D111" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F111" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G111" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H111">
         <v>0</v>
@@ -5338,25 +5770,25 @@
         <v>46147</v>
       </c>
       <c r="B112" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C112" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D112" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E112" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F112" t="s">
         <v>8</v>
       </c>
       <c r="G112" t="s">
-        <v>19</v>
-      </c>
-      <c r="H112">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H112" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -5364,25 +5796,25 @@
         <v>46147</v>
       </c>
       <c r="B113" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C113" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D113" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E113" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F113" t="s">
         <v>8</v>
       </c>
       <c r="G113" t="s">
-        <v>36</v>
-      </c>
-      <c r="H113" t="s">
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -5390,13 +5822,13 @@
         <v>46147</v>
       </c>
       <c r="B114" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C114" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D114" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E114" t="s">
         <v>29</v>
@@ -5416,16 +5848,16 @@
         <v>46147</v>
       </c>
       <c r="B115" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C115" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D115" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E115" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F115" t="s">
         <v>8</v>
@@ -5442,19 +5874,19 @@
         <v>46147</v>
       </c>
       <c r="B116" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C116" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D116" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E116" t="s">
         <v>31</v>
       </c>
       <c r="F116" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G116" t="s">
         <v>17</v>
@@ -5468,22 +5900,22 @@
         <v>46147</v>
       </c>
       <c r="B117" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C117" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D117" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E117" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F117" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G117" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H117">
         <v>0</v>
@@ -5494,22 +5926,22 @@
         <v>46147</v>
       </c>
       <c r="B118" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C118" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D118" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="E118" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F118" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G118" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H118">
         <v>0</v>
@@ -5520,22 +5952,22 @@
         <v>46147</v>
       </c>
       <c r="B119" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C119" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D119" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E119" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F119" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G119" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H119">
         <v>0</v>
@@ -5546,13 +5978,13 @@
         <v>46147</v>
       </c>
       <c r="B120" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C120" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D120" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E120" t="s">
         <v>29</v>
@@ -5572,13 +6004,13 @@
         <v>46147</v>
       </c>
       <c r="B121" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C121" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D121" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E121" t="s">
         <v>29</v>
@@ -5598,13 +6030,13 @@
         <v>46147</v>
       </c>
       <c r="B122" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C122" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D122" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E122" t="s">
         <v>29</v>
@@ -5613,10 +6045,10 @@
         <v>8</v>
       </c>
       <c r="G122" t="s">
-        <v>17</v>
-      </c>
-      <c r="H122">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H122" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -5624,25 +6056,25 @@
         <v>46147</v>
       </c>
       <c r="B123" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C123" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D123" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E123" t="s">
         <v>29</v>
       </c>
       <c r="F123" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G123" t="s">
-        <v>36</v>
-      </c>
-      <c r="H123" t="s">
-        <v>24</v>
+        <v>33</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -5650,22 +6082,22 @@
         <v>46147</v>
       </c>
       <c r="B124" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C124" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D124" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E124" t="s">
         <v>29</v>
       </c>
       <c r="F124" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G124" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H124">
         <v>0</v>
@@ -5676,13 +6108,13 @@
         <v>46147</v>
       </c>
       <c r="B125" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C125" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D125" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E125" t="s">
         <v>29</v>
@@ -5702,10 +6134,10 @@
         <v>46147</v>
       </c>
       <c r="B126" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C126" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
         <v>13</v>
@@ -5728,22 +6160,22 @@
         <v>46147</v>
       </c>
       <c r="B127" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D127" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E127" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F127" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G127" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H127">
         <v>0</v>
@@ -5754,22 +6186,22 @@
         <v>46147</v>
       </c>
       <c r="B128" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C128" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D128" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E128" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F128" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G128" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -5780,19 +6212,19 @@
         <v>46147</v>
       </c>
       <c r="B129" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C129" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D129" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E129" t="s">
         <v>29</v>
       </c>
       <c r="F129" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G129" t="s">
         <v>33</v>
@@ -5806,22 +6238,22 @@
         <v>46147</v>
       </c>
       <c r="B130" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C130" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D130" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F130" t="s">
         <v>7</v>
       </c>
       <c r="G130" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H130">
         <v>0</v>
@@ -5832,13 +6264,13 @@
         <v>46147</v>
       </c>
       <c r="B131" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C131" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D131" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E131" t="s">
         <v>31</v>
@@ -5858,13 +6290,13 @@
         <v>46147</v>
       </c>
       <c r="B132" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C132" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D132" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E132" t="s">
         <v>31</v>
@@ -5884,19 +6316,19 @@
         <v>46147</v>
       </c>
       <c r="B133" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C133" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D133" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E133" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F133" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G133" t="s">
         <v>17</v>
@@ -5910,10 +6342,10 @@
         <v>46147</v>
       </c>
       <c r="B134" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C134" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D134" t="s">
         <v>11</v>
@@ -5936,22 +6368,22 @@
         <v>46147</v>
       </c>
       <c r="B135" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C135" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D135" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E135" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F135" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G135" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -5962,13 +6394,13 @@
         <v>46147</v>
       </c>
       <c r="B136" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C136" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D136" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E136" t="s">
         <v>31</v>
@@ -5978,9 +6410,6 @@
       </c>
       <c r="G136" t="s">
         <v>19</v>
-      </c>
-      <c r="H136">
-        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -5988,22 +6417,22 @@
         <v>46147</v>
       </c>
       <c r="B137" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C137" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D137" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E137" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F137" t="s">
         <v>7</v>
       </c>
       <c r="G137" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -6014,13 +6443,13 @@
         <v>46147</v>
       </c>
       <c r="B138" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C138" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D138" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E138" t="s">
         <v>31</v>
@@ -6029,7 +6458,10 @@
         <v>7</v>
       </c>
       <c r="G138" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -6037,19 +6469,19 @@
         <v>46147</v>
       </c>
       <c r="B139" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C139" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D139" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="E139" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F139" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G139" t="s">
         <v>17</v>
@@ -6063,19 +6495,19 @@
         <v>46147</v>
       </c>
       <c r="B140" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C140" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D140" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E140" t="s">
         <v>31</v>
       </c>
       <c r="F140" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G140" t="s">
         <v>17</v>
@@ -6089,22 +6521,22 @@
         <v>46147</v>
       </c>
       <c r="B141" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C141" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D141" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E141" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F141" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G141" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H141">
         <v>0</v>
@@ -6115,22 +6547,22 @@
         <v>46147</v>
       </c>
       <c r="B142" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C142" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D142" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E142" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F142" t="s">
         <v>8</v>
       </c>
       <c r="G142" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -6141,22 +6573,22 @@
         <v>46147</v>
       </c>
       <c r="B143" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C143" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D143" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E143" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F143" t="s">
         <v>7</v>
       </c>
       <c r="G143" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -6167,22 +6599,22 @@
         <v>46147</v>
       </c>
       <c r="B144" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C144" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D144" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E144" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F144" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G144" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H144">
         <v>0</v>
@@ -6193,19 +6625,19 @@
         <v>46147</v>
       </c>
       <c r="B145" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C145" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D145" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E145" t="s">
         <v>29</v>
       </c>
       <c r="F145" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G145" t="s">
         <v>17</v>
@@ -6219,22 +6651,22 @@
         <v>46147</v>
       </c>
       <c r="B146" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C146" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D146" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E146" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F146" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G146" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -6245,13 +6677,13 @@
         <v>46147</v>
       </c>
       <c r="B147" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C147" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D147" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E147" t="s">
         <v>29</v>
@@ -6260,7 +6692,7 @@
         <v>8</v>
       </c>
       <c r="G147" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -6271,13 +6703,13 @@
         <v>46147</v>
       </c>
       <c r="B148" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C148" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D148" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E148" t="s">
         <v>29</v>
@@ -6286,7 +6718,7 @@
         <v>8</v>
       </c>
       <c r="G148" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -6297,10 +6729,10 @@
         <v>46147</v>
       </c>
       <c r="B149" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C149" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D149" t="s">
         <v>6</v>
@@ -6320,22 +6752,22 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B150" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C150" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D150" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E150" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F150" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G150" t="s">
         <v>17</v>
@@ -6346,16 +6778,16 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B151" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C151" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D151" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E151" t="s">
         <v>29</v>
@@ -6364,7 +6796,7 @@
         <v>8</v>
       </c>
       <c r="G151" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -6375,10 +6807,10 @@
         <v>46148</v>
       </c>
       <c r="B152" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C152" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D152" t="s">
         <v>12</v>
@@ -6387,7 +6819,7 @@
         <v>31</v>
       </c>
       <c r="F152" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G152" t="s">
         <v>17</v>
@@ -6401,19 +6833,19 @@
         <v>46148</v>
       </c>
       <c r="B153" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C153" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D153" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E153" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F153" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G153" t="s">
         <v>17</v>
@@ -6427,10 +6859,10 @@
         <v>46148</v>
       </c>
       <c r="B154" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C154" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D154" t="s">
         <v>12</v>
@@ -6439,7 +6871,7 @@
         <v>31</v>
       </c>
       <c r="F154" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G154" t="s">
         <v>17</v>
@@ -6453,19 +6885,19 @@
         <v>46148</v>
       </c>
       <c r="B155" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C155" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D155" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E155" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F155" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G155" t="s">
         <v>17</v>
@@ -6479,16 +6911,16 @@
         <v>46148</v>
       </c>
       <c r="B156" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C156" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="D156" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E156" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F156" t="s">
         <v>7</v>
@@ -6505,25 +6937,25 @@
         <v>46148</v>
       </c>
       <c r="B157" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C157" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D157" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F157" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G157" t="s">
-        <v>17</v>
-      </c>
-      <c r="H157">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H157" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -6531,16 +6963,16 @@
         <v>46148</v>
       </c>
       <c r="B158" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C158" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D158" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E158" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F158" t="s">
         <v>7</v>
@@ -6557,25 +6989,25 @@
         <v>46148</v>
       </c>
       <c r="B159" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C159" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D159" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E159" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F159" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G159" t="s">
-        <v>36</v>
-      </c>
-      <c r="H159" t="s">
-        <v>421</v>
+        <v>19</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -6583,25 +7015,22 @@
         <v>46148</v>
       </c>
       <c r="B160" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C160" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D160" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E160" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F160" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G160" t="s">
-        <v>17</v>
-      </c>
-      <c r="H160">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -6609,13 +7038,13 @@
         <v>46148</v>
       </c>
       <c r="B161" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C161" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D161" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E161" t="s">
         <v>29</v>
@@ -6635,10 +7064,10 @@
         <v>46148</v>
       </c>
       <c r="B162" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C162" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="D162" t="s">
         <v>42</v>
@@ -6650,7 +7079,10 @@
         <v>8</v>
       </c>
       <c r="G162" t="s">
-        <v>334</v>
+        <v>33</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -6658,19 +7090,19 @@
         <v>46148</v>
       </c>
       <c r="B163" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C163" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D163" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E163" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F163" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G163" t="s">
         <v>19</v>
@@ -6684,13 +7116,13 @@
         <v>46148</v>
       </c>
       <c r="B164" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C164" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D164" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E164" t="s">
         <v>29</v>
@@ -6699,7 +7131,7 @@
         <v>8</v>
       </c>
       <c r="G164" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H164">
         <v>0</v>
@@ -6710,22 +7142,22 @@
         <v>46148</v>
       </c>
       <c r="B165" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C165" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D165" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E165" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F165" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G165" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H165">
         <v>0</v>
@@ -6736,13 +7168,13 @@
         <v>46148</v>
       </c>
       <c r="B166" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C166" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D166" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E166" t="s">
         <v>29</v>
@@ -6762,13 +7194,13 @@
         <v>46148</v>
       </c>
       <c r="B167" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C167" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D167" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E167" t="s">
         <v>29</v>
@@ -6788,13 +7220,13 @@
         <v>46148</v>
       </c>
       <c r="B168" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C168" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D168" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="E168" t="s">
         <v>29</v>
@@ -6814,19 +7246,19 @@
         <v>46148</v>
       </c>
       <c r="B169" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C169" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D169" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E169" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F169" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="G169" t="s">
         <v>17</v>
@@ -6840,19 +7272,19 @@
         <v>46148</v>
       </c>
       <c r="B170" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C170" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D170" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E170" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F170" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G170" t="s">
         <v>17</v>
@@ -6866,22 +7298,22 @@
         <v>46148</v>
       </c>
       <c r="B171" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C171" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D171" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E171" t="s">
         <v>31</v>
       </c>
       <c r="F171" t="s">
-        <v>323</v>
+        <v>7</v>
       </c>
       <c r="G171" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H171">
         <v>0</v>
@@ -6892,13 +7324,13 @@
         <v>46148</v>
       </c>
       <c r="B172" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C172" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D172" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="E172" t="s">
         <v>31</v>
@@ -6907,7 +7339,7 @@
         <v>7</v>
       </c>
       <c r="G172" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H172">
         <v>0</v>
@@ -6918,22 +7350,22 @@
         <v>46148</v>
       </c>
       <c r="B173" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C173" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D173" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E173" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F173" t="s">
         <v>7</v>
       </c>
       <c r="G173" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -6944,22 +7376,22 @@
         <v>46148</v>
       </c>
       <c r="B174" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C174" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D174" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E174" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F174" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G174" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H174">
         <v>0</v>
@@ -6970,16 +7402,16 @@
         <v>46148</v>
       </c>
       <c r="B175" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C175" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D175" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="E175" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F175" t="s">
         <v>7</v>
@@ -6996,13 +7428,13 @@
         <v>46148</v>
       </c>
       <c r="B176" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C176" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D176" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E176" t="s">
         <v>29</v>
@@ -7011,7 +7443,7 @@
         <v>8</v>
       </c>
       <c r="G176" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H176">
         <v>0</v>
@@ -7022,22 +7454,22 @@
         <v>46148</v>
       </c>
       <c r="B177" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C177" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D177" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E177" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F177" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G177" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H177">
         <v>0</v>
@@ -7048,13 +7480,13 @@
         <v>46148</v>
       </c>
       <c r="B178" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C178" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D178" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E178" t="s">
         <v>29</v>
@@ -7063,7 +7495,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H178">
         <v>0</v>
@@ -7074,13 +7506,13 @@
         <v>46148</v>
       </c>
       <c r="B179" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C179" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D179" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E179" t="s">
         <v>29</v>
@@ -7089,7 +7521,7 @@
         <v>8</v>
       </c>
       <c r="G179" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H179">
         <v>0</v>
@@ -7100,19 +7532,19 @@
         <v>46148</v>
       </c>
       <c r="B180" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C180" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D180" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E180" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F180" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G180" t="s">
         <v>17</v>
@@ -7126,13 +7558,13 @@
         <v>46148</v>
       </c>
       <c r="B181" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C181" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D181" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E181" t="s">
         <v>29</v>
@@ -7141,7 +7573,7 @@
         <v>8</v>
       </c>
       <c r="G181" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H181">
         <v>0</v>
@@ -7152,22 +7584,22 @@
         <v>46148</v>
       </c>
       <c r="B182" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C182" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D182" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E182" t="s">
         <v>31</v>
       </c>
       <c r="F182" t="s">
-        <v>7</v>
+        <v>323</v>
       </c>
       <c r="G182" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H182">
         <v>0</v>
@@ -7178,13 +7610,13 @@
         <v>46148</v>
       </c>
       <c r="B183" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C183" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D183" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E183" t="s">
         <v>29</v>
@@ -7193,7 +7625,7 @@
         <v>8</v>
       </c>
       <c r="G183" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H183">
         <v>0</v>
@@ -7204,22 +7636,22 @@
         <v>46148</v>
       </c>
       <c r="B184" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C184" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D184" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E184" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F184" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="G184" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H184">
         <v>0</v>
@@ -7230,25 +7662,25 @@
         <v>46148</v>
       </c>
       <c r="B185" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C185" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D185" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E185" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F185" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="G185" t="s">
-        <v>17</v>
-      </c>
-      <c r="H185">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H185" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -7256,22 +7688,22 @@
         <v>46148</v>
       </c>
       <c r="B186" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C186" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D186" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E186" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F186" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G186" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H186">
         <v>0</v>
@@ -7282,25 +7714,25 @@
         <v>46148</v>
       </c>
       <c r="B187" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C187" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D187" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E187" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F187" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="G187" t="s">
-        <v>36</v>
-      </c>
-      <c r="H187" t="s">
-        <v>37</v>
+        <v>33</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -7308,19 +7740,19 @@
         <v>46148</v>
       </c>
       <c r="B188" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C188" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D188" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E188" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F188" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G188" t="s">
         <v>19</v>
@@ -7334,13 +7766,13 @@
         <v>46148</v>
       </c>
       <c r="B189" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C189" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D189" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E189" t="s">
         <v>29</v>
@@ -7349,7 +7781,7 @@
         <v>8</v>
       </c>
       <c r="G189" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H189">
         <v>0</v>
@@ -7360,10 +7792,10 @@
         <v>46148</v>
       </c>
       <c r="B190" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C190" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D190" t="s">
         <v>14</v>
@@ -7375,7 +7807,7 @@
         <v>8</v>
       </c>
       <c r="G190" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -7386,13 +7818,13 @@
         <v>46148</v>
       </c>
       <c r="B191" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C191" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D191" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E191" t="s">
         <v>29</v>
@@ -7412,22 +7844,22 @@
         <v>46148</v>
       </c>
       <c r="B192" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C192" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D192" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E192" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F192" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G192" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H192">
         <v>0</v>
@@ -7438,13 +7870,13 @@
         <v>46148</v>
       </c>
       <c r="B193" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C193" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D193" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="E193" t="s">
         <v>29</v>
@@ -7453,10 +7885,7 @@
         <v>8</v>
       </c>
       <c r="G193" t="s">
-        <v>17</v>
-      </c>
-      <c r="H193">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -7464,13 +7893,13 @@
         <v>46148</v>
       </c>
       <c r="B194" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C194" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D194" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E194" t="s">
         <v>31</v>
@@ -7479,7 +7908,7 @@
         <v>7</v>
       </c>
       <c r="G194" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H194">
         <v>0</v>
@@ -7490,10 +7919,10 @@
         <v>46148</v>
       </c>
       <c r="B195" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C195" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D195" t="s">
         <v>42</v>
@@ -7505,7 +7934,10 @@
         <v>8</v>
       </c>
       <c r="G195" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="H195">
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
@@ -7513,13 +7945,13 @@
         <v>46148</v>
       </c>
       <c r="B196" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C196" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D196" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E196" t="s">
         <v>31</v>
@@ -7528,7 +7960,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H196">
         <v>0</v>
@@ -7539,13 +7971,13 @@
         <v>46148</v>
       </c>
       <c r="B197" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C197" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D197" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E197" t="s">
         <v>29</v>
@@ -7565,10 +7997,10 @@
         <v>46148</v>
       </c>
       <c r="B198" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C198" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D198" t="s">
         <v>23</v>
@@ -7591,13 +8023,13 @@
         <v>46148</v>
       </c>
       <c r="B199" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C199" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D199" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E199" t="s">
         <v>29</v>
@@ -7617,19 +8049,19 @@
         <v>46148</v>
       </c>
       <c r="B200" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C200" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D200" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E200" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F200" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G200" t="s">
         <v>17</v>
@@ -7640,22 +8072,22 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B201" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C201" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D201" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E201" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F201" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G201" t="s">
         <v>17</v>
@@ -7666,16 +8098,16 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B202" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C202" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D202" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E202" t="s">
         <v>29</v>
@@ -7695,19 +8127,19 @@
         <v>46149</v>
       </c>
       <c r="B203" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C203" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D203" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E203" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F203" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G203" t="s">
         <v>17</v>
@@ -7721,19 +8153,19 @@
         <v>46149</v>
       </c>
       <c r="B204" t="s">
-        <v>417</v>
+        <v>455</v>
       </c>
       <c r="C204" t="s">
-        <v>418</v>
+        <v>456</v>
       </c>
       <c r="D204" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E204" t="s">
         <v>29</v>
       </c>
       <c r="F204" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G204" t="s">
         <v>17</v>
@@ -7747,13 +8179,13 @@
         <v>46149</v>
       </c>
       <c r="B205" t="s">
-        <v>419</v>
+        <v>457</v>
       </c>
       <c r="C205" t="s">
-        <v>420</v>
+        <v>458</v>
       </c>
       <c r="D205" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E205" t="s">
         <v>29</v>
@@ -7773,22 +8205,22 @@
         <v>46149</v>
       </c>
       <c r="B206" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C206" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D206" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E206" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F206" t="s">
-        <v>7</v>
+        <v>461</v>
       </c>
       <c r="G206" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H206">
         <v>0</v>
@@ -7799,13 +8231,13 @@
         <v>46149</v>
       </c>
       <c r="B207" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C207" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D207" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E207" t="s">
         <v>29</v>
@@ -7814,10 +8246,10 @@
         <v>8</v>
       </c>
       <c r="G207" t="s">
-        <v>17</v>
-      </c>
-      <c r="H207">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="H207" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
@@ -7825,22 +8257,22 @@
         <v>46149</v>
       </c>
       <c r="B208" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C208" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="D208" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E208" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F208" t="s">
-        <v>461</v>
+        <v>8</v>
       </c>
       <c r="G208" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H208">
         <v>0</v>
@@ -7851,13 +8283,13 @@
         <v>46149</v>
       </c>
       <c r="B209" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C209" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D209" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E209" t="s">
         <v>29</v>
@@ -7866,10 +8298,10 @@
         <v>8</v>
       </c>
       <c r="G209" t="s">
-        <v>18</v>
-      </c>
-      <c r="H209" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="H209">
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
@@ -7877,13 +8309,13 @@
         <v>46149</v>
       </c>
       <c r="B210" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C210" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D210" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E210" t="s">
         <v>29</v>
@@ -7892,7 +8324,7 @@
         <v>8</v>
       </c>
       <c r="G210" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H210">
         <v>0</v>
@@ -7903,13 +8335,13 @@
         <v>46149</v>
       </c>
       <c r="B211" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C211" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D211" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E211" t="s">
         <v>29</v>
@@ -7929,13 +8361,13 @@
         <v>46149</v>
       </c>
       <c r="B212" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C212" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D212" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E212" t="s">
         <v>29</v>
@@ -7955,13 +8387,13 @@
         <v>46149</v>
       </c>
       <c r="B213" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C213" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D213" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E213" t="s">
         <v>29</v>
@@ -7981,13 +8413,13 @@
         <v>46149</v>
       </c>
       <c r="B214" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C214" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D214" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E214" t="s">
         <v>29</v>
@@ -8007,13 +8439,13 @@
         <v>46149</v>
       </c>
       <c r="B215" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C215" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D215" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E215" t="s">
         <v>29</v>
@@ -8022,7 +8454,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H215">
         <v>0</v>
@@ -8033,19 +8465,19 @@
         <v>46149</v>
       </c>
       <c r="B216" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C216" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="D216" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E216" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F216" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G216" t="s">
         <v>17</v>
@@ -8059,19 +8491,19 @@
         <v>46149</v>
       </c>
       <c r="B217" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="D217" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E217" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F217" t="s">
-        <v>8</v>
+        <v>461</v>
       </c>
       <c r="G217" t="s">
         <v>19</v>
@@ -8085,19 +8517,19 @@
         <v>46149</v>
       </c>
       <c r="B218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C218" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D218" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="E218" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F218" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G218" t="s">
         <v>17</v>
@@ -8111,22 +8543,22 @@
         <v>46149</v>
       </c>
       <c r="B219" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C219" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D219" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E219" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F219" t="s">
-        <v>461</v>
+        <v>7</v>
       </c>
       <c r="G219" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H219">
         <v>0</v>
@@ -8137,13 +8569,13 @@
         <v>46149</v>
       </c>
       <c r="B220" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C220" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D220" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E220" t="s">
         <v>29</v>
@@ -8152,10 +8584,7 @@
         <v>8</v>
       </c>
       <c r="G220" t="s">
-        <v>17</v>
-      </c>
-      <c r="H220">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
@@ -8163,19 +8592,19 @@
         <v>46149</v>
       </c>
       <c r="B221" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C221" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D221" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E221" t="s">
         <v>29</v>
       </c>
       <c r="F221" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G221" t="s">
         <v>17</v>
@@ -8189,22 +8618,25 @@
         <v>46149</v>
       </c>
       <c r="B222" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C222" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="D222" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E222" t="s">
         <v>29</v>
       </c>
       <c r="F222" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G222" t="s">
-        <v>334</v>
+        <v>17</v>
+      </c>
+      <c r="H222">
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
@@ -8212,22 +8644,22 @@
         <v>46149</v>
       </c>
       <c r="B223" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C223" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D223" t="s">
-        <v>15</v>
+        <v>496</v>
       </c>
       <c r="E223" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F223" t="s">
         <v>8</v>
       </c>
       <c r="G223" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H223">
         <v>0</v>
@@ -8238,19 +8670,19 @@
         <v>46149</v>
       </c>
       <c r="B224" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C224" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D224" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E224" t="s">
         <v>29</v>
       </c>
       <c r="F224" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G224" t="s">
         <v>17</v>
@@ -8264,22 +8696,22 @@
         <v>46149</v>
       </c>
       <c r="B225" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C225" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="D225" t="s">
-        <v>496</v>
+        <v>21</v>
       </c>
       <c r="E225" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F225" t="s">
         <v>8</v>
       </c>
       <c r="G225" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H225">
         <v>0</v>
@@ -8290,22 +8722,22 @@
         <v>46149</v>
       </c>
       <c r="B226" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C226" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D226" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E226" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F226" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G226" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H226">
         <v>0</v>
@@ -8316,13 +8748,13 @@
         <v>46149</v>
       </c>
       <c r="B227" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C227" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D227" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E227" t="s">
         <v>29</v>
@@ -8342,22 +8774,22 @@
         <v>46149</v>
       </c>
       <c r="B228" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C228" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D228" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E228" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F228" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G228" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H228">
         <v>0</v>
@@ -8368,13 +8800,13 @@
         <v>46149</v>
       </c>
       <c r="B229" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C229" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D229" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E229" t="s">
         <v>29</v>
@@ -8394,13 +8826,13 @@
         <v>46149</v>
       </c>
       <c r="B230" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C230" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="D230" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E230" t="s">
         <v>29</v>
@@ -8420,10 +8852,10 @@
         <v>46149</v>
       </c>
       <c r="B231" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C231" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D231" t="s">
         <v>21</v>
@@ -8446,19 +8878,19 @@
         <v>46149</v>
       </c>
       <c r="B232" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C232" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D232" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E232" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F232" t="s">
-        <v>8</v>
+        <v>461</v>
       </c>
       <c r="G232" t="s">
         <v>17</v>
@@ -8472,19 +8904,19 @@
         <v>46149</v>
       </c>
       <c r="B233" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C233" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="D233" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E233" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F233" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G233" t="s">
         <v>17</v>
@@ -8498,19 +8930,19 @@
         <v>46149</v>
       </c>
       <c r="B234" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C234" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D234" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E234" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F234" t="s">
-        <v>461</v>
+        <v>8</v>
       </c>
       <c r="G234" t="s">
         <v>17</v>
@@ -8524,10 +8956,10 @@
         <v>46149</v>
       </c>
       <c r="B235" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C235" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D235" t="s">
         <v>35</v>
@@ -8536,7 +8968,7 @@
         <v>31</v>
       </c>
       <c r="F235" t="s">
-        <v>7</v>
+        <v>521</v>
       </c>
       <c r="G235" t="s">
         <v>17</v>
@@ -8550,13 +8982,13 @@
         <v>46149</v>
       </c>
       <c r="B236" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C236" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="D236" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E236" t="s">
         <v>29</v>
@@ -8576,19 +9008,19 @@
         <v>46149</v>
       </c>
       <c r="B237" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C237" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="D237" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E237" t="s">
         <v>31</v>
       </c>
       <c r="F237" t="s">
-        <v>521</v>
+        <v>7</v>
       </c>
       <c r="G237" t="s">
         <v>17</v>
@@ -8602,22 +9034,22 @@
         <v>46149</v>
       </c>
       <c r="B238" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C238" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D238" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E238" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F238" t="s">
-        <v>8</v>
+        <v>461</v>
       </c>
       <c r="G238" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H238">
         <v>0</v>
@@ -8628,13 +9060,13 @@
         <v>46149</v>
       </c>
       <c r="B239" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C239" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D239" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E239" t="s">
         <v>31</v>
@@ -8643,7 +9075,7 @@
         <v>7</v>
       </c>
       <c r="G239" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H239">
         <v>0</v>
@@ -8654,19 +9086,19 @@
         <v>46149</v>
       </c>
       <c r="B240" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C240" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="D240" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E240" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F240" t="s">
-        <v>461</v>
+        <v>8</v>
       </c>
       <c r="G240" t="s">
         <v>19</v>
@@ -8680,10 +9112,10 @@
         <v>46149</v>
       </c>
       <c r="B241" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C241" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D241" t="s">
         <v>38</v>
@@ -8695,7 +9127,7 @@
         <v>7</v>
       </c>
       <c r="G241" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H241">
         <v>0</v>
@@ -8706,13 +9138,13 @@
         <v>46149</v>
       </c>
       <c r="B242" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C242" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="D242" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E242" t="s">
         <v>29</v>
@@ -8721,7 +9153,7 @@
         <v>8</v>
       </c>
       <c r="G242" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H242">
         <v>0</v>
@@ -8732,13 +9164,13 @@
         <v>46149</v>
       </c>
       <c r="B243" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C243" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D243" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="E243" t="s">
         <v>31</v>
@@ -8747,7 +9179,7 @@
         <v>7</v>
       </c>
       <c r="G243" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H243">
         <v>0</v>
@@ -8758,19 +9190,19 @@
         <v>46149</v>
       </c>
       <c r="B244" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C244" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D244" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E244" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F244" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G244" t="s">
         <v>17</v>
@@ -8784,13 +9216,13 @@
         <v>46149</v>
       </c>
       <c r="B245" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C245" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D245" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E245" t="s">
         <v>31</v>
@@ -8799,7 +9231,7 @@
         <v>7</v>
       </c>
       <c r="G245" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H245">
         <v>0</v>
@@ -8810,19 +9242,19 @@
         <v>46149</v>
       </c>
       <c r="B246" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C246" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D246" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E246" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F246" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G246" t="s">
         <v>17</v>
@@ -8836,22 +9268,22 @@
         <v>46149</v>
       </c>
       <c r="B247" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C247" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D247" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E247" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F247" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G247" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H247">
         <v>0</v>
@@ -8862,13 +9294,13 @@
         <v>46149</v>
       </c>
       <c r="B248" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C248" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D248" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E248" t="s">
         <v>29</v>
@@ -8888,13 +9320,13 @@
         <v>46149</v>
       </c>
       <c r="B249" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C249" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D249" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E249" t="s">
         <v>29</v>
@@ -8903,7 +9335,7 @@
         <v>8</v>
       </c>
       <c r="G249" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H249">
         <v>0</v>
@@ -8914,13 +9346,13 @@
         <v>46149</v>
       </c>
       <c r="B250" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C250" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D250" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E250" t="s">
         <v>29</v>
@@ -8929,7 +9361,7 @@
         <v>8</v>
       </c>
       <c r="G250" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H250">
         <v>0</v>
@@ -8940,13 +9372,13 @@
         <v>46149</v>
       </c>
       <c r="B251" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C251" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D251" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E251" t="s">
         <v>29</v>
@@ -8963,16 +9395,16 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B252" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C252" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D252" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E252" t="s">
         <v>29</v>
@@ -8981,7 +9413,7 @@
         <v>8</v>
       </c>
       <c r="G252" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H252">
         <v>0</v>
@@ -8989,22 +9421,22 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B253" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C253" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D253" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E253" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F253" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G253" t="s">
         <v>17</v>
@@ -9018,19 +9450,19 @@
         <v>46150</v>
       </c>
       <c r="B254" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C254" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D254" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E254" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F254" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="G254" t="s">
         <v>17</v>
@@ -9044,19 +9476,19 @@
         <v>46150</v>
       </c>
       <c r="B255" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C255" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D255" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E255" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F255" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="G255" t="s">
         <v>17</v>
@@ -9070,19 +9502,19 @@
         <v>46150</v>
       </c>
       <c r="B256" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C256" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="D256" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E256" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F256" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G256" t="s">
         <v>17</v>
@@ -9096,22 +9528,22 @@
         <v>46150</v>
       </c>
       <c r="B257" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C257" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D257" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E257" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F257" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G257" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H257">
         <v>0</v>
@@ -9122,22 +9554,22 @@
         <v>46150</v>
       </c>
       <c r="B258" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C258" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D258" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E258" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F258" t="s">
         <v>7</v>
       </c>
       <c r="G258" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H258">
         <v>0</v>
@@ -9148,22 +9580,22 @@
         <v>46150</v>
       </c>
       <c r="B259" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C259" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D259" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E259" t="s">
         <v>29</v>
       </c>
       <c r="F259" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G259" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H259">
         <v>0</v>
@@ -9174,22 +9606,22 @@
         <v>46150</v>
       </c>
       <c r="B260" t="s">
-        <v>566</v>
+        <v>225</v>
       </c>
       <c r="C260" t="s">
-        <v>567</v>
+        <v>226</v>
       </c>
       <c r="D260" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E260" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F260" t="s">
         <v>7</v>
       </c>
       <c r="G260" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H260">
         <v>0</v>
@@ -9200,13 +9632,13 @@
         <v>46150</v>
       </c>
       <c r="B261" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C261" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D261" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E261" t="s">
         <v>29</v>
@@ -9215,10 +9647,7 @@
         <v>8</v>
       </c>
       <c r="G261" t="s">
-        <v>17</v>
-      </c>
-      <c r="H261">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
@@ -9226,13 +9655,13 @@
         <v>46150</v>
       </c>
       <c r="B262" t="s">
-        <v>225</v>
+        <v>572</v>
       </c>
       <c r="C262" t="s">
-        <v>226</v>
+        <v>573</v>
       </c>
       <c r="D262" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E262" t="s">
         <v>31</v>
@@ -9252,13 +9681,13 @@
         <v>46150</v>
       </c>
       <c r="B263" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C263" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="D263" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E263" t="s">
         <v>29</v>
@@ -9267,7 +9696,10 @@
         <v>8</v>
       </c>
       <c r="G263" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="H263">
+        <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
@@ -9275,22 +9707,22 @@
         <v>46150</v>
       </c>
       <c r="B264" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C264" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D264" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E264" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F264" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G264" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H264">
         <v>0</v>
@@ -9301,13 +9733,13 @@
         <v>46150</v>
       </c>
       <c r="B265" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C265" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D265" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E265" t="s">
         <v>29</v>
@@ -9327,13 +9759,13 @@
         <v>46150</v>
       </c>
       <c r="B266" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C266" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="D266" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E266" t="s">
         <v>29</v>
@@ -9342,7 +9774,7 @@
         <v>8</v>
       </c>
       <c r="G266" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H266">
         <v>0</v>
@@ -9353,22 +9785,22 @@
         <v>46150</v>
       </c>
       <c r="B267" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C267" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="D267" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E267" t="s">
         <v>29</v>
       </c>
       <c r="F267" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G267" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H267">
         <v>0</v>
@@ -9379,13 +9811,13 @@
         <v>46150</v>
       </c>
       <c r="B268" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C268" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="D268" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E268" t="s">
         <v>29</v>
@@ -9405,25 +9837,22 @@
         <v>46150</v>
       </c>
       <c r="B269" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C269" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="D269" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E269" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F269" t="s">
         <v>7</v>
       </c>
       <c r="G269" t="s">
         <v>19</v>
-      </c>
-      <c r="H269">
-        <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
@@ -9431,13 +9860,13 @@
         <v>46150</v>
       </c>
       <c r="B270" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C270" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="D270" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E270" t="s">
         <v>29</v>
@@ -9457,22 +9886,25 @@
         <v>46150</v>
       </c>
       <c r="B271" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C271" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="D271" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E271" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F271" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G271" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="H271">
+        <v>0</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
@@ -9480,13 +9912,13 @@
         <v>46150</v>
       </c>
       <c r="B272" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C272" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="D272" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E272" t="s">
         <v>29</v>
@@ -9506,19 +9938,19 @@
         <v>46150</v>
       </c>
       <c r="B273" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C273" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D273" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E273" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F273" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G273" t="s">
         <v>17</v>
@@ -9532,13 +9964,13 @@
         <v>46150</v>
       </c>
       <c r="B274" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C274" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D274" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E274" t="s">
         <v>29</v>
@@ -9558,13 +9990,13 @@
         <v>46150</v>
       </c>
       <c r="B275" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C275" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="D275" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E275" t="s">
         <v>31</v>
@@ -9584,16 +10016,16 @@
         <v>46150</v>
       </c>
       <c r="B276" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C276" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D276" t="s">
-        <v>13</v>
+        <v>496</v>
       </c>
       <c r="E276" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F276" t="s">
         <v>8</v>
@@ -9610,19 +10042,19 @@
         <v>46150</v>
       </c>
       <c r="B277" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C277" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D277" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E277" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F277" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G277" t="s">
         <v>17</v>
@@ -9636,22 +10068,22 @@
         <v>46150</v>
       </c>
       <c r="B278" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C278" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="D278" t="s">
-        <v>496</v>
+        <v>26</v>
       </c>
       <c r="E278" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F278" t="s">
         <v>8</v>
       </c>
       <c r="G278" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H278">
         <v>0</v>
@@ -9662,19 +10094,19 @@
         <v>46150</v>
       </c>
       <c r="B279" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C279" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D279" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E279" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F279" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G279" t="s">
         <v>17</v>
@@ -9688,22 +10120,22 @@
         <v>46150</v>
       </c>
       <c r="B280" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C280" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D280" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E280" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F280" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G280" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H280">
         <v>0</v>
@@ -9714,13 +10146,13 @@
         <v>46150</v>
       </c>
       <c r="B281" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C281" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="D281" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="E281" t="s">
         <v>31</v>
@@ -9740,13 +10172,13 @@
         <v>46150</v>
       </c>
       <c r="B282" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C282" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="D282" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E282" t="s">
         <v>31</v>
@@ -9755,7 +10187,7 @@
         <v>7</v>
       </c>
       <c r="G282" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H282">
         <v>0</v>
@@ -9766,19 +10198,19 @@
         <v>46150</v>
       </c>
       <c r="B283" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C283" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="D283" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E283" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F283" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G283" t="s">
         <v>17</v>
@@ -9792,13 +10224,13 @@
         <v>46150</v>
       </c>
       <c r="B284" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="C284" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="D284" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E284" t="s">
         <v>31</v>
@@ -9807,7 +10239,7 @@
         <v>7</v>
       </c>
       <c r="G284" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H284">
         <v>0</v>
@@ -9818,19 +10250,19 @@
         <v>46150</v>
       </c>
       <c r="B285" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="C285" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D285" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="E285" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F285" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G285" t="s">
         <v>17</v>
@@ -9844,19 +10276,19 @@
         <v>46150</v>
       </c>
       <c r="B286" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C286" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D286" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E286" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F286" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G286" t="s">
         <v>17</v>
@@ -9870,13 +10302,13 @@
         <v>46150</v>
       </c>
       <c r="B287" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C287" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D287" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E287" t="s">
         <v>31</v>
@@ -9896,13 +10328,13 @@
         <v>46150</v>
       </c>
       <c r="B288" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C288" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D288" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E288" t="s">
         <v>29</v>
@@ -9922,10 +10354,10 @@
         <v>46150</v>
       </c>
       <c r="B289" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C289" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D289" t="s">
         <v>23</v>
@@ -9937,7 +10369,7 @@
         <v>7</v>
       </c>
       <c r="G289" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H289">
         <v>0</v>
@@ -9948,13 +10380,13 @@
         <v>46150</v>
       </c>
       <c r="B290" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C290" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D290" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E290" t="s">
         <v>29</v>
@@ -9974,22 +10406,22 @@
         <v>46150</v>
       </c>
       <c r="B291" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="C291" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D291" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="E291" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F291" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G291" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H291">
         <v>0</v>
@@ -10000,22 +10432,22 @@
         <v>46150</v>
       </c>
       <c r="B292" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C292" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D292" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E292" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F292" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G292" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H292">
         <v>0</v>
@@ -10026,13 +10458,13 @@
         <v>46150</v>
       </c>
       <c r="B293" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C293" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D293" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E293" t="s">
         <v>29</v>
@@ -10041,7 +10473,7 @@
         <v>8</v>
       </c>
       <c r="G293" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H293">
         <v>0</v>
@@ -10052,22 +10484,22 @@
         <v>46150</v>
       </c>
       <c r="B294" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C294" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D294" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E294" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F294" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G294" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H294">
         <v>0</v>
@@ -10078,13 +10510,13 @@
         <v>46150</v>
       </c>
       <c r="B295" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C295" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D295" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E295" t="s">
         <v>29</v>
@@ -10093,10 +10525,10 @@
         <v>8</v>
       </c>
       <c r="G295" t="s">
-        <v>17</v>
-      </c>
-      <c r="H295">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="H295" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
@@ -10104,13 +10536,13 @@
         <v>46150</v>
       </c>
       <c r="B296" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="C296" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D296" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E296" t="s">
         <v>29</v>
@@ -10119,7 +10551,7 @@
         <v>8</v>
       </c>
       <c r="G296" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H296">
         <v>0</v>
@@ -10130,13 +10562,13 @@
         <v>46150</v>
       </c>
       <c r="B297" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="C297" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="D297" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E297" t="s">
         <v>29</v>
@@ -10145,10 +10577,10 @@
         <v>8</v>
       </c>
       <c r="G297" t="s">
-        <v>36</v>
-      </c>
-      <c r="H297" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="H297">
+        <v>0</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
@@ -10156,22 +10588,22 @@
         <v>46150</v>
       </c>
       <c r="B298" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C298" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D298" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E298" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F298" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G298" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H298">
         <v>0</v>
@@ -10182,13 +10614,13 @@
         <v>46150</v>
       </c>
       <c r="B299" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="C299" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="D299" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E299" t="s">
         <v>29</v>
@@ -10208,22 +10640,22 @@
         <v>46150</v>
       </c>
       <c r="B300" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C300" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="D300" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E300" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F300" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G300" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H300">
         <v>0</v>
@@ -10234,22 +10666,22 @@
         <v>46150</v>
       </c>
       <c r="B301" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C301" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="D301" t="s">
-        <v>20</v>
+        <v>496</v>
       </c>
       <c r="E301" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F301" t="s">
         <v>8</v>
       </c>
       <c r="G301" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H301">
         <v>0</v>
@@ -10260,13 +10692,13 @@
         <v>46150</v>
       </c>
       <c r="B302" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C302" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="D302" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E302" t="s">
         <v>29</v>
@@ -10275,7 +10707,7 @@
         <v>8</v>
       </c>
       <c r="G302" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H302">
         <v>0</v>
@@ -10286,22 +10718,22 @@
         <v>46150</v>
       </c>
       <c r="B303" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C303" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="D303" t="s">
-        <v>496</v>
+        <v>12</v>
       </c>
       <c r="E303" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F303" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G303" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H303">
         <v>0</v>
@@ -10312,19 +10744,19 @@
         <v>46150</v>
       </c>
       <c r="B304" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C304" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D304" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E304" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F304" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G304" t="s">
         <v>17</v>
@@ -10338,19 +10770,19 @@
         <v>46150</v>
       </c>
       <c r="B305" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C305" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="D305" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E305" t="s">
         <v>29</v>
       </c>
       <c r="F305" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G305" t="s">
         <v>17</v>
@@ -10364,19 +10796,19 @@
         <v>46150</v>
       </c>
       <c r="B306" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C306" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D306" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E306" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F306" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G306" t="s">
         <v>17</v>
@@ -10390,13 +10822,13 @@
         <v>46150</v>
       </c>
       <c r="B307" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C307" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="D307" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E307" t="s">
         <v>29</v>
@@ -10416,13 +10848,13 @@
         <v>46150</v>
       </c>
       <c r="B308" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C308" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="D308" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E308" t="s">
         <v>29</v>
@@ -10439,19 +10871,19 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B309" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C309" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="D309" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E309" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F309" t="s">
         <v>8</v>
@@ -10465,22 +10897,22 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B310" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C310" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="D310" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E310" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F310" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G310" t="s">
         <v>17</v>
@@ -10494,19 +10926,19 @@
         <v>46153</v>
       </c>
       <c r="B311" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C311" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D311" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E311" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F311" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G311" t="s">
         <v>17</v>
@@ -10520,16 +10952,16 @@
         <v>46153</v>
       </c>
       <c r="B312" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="C312" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="D312" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E312" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F312" t="s">
         <v>7</v>
@@ -10538,6 +10970,1901 @@
         <v>17</v>
       </c>
       <c r="H312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A313" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B313" t="s">
+        <v>677</v>
+      </c>
+      <c r="C313" t="s">
+        <v>678</v>
+      </c>
+      <c r="D313" t="s">
+        <v>14</v>
+      </c>
+      <c r="E313" t="s">
+        <v>29</v>
+      </c>
+      <c r="F313" t="s">
+        <v>8</v>
+      </c>
+      <c r="G313" t="s">
+        <v>19</v>
+      </c>
+      <c r="H313">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A314" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B314" t="s">
+        <v>679</v>
+      </c>
+      <c r="C314" t="s">
+        <v>680</v>
+      </c>
+      <c r="D314" t="s">
+        <v>42</v>
+      </c>
+      <c r="E314" t="s">
+        <v>29</v>
+      </c>
+      <c r="F314" t="s">
+        <v>8</v>
+      </c>
+      <c r="G314" t="s">
+        <v>18</v>
+      </c>
+      <c r="H314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A315" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B315" t="s">
+        <v>681</v>
+      </c>
+      <c r="C315" t="s">
+        <v>682</v>
+      </c>
+      <c r="D315" t="s">
+        <v>6</v>
+      </c>
+      <c r="E315" t="s">
+        <v>29</v>
+      </c>
+      <c r="F315" t="s">
+        <v>8</v>
+      </c>
+      <c r="G315" t="s">
+        <v>18</v>
+      </c>
+      <c r="H315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A316" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B316" t="s">
+        <v>683</v>
+      </c>
+      <c r="C316" t="s">
+        <v>684</v>
+      </c>
+      <c r="D316" t="s">
+        <v>11</v>
+      </c>
+      <c r="E316" t="s">
+        <v>29</v>
+      </c>
+      <c r="F316" t="s">
+        <v>8</v>
+      </c>
+      <c r="G316" t="s">
+        <v>19</v>
+      </c>
+      <c r="H316">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A317" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B317" t="s">
+        <v>685</v>
+      </c>
+      <c r="C317" t="s">
+        <v>686</v>
+      </c>
+      <c r="D317" t="s">
+        <v>13</v>
+      </c>
+      <c r="E317" t="s">
+        <v>29</v>
+      </c>
+      <c r="F317" t="s">
+        <v>8</v>
+      </c>
+      <c r="G317" t="s">
+        <v>17</v>
+      </c>
+      <c r="H317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A318" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B318" t="s">
+        <v>687</v>
+      </c>
+      <c r="C318" t="s">
+        <v>688</v>
+      </c>
+      <c r="D318" t="s">
+        <v>42</v>
+      </c>
+      <c r="E318" t="s">
+        <v>29</v>
+      </c>
+      <c r="F318" t="s">
+        <v>8</v>
+      </c>
+      <c r="G318" t="s">
+        <v>18</v>
+      </c>
+      <c r="H318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A319" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B319" t="s">
+        <v>689</v>
+      </c>
+      <c r="C319" t="s">
+        <v>690</v>
+      </c>
+      <c r="D319" t="s">
+        <v>9</v>
+      </c>
+      <c r="E319" t="s">
+        <v>31</v>
+      </c>
+      <c r="F319" t="s">
+        <v>7</v>
+      </c>
+      <c r="G319" t="s">
+        <v>36</v>
+      </c>
+      <c r="H319" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A320" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B320" t="s">
+        <v>281</v>
+      </c>
+      <c r="C320" t="s">
+        <v>282</v>
+      </c>
+      <c r="D320" t="s">
+        <v>22</v>
+      </c>
+      <c r="E320" t="s">
+        <v>31</v>
+      </c>
+      <c r="F320" t="s">
+        <v>7</v>
+      </c>
+      <c r="G320" t="s">
+        <v>17</v>
+      </c>
+      <c r="H320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A321" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B321" t="s">
+        <v>691</v>
+      </c>
+      <c r="C321" t="s">
+        <v>692</v>
+      </c>
+      <c r="D321" t="s">
+        <v>20</v>
+      </c>
+      <c r="E321" t="s">
+        <v>29</v>
+      </c>
+      <c r="F321" t="s">
+        <v>8</v>
+      </c>
+      <c r="G321" t="s">
+        <v>17</v>
+      </c>
+      <c r="H321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A322" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B322" t="s">
+        <v>693</v>
+      </c>
+      <c r="C322" t="s">
+        <v>694</v>
+      </c>
+      <c r="D322" t="s">
+        <v>15</v>
+      </c>
+      <c r="E322" t="s">
+        <v>29</v>
+      </c>
+      <c r="F322" t="s">
+        <v>8</v>
+      </c>
+      <c r="G322" t="s">
+        <v>18</v>
+      </c>
+      <c r="H322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A323" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B323" t="s">
+        <v>695</v>
+      </c>
+      <c r="C323" t="s">
+        <v>696</v>
+      </c>
+      <c r="D323" t="s">
+        <v>13</v>
+      </c>
+      <c r="E323" t="s">
+        <v>29</v>
+      </c>
+      <c r="F323" t="s">
+        <v>8</v>
+      </c>
+      <c r="G323" t="s">
+        <v>17</v>
+      </c>
+      <c r="H323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A324" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B324" t="s">
+        <v>697</v>
+      </c>
+      <c r="C324" t="s">
+        <v>698</v>
+      </c>
+      <c r="D324" t="s">
+        <v>14</v>
+      </c>
+      <c r="E324" t="s">
+        <v>29</v>
+      </c>
+      <c r="F324" t="s">
+        <v>8</v>
+      </c>
+      <c r="G324" t="s">
+        <v>17</v>
+      </c>
+      <c r="H324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A325" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B325" t="s">
+        <v>699</v>
+      </c>
+      <c r="C325" t="s">
+        <v>700</v>
+      </c>
+      <c r="D325" t="s">
+        <v>21</v>
+      </c>
+      <c r="E325" t="s">
+        <v>29</v>
+      </c>
+      <c r="F325" t="s">
+        <v>8</v>
+      </c>
+      <c r="G325" t="s">
+        <v>17</v>
+      </c>
+      <c r="H325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A326" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B326" t="s">
+        <v>701</v>
+      </c>
+      <c r="C326" t="s">
+        <v>702</v>
+      </c>
+      <c r="D326" t="s">
+        <v>11</v>
+      </c>
+      <c r="E326" t="s">
+        <v>29</v>
+      </c>
+      <c r="F326" t="s">
+        <v>8</v>
+      </c>
+      <c r="G326" t="s">
+        <v>19</v>
+      </c>
+      <c r="H326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A327" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B327" t="s">
+        <v>703</v>
+      </c>
+      <c r="C327" t="s">
+        <v>704</v>
+      </c>
+      <c r="D327" t="s">
+        <v>15</v>
+      </c>
+      <c r="E327" t="s">
+        <v>29</v>
+      </c>
+      <c r="F327" t="s">
+        <v>8</v>
+      </c>
+      <c r="G327" t="s">
+        <v>17</v>
+      </c>
+      <c r="H327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A328" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B328" t="s">
+        <v>705</v>
+      </c>
+      <c r="C328" t="s">
+        <v>706</v>
+      </c>
+      <c r="D328" t="s">
+        <v>41</v>
+      </c>
+      <c r="E328" t="s">
+        <v>31</v>
+      </c>
+      <c r="F328" t="s">
+        <v>7</v>
+      </c>
+      <c r="G328" t="s">
+        <v>17</v>
+      </c>
+      <c r="H328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A329" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B329" t="s">
+        <v>707</v>
+      </c>
+      <c r="C329" t="s">
+        <v>708</v>
+      </c>
+      <c r="D329" t="s">
+        <v>35</v>
+      </c>
+      <c r="E329" t="s">
+        <v>31</v>
+      </c>
+      <c r="F329" t="s">
+        <v>7</v>
+      </c>
+      <c r="G329" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A330" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B330" t="s">
+        <v>709</v>
+      </c>
+      <c r="C330" t="s">
+        <v>710</v>
+      </c>
+      <c r="D330" t="s">
+        <v>20</v>
+      </c>
+      <c r="E330" t="s">
+        <v>29</v>
+      </c>
+      <c r="F330" t="s">
+        <v>8</v>
+      </c>
+      <c r="G330" t="s">
+        <v>19</v>
+      </c>
+      <c r="H330">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A331" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B331" t="s">
+        <v>711</v>
+      </c>
+      <c r="C331" t="s">
+        <v>712</v>
+      </c>
+      <c r="D331" t="s">
+        <v>6</v>
+      </c>
+      <c r="E331" t="s">
+        <v>29</v>
+      </c>
+      <c r="F331" t="s">
+        <v>8</v>
+      </c>
+      <c r="G331" t="s">
+        <v>17</v>
+      </c>
+      <c r="H331">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A332" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B332" t="s">
+        <v>713</v>
+      </c>
+      <c r="C332" t="s">
+        <v>714</v>
+      </c>
+      <c r="D332" t="s">
+        <v>20</v>
+      </c>
+      <c r="E332" t="s">
+        <v>29</v>
+      </c>
+      <c r="F332" t="s">
+        <v>8</v>
+      </c>
+      <c r="G332" t="s">
+        <v>17</v>
+      </c>
+      <c r="H332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A333" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B333" t="s">
+        <v>715</v>
+      </c>
+      <c r="C333" t="s">
+        <v>716</v>
+      </c>
+      <c r="D333" t="s">
+        <v>27</v>
+      </c>
+      <c r="E333" t="s">
+        <v>31</v>
+      </c>
+      <c r="F333" t="s">
+        <v>7</v>
+      </c>
+      <c r="G333" t="s">
+        <v>18</v>
+      </c>
+      <c r="H333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A334" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B334" t="s">
+        <v>438</v>
+      </c>
+      <c r="C334" t="s">
+        <v>439</v>
+      </c>
+      <c r="D334" t="s">
+        <v>15</v>
+      </c>
+      <c r="E334" t="s">
+        <v>29</v>
+      </c>
+      <c r="F334" t="s">
+        <v>8</v>
+      </c>
+      <c r="G334" t="s">
+        <v>17</v>
+      </c>
+      <c r="H334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A335" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B335" t="s">
+        <v>717</v>
+      </c>
+      <c r="C335" t="s">
+        <v>718</v>
+      </c>
+      <c r="D335" t="s">
+        <v>14</v>
+      </c>
+      <c r="E335" t="s">
+        <v>29</v>
+      </c>
+      <c r="F335" t="s">
+        <v>8</v>
+      </c>
+      <c r="G335" t="s">
+        <v>17</v>
+      </c>
+      <c r="H335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A336" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B336" t="s">
+        <v>719</v>
+      </c>
+      <c r="C336" t="s">
+        <v>720</v>
+      </c>
+      <c r="D336" t="s">
+        <v>21</v>
+      </c>
+      <c r="E336" t="s">
+        <v>29</v>
+      </c>
+      <c r="F336" t="s">
+        <v>8</v>
+      </c>
+      <c r="G336" t="s">
+        <v>17</v>
+      </c>
+      <c r="H336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A337" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B337" t="s">
+        <v>721</v>
+      </c>
+      <c r="C337" t="s">
+        <v>722</v>
+      </c>
+      <c r="D337" t="s">
+        <v>27</v>
+      </c>
+      <c r="E337" t="s">
+        <v>31</v>
+      </c>
+      <c r="F337" t="s">
+        <v>7</v>
+      </c>
+      <c r="G337" t="s">
+        <v>17</v>
+      </c>
+      <c r="H337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A338" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B338" t="s">
+        <v>723</v>
+      </c>
+      <c r="C338" t="s">
+        <v>724</v>
+      </c>
+      <c r="D338" t="s">
+        <v>15</v>
+      </c>
+      <c r="E338" t="s">
+        <v>29</v>
+      </c>
+      <c r="F338" t="s">
+        <v>8</v>
+      </c>
+      <c r="G338" t="s">
+        <v>17</v>
+      </c>
+      <c r="H338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A339" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B339" t="s">
+        <v>725</v>
+      </c>
+      <c r="C339" t="s">
+        <v>726</v>
+      </c>
+      <c r="D339" t="s">
+        <v>13</v>
+      </c>
+      <c r="E339" t="s">
+        <v>29</v>
+      </c>
+      <c r="F339" t="s">
+        <v>8</v>
+      </c>
+      <c r="G339" t="s">
+        <v>17</v>
+      </c>
+      <c r="H339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A340" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B340" t="s">
+        <v>727</v>
+      </c>
+      <c r="C340" t="s">
+        <v>728</v>
+      </c>
+      <c r="D340" t="s">
+        <v>13</v>
+      </c>
+      <c r="E340" t="s">
+        <v>29</v>
+      </c>
+      <c r="F340" t="s">
+        <v>8</v>
+      </c>
+      <c r="G340" t="s">
+        <v>17</v>
+      </c>
+      <c r="H340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A341" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B341" t="s">
+        <v>729</v>
+      </c>
+      <c r="C341" t="s">
+        <v>730</v>
+      </c>
+      <c r="D341" t="s">
+        <v>496</v>
+      </c>
+      <c r="E341" t="s">
+        <v>31</v>
+      </c>
+      <c r="F341" t="s">
+        <v>8</v>
+      </c>
+      <c r="G341" t="s">
+        <v>17</v>
+      </c>
+      <c r="H341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A342" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B342" t="s">
+        <v>731</v>
+      </c>
+      <c r="C342" t="s">
+        <v>732</v>
+      </c>
+      <c r="D342" t="s">
+        <v>9</v>
+      </c>
+      <c r="E342" t="s">
+        <v>31</v>
+      </c>
+      <c r="F342" t="s">
+        <v>7</v>
+      </c>
+      <c r="G342" t="s">
+        <v>36</v>
+      </c>
+      <c r="H342" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A343" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B343" t="s">
+        <v>733</v>
+      </c>
+      <c r="C343" t="s">
+        <v>734</v>
+      </c>
+      <c r="D343" t="s">
+        <v>15</v>
+      </c>
+      <c r="E343" t="s">
+        <v>29</v>
+      </c>
+      <c r="F343" t="s">
+        <v>8</v>
+      </c>
+      <c r="G343" t="s">
+        <v>17</v>
+      </c>
+      <c r="H343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A344" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B344" t="s">
+        <v>735</v>
+      </c>
+      <c r="C344" t="s">
+        <v>736</v>
+      </c>
+      <c r="D344" t="s">
+        <v>15</v>
+      </c>
+      <c r="E344" t="s">
+        <v>29</v>
+      </c>
+      <c r="F344" t="s">
+        <v>8</v>
+      </c>
+      <c r="G344" t="s">
+        <v>17</v>
+      </c>
+      <c r="H344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A345" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B345" t="s">
+        <v>737</v>
+      </c>
+      <c r="C345" t="s">
+        <v>738</v>
+      </c>
+      <c r="D345" t="s">
+        <v>38</v>
+      </c>
+      <c r="E345" t="s">
+        <v>31</v>
+      </c>
+      <c r="F345" t="s">
+        <v>7</v>
+      </c>
+      <c r="G345" t="s">
+        <v>17</v>
+      </c>
+      <c r="H345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A346" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B346" t="s">
+        <v>739</v>
+      </c>
+      <c r="C346" t="s">
+        <v>740</v>
+      </c>
+      <c r="D346" t="s">
+        <v>496</v>
+      </c>
+      <c r="E346" t="s">
+        <v>31</v>
+      </c>
+      <c r="F346" t="s">
+        <v>8</v>
+      </c>
+      <c r="G346" t="s">
+        <v>17</v>
+      </c>
+      <c r="H346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A347" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B347" t="s">
+        <v>741</v>
+      </c>
+      <c r="C347" t="s">
+        <v>742</v>
+      </c>
+      <c r="D347" t="s">
+        <v>13</v>
+      </c>
+      <c r="E347" t="s">
+        <v>29</v>
+      </c>
+      <c r="F347" t="s">
+        <v>8</v>
+      </c>
+      <c r="G347" t="s">
+        <v>17</v>
+      </c>
+      <c r="H347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A348" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B348" t="s">
+        <v>743</v>
+      </c>
+      <c r="C348" t="s">
+        <v>744</v>
+      </c>
+      <c r="D348" t="s">
+        <v>26</v>
+      </c>
+      <c r="E348" t="s">
+        <v>29</v>
+      </c>
+      <c r="F348" t="s">
+        <v>8</v>
+      </c>
+      <c r="G348" t="s">
+        <v>17</v>
+      </c>
+      <c r="H348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A349" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B349" t="s">
+        <v>745</v>
+      </c>
+      <c r="C349" t="s">
+        <v>746</v>
+      </c>
+      <c r="D349" t="s">
+        <v>14</v>
+      </c>
+      <c r="E349" t="s">
+        <v>29</v>
+      </c>
+      <c r="F349" t="s">
+        <v>8</v>
+      </c>
+      <c r="G349" t="s">
+        <v>36</v>
+      </c>
+      <c r="H349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A350" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B350" t="s">
+        <v>747</v>
+      </c>
+      <c r="C350" t="s">
+        <v>748</v>
+      </c>
+      <c r="D350" t="s">
+        <v>38</v>
+      </c>
+      <c r="E350" t="s">
+        <v>31</v>
+      </c>
+      <c r="F350" t="s">
+        <v>7</v>
+      </c>
+      <c r="G350" t="s">
+        <v>17</v>
+      </c>
+      <c r="H350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A351" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B351" t="s">
+        <v>749</v>
+      </c>
+      <c r="C351" t="s">
+        <v>750</v>
+      </c>
+      <c r="D351" t="s">
+        <v>21</v>
+      </c>
+      <c r="E351" t="s">
+        <v>29</v>
+      </c>
+      <c r="F351" t="s">
+        <v>8</v>
+      </c>
+      <c r="G351" t="s">
+        <v>17</v>
+      </c>
+      <c r="H351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A352" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B352" t="s">
+        <v>751</v>
+      </c>
+      <c r="C352" t="s">
+        <v>752</v>
+      </c>
+      <c r="D352" t="s">
+        <v>15</v>
+      </c>
+      <c r="E352" t="s">
+        <v>29</v>
+      </c>
+      <c r="F352" t="s">
+        <v>8</v>
+      </c>
+      <c r="G352" t="s">
+        <v>17</v>
+      </c>
+      <c r="H352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A353" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B353" t="s">
+        <v>753</v>
+      </c>
+      <c r="C353" t="s">
+        <v>754</v>
+      </c>
+      <c r="D353" t="s">
+        <v>21</v>
+      </c>
+      <c r="E353" t="s">
+        <v>29</v>
+      </c>
+      <c r="F353" t="s">
+        <v>8</v>
+      </c>
+      <c r="G353" t="s">
+        <v>19</v>
+      </c>
+      <c r="H353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A354" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B354" t="s">
+        <v>755</v>
+      </c>
+      <c r="C354" t="s">
+        <v>756</v>
+      </c>
+      <c r="D354" t="s">
+        <v>23</v>
+      </c>
+      <c r="E354" t="s">
+        <v>31</v>
+      </c>
+      <c r="F354" t="s">
+        <v>7</v>
+      </c>
+      <c r="G354" t="s">
+        <v>17</v>
+      </c>
+      <c r="H354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A355" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B355" t="s">
+        <v>757</v>
+      </c>
+      <c r="C355" t="s">
+        <v>758</v>
+      </c>
+      <c r="D355" t="s">
+        <v>20</v>
+      </c>
+      <c r="E355" t="s">
+        <v>29</v>
+      </c>
+      <c r="F355" t="s">
+        <v>8</v>
+      </c>
+      <c r="G355" t="s">
+        <v>17</v>
+      </c>
+      <c r="H355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A356" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B356" t="s">
+        <v>759</v>
+      </c>
+      <c r="C356" t="s">
+        <v>760</v>
+      </c>
+      <c r="D356" t="s">
+        <v>11</v>
+      </c>
+      <c r="E356" t="s">
+        <v>29</v>
+      </c>
+      <c r="F356" t="s">
+        <v>8</v>
+      </c>
+      <c r="G356" t="s">
+        <v>17</v>
+      </c>
+      <c r="H356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A357" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B357" t="s">
+        <v>761</v>
+      </c>
+      <c r="C357" t="s">
+        <v>762</v>
+      </c>
+      <c r="D357" t="s">
+        <v>11</v>
+      </c>
+      <c r="E357" t="s">
+        <v>29</v>
+      </c>
+      <c r="F357" t="s">
+        <v>8</v>
+      </c>
+      <c r="G357" t="s">
+        <v>17</v>
+      </c>
+      <c r="H357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A358" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B358" t="s">
+        <v>763</v>
+      </c>
+      <c r="C358" t="s">
+        <v>764</v>
+      </c>
+      <c r="D358" t="s">
+        <v>11</v>
+      </c>
+      <c r="E358" t="s">
+        <v>29</v>
+      </c>
+      <c r="F358" t="s">
+        <v>8</v>
+      </c>
+      <c r="G358" t="s">
+        <v>18</v>
+      </c>
+      <c r="H358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A359" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B359" t="s">
+        <v>765</v>
+      </c>
+      <c r="C359" t="s">
+        <v>766</v>
+      </c>
+      <c r="D359" t="s">
+        <v>22</v>
+      </c>
+      <c r="E359" t="s">
+        <v>31</v>
+      </c>
+      <c r="F359" t="s">
+        <v>7</v>
+      </c>
+      <c r="G359" t="s">
+        <v>17</v>
+      </c>
+      <c r="H359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A360" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B360" t="s">
+        <v>767</v>
+      </c>
+      <c r="C360" t="s">
+        <v>768</v>
+      </c>
+      <c r="D360" t="s">
+        <v>13</v>
+      </c>
+      <c r="E360" t="s">
+        <v>29</v>
+      </c>
+      <c r="F360" t="s">
+        <v>8</v>
+      </c>
+      <c r="G360" t="s">
+        <v>18</v>
+      </c>
+      <c r="H360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A361" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B361" t="s">
+        <v>769</v>
+      </c>
+      <c r="C361" t="s">
+        <v>770</v>
+      </c>
+      <c r="D361" t="s">
+        <v>27</v>
+      </c>
+      <c r="E361" t="s">
+        <v>31</v>
+      </c>
+      <c r="F361" t="s">
+        <v>7</v>
+      </c>
+      <c r="G361" t="s">
+        <v>36</v>
+      </c>
+      <c r="H361" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A362" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B362" t="s">
+        <v>771</v>
+      </c>
+      <c r="C362" t="s">
+        <v>772</v>
+      </c>
+      <c r="D362" t="s">
+        <v>38</v>
+      </c>
+      <c r="E362" t="s">
+        <v>31</v>
+      </c>
+      <c r="F362" t="s">
+        <v>7</v>
+      </c>
+      <c r="G362" t="s">
+        <v>17</v>
+      </c>
+      <c r="H362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A363" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B363" t="s">
+        <v>773</v>
+      </c>
+      <c r="C363" t="s">
+        <v>774</v>
+      </c>
+      <c r="D363" t="s">
+        <v>6</v>
+      </c>
+      <c r="E363" t="s">
+        <v>29</v>
+      </c>
+      <c r="F363" t="s">
+        <v>8</v>
+      </c>
+      <c r="G363" t="s">
+        <v>17</v>
+      </c>
+      <c r="H363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A364" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B364" t="s">
+        <v>775</v>
+      </c>
+      <c r="C364" t="s">
+        <v>776</v>
+      </c>
+      <c r="D364" t="s">
+        <v>11</v>
+      </c>
+      <c r="E364" t="s">
+        <v>29</v>
+      </c>
+      <c r="F364" t="s">
+        <v>8</v>
+      </c>
+      <c r="G364" t="s">
+        <v>18</v>
+      </c>
+      <c r="H364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A365" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B365" t="s">
+        <v>777</v>
+      </c>
+      <c r="C365" t="s">
+        <v>778</v>
+      </c>
+      <c r="D365" t="s">
+        <v>14</v>
+      </c>
+      <c r="E365" t="s">
+        <v>29</v>
+      </c>
+      <c r="F365" t="s">
+        <v>8</v>
+      </c>
+      <c r="G365" t="s">
+        <v>17</v>
+      </c>
+      <c r="H365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A366" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B366" t="s">
+        <v>779</v>
+      </c>
+      <c r="C366" t="s">
+        <v>780</v>
+      </c>
+      <c r="D366" t="s">
+        <v>13</v>
+      </c>
+      <c r="E366" t="s">
+        <v>29</v>
+      </c>
+      <c r="F366" t="s">
+        <v>8</v>
+      </c>
+      <c r="G366" t="s">
+        <v>17</v>
+      </c>
+      <c r="H366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A367" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B367" t="s">
+        <v>781</v>
+      </c>
+      <c r="C367" t="s">
+        <v>782</v>
+      </c>
+      <c r="D367" t="s">
+        <v>496</v>
+      </c>
+      <c r="E367" t="s">
+        <v>31</v>
+      </c>
+      <c r="F367" t="s">
+        <v>8</v>
+      </c>
+      <c r="G367" t="s">
+        <v>17</v>
+      </c>
+      <c r="H367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A368" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B368" t="s">
+        <v>783</v>
+      </c>
+      <c r="C368" t="s">
+        <v>784</v>
+      </c>
+      <c r="D368" t="s">
+        <v>15</v>
+      </c>
+      <c r="E368" t="s">
+        <v>29</v>
+      </c>
+      <c r="F368" t="s">
+        <v>8</v>
+      </c>
+      <c r="G368" t="s">
+        <v>19</v>
+      </c>
+      <c r="H368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A369" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B369" t="s">
+        <v>785</v>
+      </c>
+      <c r="C369" t="s">
+        <v>786</v>
+      </c>
+      <c r="D369" t="s">
+        <v>21</v>
+      </c>
+      <c r="E369" t="s">
+        <v>29</v>
+      </c>
+      <c r="F369" t="s">
+        <v>8</v>
+      </c>
+      <c r="G369" t="s">
+        <v>17</v>
+      </c>
+      <c r="H369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A370" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B370" t="s">
+        <v>787</v>
+      </c>
+      <c r="C370" t="s">
+        <v>788</v>
+      </c>
+      <c r="D370" t="s">
+        <v>11</v>
+      </c>
+      <c r="E370" t="s">
+        <v>29</v>
+      </c>
+      <c r="F370" t="s">
+        <v>8</v>
+      </c>
+      <c r="G370" t="s">
+        <v>17</v>
+      </c>
+      <c r="H370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A371" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B371" t="s">
+        <v>789</v>
+      </c>
+      <c r="C371" t="s">
+        <v>790</v>
+      </c>
+      <c r="D371" t="s">
+        <v>22</v>
+      </c>
+      <c r="E371" t="s">
+        <v>31</v>
+      </c>
+      <c r="F371" t="s">
+        <v>7</v>
+      </c>
+      <c r="G371" t="s">
+        <v>17</v>
+      </c>
+      <c r="H371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A372" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B372" t="s">
+        <v>791</v>
+      </c>
+      <c r="C372" t="s">
+        <v>792</v>
+      </c>
+      <c r="D372" t="s">
+        <v>26</v>
+      </c>
+      <c r="E372" t="s">
+        <v>29</v>
+      </c>
+      <c r="F372" t="s">
+        <v>8</v>
+      </c>
+      <c r="G372" t="s">
+        <v>17</v>
+      </c>
+      <c r="H372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A373" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B373" t="s">
+        <v>793</v>
+      </c>
+      <c r="C373" t="s">
+        <v>794</v>
+      </c>
+      <c r="D373" t="s">
+        <v>27</v>
+      </c>
+      <c r="E373" t="s">
+        <v>31</v>
+      </c>
+      <c r="F373" t="s">
+        <v>461</v>
+      </c>
+      <c r="G373" t="s">
+        <v>17</v>
+      </c>
+      <c r="H373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A374" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B374" t="s">
+        <v>795</v>
+      </c>
+      <c r="C374" t="s">
+        <v>796</v>
+      </c>
+      <c r="D374" t="s">
+        <v>13</v>
+      </c>
+      <c r="E374" t="s">
+        <v>29</v>
+      </c>
+      <c r="F374" t="s">
+        <v>8</v>
+      </c>
+      <c r="G374" t="s">
+        <v>17</v>
+      </c>
+      <c r="H374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A375" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B375" t="s">
+        <v>797</v>
+      </c>
+      <c r="C375" t="s">
+        <v>798</v>
+      </c>
+      <c r="D375" t="s">
+        <v>27</v>
+      </c>
+      <c r="E375" t="s">
+        <v>31</v>
+      </c>
+      <c r="F375" t="s">
+        <v>7</v>
+      </c>
+      <c r="G375" t="s">
+        <v>18</v>
+      </c>
+      <c r="H375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A376" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B376" t="s">
+        <v>799</v>
+      </c>
+      <c r="C376" t="s">
+        <v>800</v>
+      </c>
+      <c r="D376" t="s">
+        <v>14</v>
+      </c>
+      <c r="E376" t="s">
+        <v>29</v>
+      </c>
+      <c r="F376" t="s">
+        <v>8</v>
+      </c>
+      <c r="G376" t="s">
+        <v>19</v>
+      </c>
+      <c r="H376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A377" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B377" t="s">
+        <v>801</v>
+      </c>
+      <c r="C377" t="s">
+        <v>802</v>
+      </c>
+      <c r="D377" t="s">
+        <v>22</v>
+      </c>
+      <c r="E377" t="s">
+        <v>31</v>
+      </c>
+      <c r="F377" t="s">
+        <v>7</v>
+      </c>
+      <c r="G377" t="s">
+        <v>17</v>
+      </c>
+      <c r="H377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A378" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B378" t="s">
+        <v>803</v>
+      </c>
+      <c r="C378" t="s">
+        <v>804</v>
+      </c>
+      <c r="D378" t="s">
+        <v>6</v>
+      </c>
+      <c r="E378" t="s">
+        <v>29</v>
+      </c>
+      <c r="F378" t="s">
+        <v>8</v>
+      </c>
+      <c r="G378" t="s">
+        <v>17</v>
+      </c>
+      <c r="H378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A379" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B379" t="s">
+        <v>805</v>
+      </c>
+      <c r="C379" t="s">
+        <v>806</v>
+      </c>
+      <c r="D379" t="s">
+        <v>21</v>
+      </c>
+      <c r="E379" t="s">
+        <v>29</v>
+      </c>
+      <c r="F379" t="s">
+        <v>8</v>
+      </c>
+      <c r="G379" t="s">
+        <v>17</v>
+      </c>
+      <c r="H379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A380" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B380" t="s">
+        <v>807</v>
+      </c>
+      <c r="C380" t="s">
+        <v>808</v>
+      </c>
+      <c r="D380" t="s">
+        <v>15</v>
+      </c>
+      <c r="E380" t="s">
+        <v>29</v>
+      </c>
+      <c r="F380" t="s">
+        <v>8</v>
+      </c>
+      <c r="G380" t="s">
+        <v>17</v>
+      </c>
+      <c r="H380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A381" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B381" t="s">
+        <v>809</v>
+      </c>
+      <c r="C381" t="s">
+        <v>810</v>
+      </c>
+      <c r="D381" t="s">
+        <v>20</v>
+      </c>
+      <c r="E381" t="s">
+        <v>29</v>
+      </c>
+      <c r="F381" t="s">
+        <v>8</v>
+      </c>
+      <c r="G381" t="s">
+        <v>17</v>
+      </c>
+      <c r="H381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A382" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B382" t="s">
+        <v>811</v>
+      </c>
+      <c r="C382" t="s">
+        <v>812</v>
+      </c>
+      <c r="D382" t="s">
+        <v>13</v>
+      </c>
+      <c r="E382" t="s">
+        <v>29</v>
+      </c>
+      <c r="F382" t="s">
+        <v>8</v>
+      </c>
+      <c r="G382" t="s">
+        <v>17</v>
+      </c>
+      <c r="H382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A383" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B383" t="s">
+        <v>813</v>
+      </c>
+      <c r="C383" t="s">
+        <v>814</v>
+      </c>
+      <c r="D383" t="s">
+        <v>14</v>
+      </c>
+      <c r="E383" t="s">
+        <v>29</v>
+      </c>
+      <c r="F383" t="s">
+        <v>8</v>
+      </c>
+      <c r="G383" t="s">
+        <v>17</v>
+      </c>
+      <c r="H383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A384" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B384" t="s">
+        <v>815</v>
+      </c>
+      <c r="C384" t="s">
+        <v>816</v>
+      </c>
+      <c r="D384" t="s">
+        <v>42</v>
+      </c>
+      <c r="E384" t="s">
+        <v>29</v>
+      </c>
+      <c r="F384" t="s">
+        <v>8</v>
+      </c>
+      <c r="G384" t="s">
+        <v>17</v>
+      </c>
+      <c r="H384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A385" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B385" t="s">
+        <v>817</v>
+      </c>
+      <c r="C385" t="s">
+        <v>818</v>
+      </c>
+      <c r="D385" t="s">
+        <v>11</v>
+      </c>
+      <c r="E385" t="s">
+        <v>29</v>
+      </c>
+      <c r="F385" t="s">
+        <v>8</v>
+      </c>
+      <c r="G385" t="s">
+        <v>17</v>
+      </c>
+      <c r="H385">
         <v>0</v>
       </c>
     </row>
